--- a/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="742">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -1732,13 +1732,752 @@
   <si>
     <t xml:space="preserve">Web_SQL_Injection</t>
   </si>
+  <si>
+    <t xml:space="preserve">0.995868 ± 0.000121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995839 ± 0.000130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995868 ± 0.000121 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995841 ± 0.000128 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898896 ± 0.022358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897954 ± 0.017360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895331 ± 0.011207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990731 ± 0.000273 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514280 ± 0.022613 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888197 ± 0.025505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514280 ± 0.022613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625090 ± 0.024717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.230583 ± 0.018574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363666 ± 0.018201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.200487 ± 0.013458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351127 ± 0.024124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987224 ± 0.002190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985747 ± 0.001933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.985792 ± 0.002183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707422 ± 0.030732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579843 ± 0.011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614769 ± 0.007405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971206 ± 0.004882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968107 ± 0.000838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968073 ± 0.000816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968057 ± 0.000833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965659 ± 0.000902 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514057 ± 0.009289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500307 ± 0.021506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473830 ± 0.016348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484033 ± 0.009249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814750 ± 0.001998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855801 ± 0.003429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.794574 ± 0.001846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805856 ± 0.002186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854229 ± 0.010053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883069 ± 0.009629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834791 ± 0.009221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.847535 ± 0.010621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974014 ± 0.000831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973910 ± 0.000830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973949 ± 0.000832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972018 ± 0.000894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548421 ± 0.038528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580192 ± 0.054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531145 ± 0.049220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520565 ± 0.042029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.770086 ± 0.011077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799011 ± 0.039992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738468 ± 0.021009 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738468 ± 0.021009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761543 ± 0.011257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812079 ± 0.001702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867410 ± 0.014507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798277 ± 0.008138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804013 ± 0.004247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989538 ± 0.000804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989512 ± 0.000808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989494 ± 0.000803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989000 ± 0.000882 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989072 ± 0.000865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989006 ± 0.000869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988731 ± 0.000867 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544799 ± 0.019849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538258 ± 0.022955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516132 ± 0.020815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530277 ± 0.021688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543483 ± 0.019082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511733 ± 0.019666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513974 ± 0.021501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829854 ± 0.002401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850454 ± 0.002953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828617 ± 0.002553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838479 ± 0.002937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821283 ± 0.002277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818002 ± 0.002488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818751 ± 0.002578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870108 ± 0.007763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889796 ± 0.010851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860209 ± 0.009683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880297 ± 0.013872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857686 ± 0.008532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844756 ± 0.012759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862313 ± 0.008312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994210 ± 0.000283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994205 ± 0.000290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994200 ± 0.000285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993844 ± 0.000324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993636 ± 0.000448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993731 ± 0.000384 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993760 ± 0.000306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505476 ± 0.018710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533130 ± 0.015803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480020 ± 0.019237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517856 ± 0.015697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492066 ± 0.017530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466882 ± 0.018453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473179 ± 0.019621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810274 ± 0.001528 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838628 ± 0.000987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810274 ± 0.001528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805702 ± 0.001476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828687 ± 0.000902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802993 ± 0.001524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796573 ± 0.001371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799473 ± 0.001612 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844365 ± 0.002965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882828 ± 0.002619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837768 ± 0.003225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870813 ± 0.002574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836126 ± 0.003035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827704 ± 0.003207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836279 ± 0.003146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.225849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.198112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.890689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.229398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.750818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.196040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.257268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.211344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.192183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.201434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.204746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.202750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2429094216694166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9286091784228083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3065005314829971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24640036109307917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7456257814915517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18999128346892563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24161345245704607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.223220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.215866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.212510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.195029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.205379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.187273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.195647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.198577</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2051,7 +2790,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="117">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2280,84 +3019,232 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2368,148 +3255,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3173,7 +3920,7 @@
       <c r="E32" s="34"/>
       <c r="F32" s="35"/>
     </row>
-    <row r="33" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
         <v>56</v>
       </c>
@@ -3197,7 +3944,7 @@
       <c r="E34" s="34"/>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
         <v>58</v>
       </c>
@@ -3223,7 +3970,7 @@
       <c r="E36" s="34"/>
       <c r="F36" s="35"/>
     </row>
-    <row r="37" customFormat="false" ht="76.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
         <v>61</v>
       </c>
@@ -3247,7 +3994,7 @@
       <c r="E38" s="34"/>
       <c r="F38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
         <v>64</v>
       </c>
@@ -3271,7 +4018,7 @@
       <c r="E40" s="34"/>
       <c r="F40" s="35"/>
     </row>
-    <row r="41" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
         <v>66</v>
       </c>
@@ -3984,7 +4731,7 @@
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="35"/>
     </row>
-    <row r="24" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -4015,7 +4762,6 @@
       <c r="J24" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="K24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="n">
@@ -4024,14 +4770,14 @@
       <c r="B25" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
     </row>
@@ -4042,14 +4788,14 @@
       <c r="B26" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
     </row>
@@ -4060,14 +4806,14 @@
       <c r="B27" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="59"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="58"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
     </row>
@@ -4078,14 +4824,14 @@
       <c r="B28" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
     </row>
@@ -4096,32 +4842,32 @@
       <c r="B29" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
       <c r="K29" s="35"/>
       <c r="L29" s="35"/>
     </row>
-    <row r="30" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
       <c r="K30" s="35"/>
       <c r="L30" s="35"/>
     </row>
@@ -4132,14 +4878,14 @@
       <c r="B31" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
       <c r="K31" s="35"/>
       <c r="L31" s="35"/>
     </row>
@@ -4150,14 +4896,14 @@
       <c r="B32" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
       <c r="K32" s="35"/>
       <c r="L32" s="35"/>
     </row>
@@ -4168,32 +4914,32 @@
       <c r="B33" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
       <c r="K33" s="35"/>
       <c r="L33" s="35"/>
     </row>
-    <row r="34" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
       <c r="K34" s="35"/>
       <c r="L34" s="35"/>
     </row>
@@ -4204,14 +4950,14 @@
       <c r="B35" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
       <c r="K35" s="35"/>
       <c r="L35" s="35"/>
     </row>
@@ -4222,14 +4968,14 @@
       <c r="B36" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
       <c r="K36" s="35"/>
       <c r="L36" s="35"/>
     </row>
@@ -4240,32 +4986,32 @@
       <c r="B37" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
       <c r="K37" s="35"/>
       <c r="L37" s="35"/>
     </row>
-    <row r="38" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
       <c r="K38" s="35"/>
       <c r="L38" s="35"/>
     </row>
@@ -4276,14 +5022,14 @@
       <c r="B39" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
       <c r="K39" s="35"/>
       <c r="L39" s="35"/>
     </row>
@@ -4294,14 +5040,14 @@
       <c r="B40" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
     </row>
@@ -4312,32 +5058,32 @@
       <c r="B41" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
     </row>
-    <row r="42" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
     </row>
@@ -4348,14 +5094,14 @@
       <c r="B43" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
     </row>
@@ -4366,124 +5112,124 @@
       <c r="B44" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="59"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="59"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="58"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="59"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="58"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="59"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="58"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="59"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="58"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="42"/>
@@ -4581,7 +5327,7 @@
       <c r="I61" s="42"/>
       <c r="J61" s="35"/>
     </row>
-    <row r="62" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="54" t="s">
         <v>91</v>
       </c>
@@ -4620,14 +5366,14 @@
       <c r="B63" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="57"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="57"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
     </row>
     <row r="64" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
@@ -4636,14 +5382,14 @@
       <c r="B64" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
     </row>
     <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
@@ -4652,14 +5398,14 @@
       <c r="B65" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="59"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="58"/>
     </row>
     <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
@@ -4668,14 +5414,14 @@
       <c r="B66" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C66" s="57"/>
-      <c r="D66" s="57"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="57"/>
-      <c r="J66" s="57"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
     </row>
     <row r="67" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
@@ -4684,30 +5430,30 @@
       <c r="B67" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
-      <c r="J67" s="57"/>
-    </row>
-    <row r="68" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+    </row>
+    <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B68" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="57"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
     </row>
     <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
@@ -4716,14 +5462,14 @@
       <c r="B69" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="57"/>
-      <c r="J69" s="57"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
     </row>
     <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
@@ -4732,14 +5478,14 @@
       <c r="B70" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
     </row>
     <row r="71" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
@@ -4748,30 +5494,30 @@
       <c r="B71" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
-      <c r="I71" s="57"/>
-      <c r="J71" s="57"/>
-    </row>
-    <row r="72" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="42"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="42"/>
+    </row>
+    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B72" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="42"/>
     </row>
     <row r="73" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
@@ -4780,14 +5526,14 @@
       <c r="B73" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="57"/>
-      <c r="J73" s="57"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="42"/>
     </row>
     <row r="74" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
@@ -4796,14 +5542,14 @@
       <c r="B74" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="42"/>
     </row>
     <row r="75" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="56" t="n">
@@ -4812,30 +5558,30 @@
       <c r="B75" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C75" s="57"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
-    </row>
-    <row r="76" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="42"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="42"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="42"/>
+    </row>
+    <row r="76" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B76" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="57"/>
-      <c r="D76" s="57"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="57"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+      <c r="I76" s="42"/>
+      <c r="J76" s="42"/>
     </row>
     <row r="77" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="56" t="n">
@@ -4844,14 +5590,14 @@
       <c r="B77" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="57"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="57"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="42"/>
+      <c r="I77" s="42"/>
+      <c r="J77" s="42"/>
     </row>
     <row r="78" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="56" t="n">
@@ -4860,14 +5606,14 @@
       <c r="B78" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C78" s="57"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="57"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="42"/>
+      <c r="I78" s="42"/>
+      <c r="J78" s="42"/>
     </row>
     <row r="79" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="56" t="n">
@@ -4876,30 +5622,30 @@
       <c r="B79" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C79" s="57"/>
-      <c r="D79" s="57"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="57"/>
-    </row>
-    <row r="80" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="42"/>
+      <c r="J79" s="42"/>
+    </row>
+    <row r="80" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B80" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="57"/>
-      <c r="D80" s="57"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57"/>
-      <c r="I80" s="57"/>
-      <c r="J80" s="57"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="42"/>
     </row>
     <row r="81" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="56" t="n">
@@ -4908,14 +5654,14 @@
       <c r="B81" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="42"/>
     </row>
     <row r="82" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="56" t="n">
@@ -4924,14 +5670,14 @@
       <c r="B82" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
-      <c r="I82" s="57"/>
-      <c r="J82" s="57"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="42"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4960,7 +5706,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="71.46"/>
   </cols>
   <sheetData>
-    <row r="1" s="61" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="60" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4979,8 +5725,8 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -4999,8 +5745,8 @@
         <v>123</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" customFormat="false" ht="135.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
@@ -5019,8 +5765,8 @@
         <v>125</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12"/>
@@ -5029,8 +5775,8 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
@@ -5047,8 +5793,8 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
     </row>
     <row r="6" customFormat="false" ht="23.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17"/>
@@ -5057,8 +5803,8 @@
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
     </row>
     <row r="7" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -5075,8 +5821,8 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
     </row>
     <row r="8" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17"/>
@@ -5085,8 +5831,8 @@
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="20"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
     </row>
     <row r="9" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
@@ -5103,8 +5849,8 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
     </row>
     <row r="10" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17"/>
@@ -5113,8 +5859,8 @@
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
@@ -5133,8 +5879,8 @@
         <v>131</v>
       </c>
       <c r="F11" s="24"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25"/>
@@ -5143,8 +5889,8 @@
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="118" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
@@ -5161,8 +5907,8 @@
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="32"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33"/>
@@ -5171,8 +5917,8 @@
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="111.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
@@ -5189,8 +5935,8 @@
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="32"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
     </row>
     <row r="16" s="12" customFormat="true" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33"/>
@@ -5199,8 +5945,8 @@
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
     </row>
     <row r="17" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
@@ -5217,12 +5963,12 @@
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
     </row>
     <row r="19" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
@@ -5241,12 +5987,12 @@
         <v>137</v>
       </c>
       <c r="F19" s="32"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
     </row>
     <row r="21" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
@@ -5305,8 +6051,8 @@
       <c r="F25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
@@ -5325,12 +6071,12 @@
         <v>143</v>
       </c>
       <c r="F27" s="32"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
@@ -5389,8 +6135,8 @@
       <c r="F33" s="32"/>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
     </row>
     <row r="35" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
@@ -5409,12 +6155,12 @@
         <v>149</v>
       </c>
       <c r="F35" s="32"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
     </row>
     <row r="37" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
@@ -5431,13 +6177,13 @@
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="32"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
     </row>
     <row r="39" customFormat="false" ht="88.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
@@ -5454,13 +6200,13 @@
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="32"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="33"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
     </row>
     <row r="41" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
@@ -5477,64 +6223,64 @@
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="32"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="62"/>
-      <c r="H44" s="62"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="61"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="62"/>
-      <c r="H45" s="62"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="62"/>
-      <c r="H46" s="62"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="62"/>
-      <c r="H48" s="62"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="62"/>
-      <c r="H50" s="62"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G51" s="62"/>
-      <c r="H51" s="62"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G52" s="62"/>
-      <c r="H52" s="62"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G53" s="62"/>
-      <c r="H53" s="62"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G54" s="62"/>
-      <c r="H54" s="62"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="61"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G55" s="62"/>
-      <c r="H55" s="62"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5569,49 +6315,49 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="35" width="15.57"/>
   </cols>
   <sheetData>
-    <row r="1" s="70" customFormat="true" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="64" t="s">
+    <row r="1" s="69" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="XFC1" s="0"/>
+      <c r="J1" s="68"/>
+      <c r="XFC1" s="1"/>
       <c r="XFD1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="71" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="72" t="n">
+      <c r="B2" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="72" t="n">
+      <c r="C2" s="71" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="73" t="n">
+      <c r="D2" s="72" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="42" t="n">
@@ -5623,26 +6369,26 @@
       <c r="G2" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H2" s="57" t="n">
+      <c r="H2" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" s="74" t="n">
+      <c r="I2" s="44" t="n">
         <v>10000</v>
       </c>
       <c r="K2" s="1"/>
-      <c r="L2" s="0"/>
-    </row>
-    <row r="3" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="71" t="s">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="72" t="n">
+      <c r="B3" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="72" t="n">
+      <c r="C3" s="71" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="73" t="n">
+      <c r="D3" s="72" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="42" t="n">
@@ -5654,26 +6400,26 @@
       <c r="G3" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H3" s="57" t="n">
+      <c r="H3" s="42" t="n">
         <v>9640</v>
       </c>
-      <c r="I3" s="74" t="n">
+      <c r="I3" s="44" t="n">
         <v>9968</v>
       </c>
       <c r="K3" s="1"/>
-      <c r="L3" s="0"/>
-    </row>
-    <row r="4" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="s">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="72" t="n">
+      <c r="B4" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="72" t="n">
+      <c r="C4" s="71" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="73" t="n">
+      <c r="D4" s="72" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="42" t="n">
@@ -5685,26 +6431,26 @@
       <c r="G4" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H4" s="57" t="n">
+      <c r="H4" s="42" t="n">
         <v>9729</v>
       </c>
-      <c r="I4" s="74" t="n">
+      <c r="I4" s="44" t="n">
         <v>9995</v>
       </c>
       <c r="K4" s="1"/>
-      <c r="L4" s="0"/>
-    </row>
-    <row r="5" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="72" t="n">
+      <c r="B5" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="72" t="n">
+      <c r="C5" s="71" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="73" t="n">
+      <c r="D5" s="72" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="42" t="n">
@@ -5716,26 +6462,26 @@
       <c r="G5" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H5" s="57" t="n">
+      <c r="H5" s="42" t="n">
         <v>9735</v>
       </c>
-      <c r="I5" s="74" t="n">
+      <c r="I5" s="44" t="n">
         <v>9960</v>
       </c>
       <c r="K5" s="1"/>
-      <c r="L5" s="0"/>
-    </row>
-    <row r="6" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="72" t="n">
+      <c r="B6" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="72" t="n">
+      <c r="C6" s="71" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="73" t="n">
+      <c r="D6" s="72" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -5747,26 +6493,26 @@
       <c r="G6" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="57" t="n">
+      <c r="H6" s="42" t="n">
         <v>9903</v>
       </c>
-      <c r="I6" s="74" t="n">
+      <c r="I6" s="44" t="n">
         <v>9959</v>
       </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="0"/>
-    </row>
-    <row r="7" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="72" t="n">
+      <c r="B7" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="72" t="n">
+      <c r="C7" s="71" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="73" t="n">
+      <c r="D7" s="72" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -5778,26 +6524,26 @@
       <c r="G7" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H7" s="57" t="n">
+      <c r="H7" s="42" t="n">
         <v>9914</v>
       </c>
-      <c r="I7" s="74" t="n">
+      <c r="I7" s="44" t="n">
         <v>9923</v>
       </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="72" t="n">
+      <c r="B8" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="72" t="n">
+      <c r="C8" s="71" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="73" t="n">
+      <c r="D8" s="72" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="42" t="n">
@@ -5809,26 +6555,26 @@
       <c r="G8" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="57" t="n">
+      <c r="H8" s="42" t="n">
         <v>9672</v>
       </c>
-      <c r="I8" s="74" t="n">
+      <c r="I8" s="44" t="n">
         <v>9806</v>
       </c>
       <c r="K8" s="1"/>
-      <c r="L8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="72" t="n">
+      <c r="B9" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="72" t="n">
+      <c r="C9" s="71" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="73" t="n">
+      <c r="D9" s="72" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="42" t="n">
@@ -5840,26 +6586,26 @@
       <c r="G9" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="57" t="n">
+      <c r="H9" s="42" t="n">
         <v>9809</v>
       </c>
-      <c r="I9" s="74" t="n">
+      <c r="I9" s="44" t="n">
         <v>9863</v>
       </c>
       <c r="K9" s="1"/>
-      <c r="L9" s="0"/>
-    </row>
-    <row r="10" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="72" t="n">
+      <c r="B10" s="71" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="72" t="n">
+      <c r="C10" s="71" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="73" t="n">
+      <c r="D10" s="72" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="42" t="n">
@@ -5871,26 +6617,26 @@
       <c r="G10" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="57" t="n">
+      <c r="H10" s="42" t="n">
         <v>9640</v>
       </c>
-      <c r="I10" s="74" t="n">
+      <c r="I10" s="44" t="n">
         <v>9665</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="0"/>
-    </row>
-    <row r="11" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="72" t="n">
+      <c r="B11" s="71" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="72" t="n">
+      <c r="C11" s="71" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="73" t="n">
+      <c r="D11" s="72" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="42" t="n">
@@ -5902,26 +6648,26 @@
       <c r="G11" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H11" s="57" t="n">
+      <c r="H11" s="42" t="n">
         <v>9838</v>
       </c>
-      <c r="I11" s="74" t="n">
+      <c r="I11" s="44" t="n">
         <v>9977</v>
       </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="72" t="n">
+      <c r="B12" s="71" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="72" t="n">
+      <c r="C12" s="71" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="73" t="n">
+      <c r="D12" s="72" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="42" t="n">
@@ -5933,26 +6679,26 @@
       <c r="G12" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="57" t="n">
+      <c r="H12" s="42" t="n">
         <v>5828</v>
       </c>
-      <c r="I12" s="74" t="n">
+      <c r="I12" s="44" t="n">
         <v>5844</v>
       </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="72" t="n">
+      <c r="B13" s="71" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="72" t="n">
+      <c r="C13" s="71" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="73" t="n">
+      <c r="D13" s="72" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="42" t="n">
@@ -5964,26 +6710,26 @@
       <c r="G13" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H13" s="57" t="n">
+      <c r="H13" s="42" t="n">
         <v>6010</v>
       </c>
-      <c r="I13" s="74" t="n">
+      <c r="I13" s="44" t="n">
         <v>6017</v>
       </c>
       <c r="K13" s="1"/>
-      <c r="L13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="70" t="s">
         <v>166</v>
       </c>
-      <c r="B14" s="72" t="n">
+      <c r="B14" s="71" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="72" t="n">
+      <c r="C14" s="71" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="73" t="n">
+      <c r="D14" s="72" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="42" t="n">
@@ -5995,26 +6741,26 @@
       <c r="G14" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H14" s="57" t="n">
+      <c r="H14" s="42" t="n">
         <v>9908</v>
       </c>
-      <c r="I14" s="74" t="n">
+      <c r="I14" s="44" t="n">
         <v>9935</v>
       </c>
       <c r="K14" s="1"/>
-      <c r="L14" s="0"/>
+      <c r="L14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="72" t="n">
+      <c r="B15" s="71" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="72" t="n">
+      <c r="C15" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="73" t="n">
+      <c r="D15" s="72" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="42" t="n">
@@ -6026,26 +6772,26 @@
       <c r="G15" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H15" s="57" t="n">
+      <c r="H15" s="42" t="n">
         <v>9719</v>
       </c>
-      <c r="I15" s="74" t="n">
+      <c r="I15" s="44" t="n">
         <v>9719</v>
       </c>
       <c r="K15" s="1"/>
-      <c r="L15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="75" t="s">
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="76" t="n">
+      <c r="B16" s="74" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="76" t="n">
+      <c r="C16" s="74" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="76" t="n">
+      <c r="D16" s="74" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="49" t="n">
@@ -6057,16 +6803,16 @@
       <c r="G16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="H16" s="77" t="n">
+      <c r="H16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="I16" s="78" t="n">
+      <c r="I16" s="52" t="n">
         <v>10000</v>
       </c>
       <c r="K16" s="1"/>
-      <c r="L16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="42" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>2830743</v>
@@ -6096,22 +6842,22 @@
         <v>140631</v>
       </c>
       <c r="K17" s="1"/>
-      <c r="L17" s="0"/>
+      <c r="L17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="79"/>
+      <c r="E18" s="75"/>
       <c r="I18" s="35"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="0"/>
+      <c r="L18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="79"/>
+      <c r="E19" s="75"/>
       <c r="I19" s="35"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="0"/>
+      <c r="L19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="76" t="s">
         <v>90</v>
       </c>
       <c r="C20" s="42" t="n">
@@ -6131,7 +6877,7 @@
       </c>
       <c r="I20" s="35"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="0"/>
+      <c r="L20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L21" s="1"/>
@@ -6179,742 +6925,742 @@
       <c r="J26" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="XFC26" s="0"/>
-      <c r="XFD26" s="0"/>
-    </row>
-    <row r="27" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="XFC26" s="1"/>
+      <c r="XFD26" s="1"/>
+    </row>
+    <row r="27" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="G27" s="57" t="s">
+      <c r="G27" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="I27" s="57" t="s">
+      <c r="I27" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="J27" s="57" t="s">
+      <c r="J27" s="42" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="28" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B28" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="G28" s="57" t="s">
+      <c r="G28" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="H28" s="57" t="s">
+      <c r="H28" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="I28" s="57" t="s">
+      <c r="I28" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="J28" s="57" t="s">
+      <c r="J28" s="42" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="29" s="35" customFormat="true" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="35" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
         <v>3</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="59"/>
-    </row>
-    <row r="30" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="58"/>
+    </row>
+    <row r="30" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="57" t="s">
+      <c r="G30" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="H30" s="57" t="s">
+      <c r="H30" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="I30" s="57" t="s">
+      <c r="I30" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="J30" s="57" t="s">
+      <c r="J30" s="42" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="31" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B31" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="E31" s="57" t="s">
+      <c r="E31" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="G31" s="57" t="s">
+      <c r="G31" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="H31" s="57" t="s">
+      <c r="H31" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="I31" s="57" t="s">
+      <c r="I31" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="J31" s="57" t="s">
+      <c r="J31" s="42" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="32" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B32" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="G32" s="57" t="s">
+      <c r="G32" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="H32" s="57" t="s">
+      <c r="H32" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="I32" s="57" t="s">
+      <c r="I32" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="J32" s="57" t="s">
+      <c r="J32" s="42" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="33" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
         <v>7</v>
       </c>
       <c r="B33" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="G33" s="57" t="s">
+      <c r="G33" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="I33" s="57" t="s">
+      <c r="I33" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="J33" s="57" t="s">
+      <c r="J33" s="42" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="34" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="E34" s="57" t="s">
+      <c r="E34" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="57" t="s">
+      <c r="G34" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="H34" s="57" t="s">
+      <c r="H34" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="I34" s="57" t="s">
+      <c r="I34" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="J34" s="57" t="s">
+      <c r="J34" s="42" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="35" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="G35" s="57" t="s">
+      <c r="G35" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="H35" s="57" t="s">
+      <c r="H35" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="I35" s="57" t="s">
+      <c r="I35" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="J35" s="57" t="s">
+      <c r="J35" s="42" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="36" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B36" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="F36" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="G36" s="57" t="s">
+      <c r="G36" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="H36" s="57" t="s">
+      <c r="H36" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="I36" s="57" t="s">
+      <c r="I36" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="J36" s="57" t="s">
+      <c r="J36" s="42" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="37" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
         <v>11</v>
       </c>
       <c r="B37" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="42" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="38" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="E38" s="57" t="s">
+      <c r="E38" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="F38" s="57" t="s">
+      <c r="F38" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="G38" s="57" t="s">
+      <c r="G38" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="H38" s="57" t="s">
+      <c r="H38" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="I38" s="57" t="s">
+      <c r="I38" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="57" t="s">
+      <c r="J38" s="42" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="39" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="57" t="s">
+      <c r="C39" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="D39" s="57" t="s">
+      <c r="D39" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="F39" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="G39" s="57" t="s">
+      <c r="G39" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="H39" s="57" t="s">
+      <c r="H39" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="I39" s="57" t="s">
+      <c r="I39" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="J39" s="57" t="s">
+      <c r="J39" s="42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="40" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B40" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="57" t="s">
+      <c r="C40" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="D40" s="57" t="s">
+      <c r="D40" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="E40" s="57" t="s">
+      <c r="E40" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="F40" s="57" t="s">
+      <c r="F40" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="G40" s="57" t="s">
+      <c r="G40" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="H40" s="57" t="s">
+      <c r="H40" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="I40" s="57" t="s">
+      <c r="I40" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="J40" s="57" t="s">
+      <c r="J40" s="42" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="41" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
         <v>15</v>
       </c>
       <c r="B41" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C41" s="57" t="s">
+      <c r="C41" s="42" t="s">
         <v>244</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="E41" s="57" t="s">
+      <c r="E41" s="42" t="s">
         <v>244</v>
       </c>
-      <c r="F41" s="57" t="s">
+      <c r="F41" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="42" t="s">
         <v>247</v>
       </c>
-      <c r="H41" s="57" t="s">
+      <c r="H41" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="I41" s="57" t="s">
+      <c r="I41" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="J41" s="57" t="s">
+      <c r="J41" s="42" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="42" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="57" t="s">
+      <c r="C42" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="D42" s="57" t="s">
+      <c r="D42" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="E42" s="57" t="s">
+      <c r="E42" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="F42" s="57" t="s">
+      <c r="F42" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="G42" s="57" t="s">
+      <c r="G42" s="42" t="s">
         <v>254</v>
       </c>
-      <c r="H42" s="57" t="s">
+      <c r="H42" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="I42" s="57" t="s">
+      <c r="I42" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="J42" s="57" t="s">
+      <c r="J42" s="42" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="43" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B43" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="57" t="s">
+      <c r="C43" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="D43" s="57" t="s">
+      <c r="D43" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="E43" s="57" t="s">
+      <c r="E43" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="F43" s="57" t="s">
+      <c r="F43" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="G43" s="57" t="s">
+      <c r="G43" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="H43" s="57" t="s">
+      <c r="H43" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="I43" s="57" t="s">
+      <c r="I43" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="J43" s="57" t="s">
+      <c r="J43" s="42" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="44" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B44" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C44" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="D44" s="57" t="s">
+      <c r="D44" s="42" t="s">
         <v>266</v>
       </c>
-      <c r="E44" s="57" t="s">
+      <c r="E44" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="F44" s="57" t="s">
+      <c r="F44" s="42" t="s">
         <v>267</v>
       </c>
-      <c r="G44" s="57" t="s">
+      <c r="G44" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="H44" s="57" t="s">
+      <c r="H44" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="I44" s="57" t="s">
+      <c r="I44" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="J44" s="57" t="s">
+      <c r="J44" s="42" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="45" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="56" t="n">
         <v>19</v>
       </c>
       <c r="B45" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C45" s="57" t="s">
+      <c r="C45" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="D45" s="57" t="s">
+      <c r="D45" s="42" t="s">
         <v>273</v>
       </c>
-      <c r="E45" s="57" t="s">
+      <c r="E45" s="42" t="s">
         <v>274</v>
       </c>
-      <c r="F45" s="57" t="s">
+      <c r="F45" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="G45" s="57" t="s">
+      <c r="G45" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="H45" s="57" t="s">
+      <c r="H45" s="42" t="s">
         <v>277</v>
       </c>
-      <c r="I45" s="57" t="s">
+      <c r="I45" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="J45" s="57" t="s">
+      <c r="J45" s="42" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="46" s="35" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B46" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C46" s="57" t="s">
+      <c r="C46" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="D46" s="57" t="s">
+      <c r="D46" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="E46" s="57" t="s">
+      <c r="E46" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="F46" s="57" t="s">
+      <c r="F46" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="G46" s="57" t="s">
+      <c r="G46" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="H46" s="57" t="s">
+      <c r="H46" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="I46" s="57" t="s">
+      <c r="I46" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="J46" s="57" t="s">
+      <c r="J46" s="42" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="47" s="35" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="59"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="59"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="58"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="59"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="58"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="59"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="58"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="59"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="58"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="58"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
-      <c r="I54" s="58"/>
-      <c r="J54" s="59"/>
+      <c r="A54" s="57"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="58"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="58"/>
-      <c r="I55" s="58"/>
-      <c r="J55" s="59"/>
-    </row>
-    <row r="64" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="57"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="58"/>
+    </row>
+    <row r="64" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="54" t="s">
         <v>91</v>
       </c>
@@ -6953,28 +7699,28 @@
       <c r="B65" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C65" s="57" t="s">
+      <c r="C65" s="42" t="s">
         <v>287</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="42" t="s">
         <v>287</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="42" t="s">
         <v>289</v>
       </c>
-      <c r="G65" s="57" t="s">
+      <c r="G65" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="42" t="s">
         <v>292</v>
       </c>
-      <c r="J65" s="57" t="s">
+      <c r="J65" s="42" t="s">
         <v>293</v>
       </c>
     </row>
@@ -6985,28 +7731,28 @@
       <c r="B66" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="D66" s="57" t="s">
+      <c r="D66" s="42" t="s">
         <v>295</v>
       </c>
-      <c r="E66" s="57" t="s">
+      <c r="E66" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="F66" s="57" t="s">
+      <c r="F66" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="G66" s="57" t="s">
+      <c r="G66" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="H66" s="57" t="s">
+      <c r="H66" s="42" t="s">
         <v>298</v>
       </c>
-      <c r="I66" s="57" t="s">
+      <c r="I66" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="57" t="s">
+      <c r="J66" s="42" t="s">
         <v>300</v>
       </c>
     </row>
@@ -7017,14 +7763,14 @@
       <c r="B67" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
-      <c r="J67" s="59"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="58"/>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
@@ -7033,28 +7779,28 @@
       <c r="B68" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="D68" s="57" t="s">
+      <c r="D68" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="E68" s="57" t="s">
+      <c r="E68" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="F68" s="57" t="s">
+      <c r="F68" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="G68" s="57" t="s">
+      <c r="G68" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="H68" s="57" t="s">
+      <c r="H68" s="42" t="s">
         <v>305</v>
       </c>
-      <c r="I68" s="57" t="s">
+      <c r="I68" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="J68" s="57" t="s">
+      <c r="J68" s="42" t="s">
         <v>307</v>
       </c>
     </row>
@@ -7065,28 +7811,28 @@
       <c r="B69" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="42" t="s">
         <v>308</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="42" t="s">
         <v>308</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="42" t="s">
         <v>310</v>
       </c>
-      <c r="G69" s="57" t="s">
+      <c r="G69" s="42" t="s">
         <v>311</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="I69" s="57" t="s">
+      <c r="I69" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="J69" s="57" t="s">
+      <c r="J69" s="42" t="s">
         <v>314</v>
       </c>
     </row>
@@ -7097,28 +7843,28 @@
       <c r="B70" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="D70" s="57" t="s">
+      <c r="D70" s="42" t="s">
         <v>316</v>
       </c>
-      <c r="E70" s="57" t="s">
+      <c r="E70" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="F70" s="57" t="s">
+      <c r="F70" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="G70" s="57" t="s">
+      <c r="G70" s="42" t="s">
         <v>318</v>
       </c>
-      <c r="H70" s="57" t="s">
+      <c r="H70" s="42" t="s">
         <v>319</v>
       </c>
-      <c r="I70" s="57" t="s">
+      <c r="I70" s="42" t="s">
         <v>320</v>
       </c>
-      <c r="J70" s="57" t="s">
+      <c r="J70" s="42" t="s">
         <v>321</v>
       </c>
     </row>
@@ -7129,28 +7875,28 @@
       <c r="B71" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C71" s="57" t="s">
+      <c r="C71" s="42" t="s">
         <v>322</v>
       </c>
-      <c r="D71" s="57" t="s">
+      <c r="D71" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="E71" s="57" t="s">
+      <c r="E71" s="42" t="s">
         <v>322</v>
       </c>
-      <c r="F71" s="57" t="s">
+      <c r="F71" s="42" t="s">
         <v>324</v>
       </c>
-      <c r="G71" s="57" t="s">
+      <c r="G71" s="42" t="s">
         <v>325</v>
       </c>
-      <c r="H71" s="57" t="s">
+      <c r="H71" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="I71" s="57" t="s">
+      <c r="I71" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="J71" s="57" t="s">
+      <c r="J71" s="42" t="s">
         <v>328</v>
       </c>
     </row>
@@ -7161,28 +7907,28 @@
       <c r="B72" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C72" s="57" t="s">
+      <c r="C72" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="D72" s="57" t="s">
+      <c r="D72" s="42" t="s">
         <v>330</v>
       </c>
-      <c r="E72" s="57" t="s">
+      <c r="E72" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="F72" s="57" t="s">
+      <c r="F72" s="42" t="s">
         <v>331</v>
       </c>
-      <c r="G72" s="57" t="s">
+      <c r="G72" s="42" t="s">
         <v>332</v>
       </c>
-      <c r="H72" s="57" t="s">
+      <c r="H72" s="42" t="s">
         <v>333</v>
       </c>
-      <c r="I72" s="57" t="s">
+      <c r="I72" s="42" t="s">
         <v>334</v>
       </c>
-      <c r="J72" s="57" t="s">
+      <c r="J72" s="42" t="s">
         <v>335</v>
       </c>
     </row>
@@ -7193,28 +7939,28 @@
       <c r="B73" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="57" t="s">
+      <c r="C73" s="42" t="s">
         <v>336</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="42" t="s">
         <v>337</v>
       </c>
-      <c r="E73" s="57" t="s">
+      <c r="E73" s="42" t="s">
         <v>336</v>
       </c>
-      <c r="F73" s="57" t="s">
+      <c r="F73" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="G73" s="57" t="s">
+      <c r="G73" s="42" t="s">
         <v>339</v>
       </c>
-      <c r="H73" s="57" t="s">
+      <c r="H73" s="42" t="s">
         <v>340</v>
       </c>
-      <c r="I73" s="57" t="s">
+      <c r="I73" s="42" t="s">
         <v>341</v>
       </c>
-      <c r="J73" s="57" t="s">
+      <c r="J73" s="42" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7225,28 +7971,28 @@
       <c r="B74" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C74" s="57" t="s">
+      <c r="C74" s="42" t="s">
         <v>343</v>
       </c>
-      <c r="D74" s="57" t="s">
+      <c r="D74" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="E74" s="57" t="s">
+      <c r="E74" s="42" t="s">
         <v>343</v>
       </c>
-      <c r="F74" s="57" t="s">
+      <c r="F74" s="42" t="s">
         <v>345</v>
       </c>
-      <c r="G74" s="57" t="s">
+      <c r="G74" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="H74" s="57" t="s">
+      <c r="H74" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="I74" s="57" t="s">
+      <c r="I74" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="J74" s="57" t="s">
+      <c r="J74" s="42" t="s">
         <v>349</v>
       </c>
     </row>
@@ -7257,28 +8003,28 @@
       <c r="B75" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="57" t="s">
+      <c r="C75" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="D75" s="57" t="s">
+      <c r="D75" s="42" t="s">
         <v>351</v>
       </c>
-      <c r="E75" s="57" t="s">
+      <c r="E75" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="F75" s="57" t="s">
+      <c r="F75" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="G75" s="57" t="s">
+      <c r="G75" s="42" t="s">
         <v>353</v>
       </c>
-      <c r="H75" s="57" t="s">
+      <c r="H75" s="42" t="s">
         <v>354</v>
       </c>
-      <c r="I75" s="57" t="s">
+      <c r="I75" s="42" t="s">
         <v>355</v>
       </c>
-      <c r="J75" s="57" t="s">
+      <c r="J75" s="42" t="s">
         <v>356</v>
       </c>
     </row>
@@ -7289,28 +8035,28 @@
       <c r="B76" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C76" s="57" t="s">
+      <c r="C76" s="42" t="s">
         <v>357</v>
       </c>
-      <c r="D76" s="57" t="s">
+      <c r="D76" s="42" t="s">
         <v>358</v>
       </c>
-      <c r="E76" s="57" t="s">
+      <c r="E76" s="42" t="s">
         <v>357</v>
       </c>
-      <c r="F76" s="57" t="s">
+      <c r="F76" s="42" t="s">
         <v>359</v>
       </c>
-      <c r="G76" s="57" t="s">
+      <c r="G76" s="42" t="s">
         <v>360</v>
       </c>
-      <c r="H76" s="57" t="s">
+      <c r="H76" s="42" t="s">
         <v>361</v>
       </c>
-      <c r="I76" s="57" t="s">
+      <c r="I76" s="42" t="s">
         <v>362</v>
       </c>
-      <c r="J76" s="57" t="s">
+      <c r="J76" s="42" t="s">
         <v>363</v>
       </c>
     </row>
@@ -7321,28 +8067,28 @@
       <c r="B77" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C77" s="57" t="s">
+      <c r="C77" s="42" t="s">
         <v>364</v>
       </c>
-      <c r="D77" s="57" t="s">
+      <c r="D77" s="42" t="s">
         <v>365</v>
       </c>
-      <c r="E77" s="57" t="s">
+      <c r="E77" s="42" t="s">
         <v>364</v>
       </c>
-      <c r="F77" s="57" t="s">
+      <c r="F77" s="42" t="s">
         <v>366</v>
       </c>
-      <c r="G77" s="57" t="s">
+      <c r="G77" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="H77" s="57" t="s">
+      <c r="H77" s="42" t="s">
         <v>368</v>
       </c>
-      <c r="I77" s="57" t="s">
+      <c r="I77" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="J77" s="57" t="s">
+      <c r="J77" s="42" t="s">
         <v>370</v>
       </c>
     </row>
@@ -7353,124 +8099,124 @@
       <c r="B78" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="57" t="s">
+      <c r="C78" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="D78" s="57" t="s">
+      <c r="D78" s="42" t="s">
         <v>372</v>
       </c>
-      <c r="E78" s="57" t="s">
+      <c r="E78" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="F78" s="57" t="s">
+      <c r="F78" s="42" t="s">
         <v>373</v>
       </c>
-      <c r="G78" s="57" t="s">
+      <c r="G78" s="42" t="s">
         <v>374</v>
       </c>
-      <c r="H78" s="57" t="s">
+      <c r="H78" s="42" t="s">
         <v>375</v>
       </c>
-      <c r="I78" s="57" t="s">
+      <c r="I78" s="42" t="s">
         <v>376</v>
       </c>
-      <c r="J78" s="57" t="s">
+      <c r="J78" s="42" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="56" t="n">
         <v>15</v>
       </c>
       <c r="B79" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C79" s="57" t="s">
+      <c r="C79" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="D79" s="57" t="s">
+      <c r="D79" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="E79" s="57" t="s">
+      <c r="E79" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="F79" s="57" t="s">
+      <c r="F79" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="G79" s="57" t="s">
+      <c r="G79" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="H79" s="57" t="s">
+      <c r="H79" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="I79" s="57" t="s">
+      <c r="I79" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="J79" s="57" t="s">
+      <c r="J79" s="42" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B80" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C80" s="57" t="s">
+      <c r="C80" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="D80" s="57" t="s">
+      <c r="D80" s="42" t="s">
         <v>386</v>
       </c>
-      <c r="E80" s="57" t="s">
+      <c r="E80" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="F80" s="57" t="s">
+      <c r="F80" s="42" t="s">
         <v>387</v>
       </c>
-      <c r="G80" s="57" t="s">
+      <c r="G80" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="H80" s="57" t="s">
+      <c r="H80" s="42" t="s">
         <v>389</v>
       </c>
-      <c r="I80" s="57" t="s">
+      <c r="I80" s="42" t="s">
         <v>390</v>
       </c>
-      <c r="J80" s="57" t="s">
+      <c r="J80" s="42" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B81" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C81" s="57" t="s">
+      <c r="C81" s="42" t="s">
         <v>392</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="42" t="s">
         <v>393</v>
       </c>
-      <c r="E81" s="57" t="s">
+      <c r="E81" s="42" t="s">
         <v>392</v>
       </c>
-      <c r="F81" s="57" t="s">
+      <c r="F81" s="42" t="s">
         <v>394</v>
       </c>
-      <c r="G81" s="57" t="s">
+      <c r="G81" s="42" t="s">
         <v>395</v>
       </c>
-      <c r="H81" s="57" t="s">
+      <c r="H81" s="42" t="s">
         <v>396</v>
       </c>
-      <c r="I81" s="57" t="s">
+      <c r="I81" s="42" t="s">
         <v>397</v>
       </c>
-      <c r="J81" s="57" t="s">
+      <c r="J81" s="42" t="s">
         <v>398</v>
       </c>
     </row>
@@ -7481,92 +8227,92 @@
       <c r="B82" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C82" s="57" t="s">
+      <c r="C82" s="42" t="s">
         <v>399</v>
       </c>
-      <c r="D82" s="57" t="s">
+      <c r="D82" s="42" t="s">
         <v>400</v>
       </c>
-      <c r="E82" s="57" t="s">
+      <c r="E82" s="42" t="s">
         <v>399</v>
       </c>
-      <c r="F82" s="57" t="s">
+      <c r="F82" s="42" t="s">
         <v>401</v>
       </c>
-      <c r="G82" s="57" t="s">
+      <c r="G82" s="42" t="s">
         <v>402</v>
       </c>
-      <c r="H82" s="57" t="s">
+      <c r="H82" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="I82" s="57" t="s">
+      <c r="I82" s="42" t="s">
         <v>404</v>
       </c>
-      <c r="J82" s="57" t="s">
+      <c r="J82" s="42" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="56" t="n">
         <v>19</v>
       </c>
       <c r="B83" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="57" t="s">
+      <c r="C83" s="42" t="s">
         <v>406</v>
       </c>
-      <c r="D83" s="57" t="s">
+      <c r="D83" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="E83" s="57" t="s">
+      <c r="E83" s="42" t="s">
         <v>406</v>
       </c>
-      <c r="F83" s="57" t="s">
+      <c r="F83" s="42" t="s">
         <v>408</v>
       </c>
-      <c r="G83" s="57" t="s">
+      <c r="G83" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="H83" s="57" t="s">
+      <c r="H83" s="42" t="s">
         <v>410</v>
       </c>
-      <c r="I83" s="57" t="s">
+      <c r="I83" s="42" t="s">
         <v>411</v>
       </c>
-      <c r="J83" s="57" t="s">
+      <c r="J83" s="42" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B84" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C84" s="57" t="s">
+      <c r="C84" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="D84" s="57" t="s">
+      <c r="D84" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="E84" s="57" t="s">
+      <c r="E84" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="F84" s="57" t="s">
+      <c r="F84" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="G84" s="57" t="s">
+      <c r="G84" s="42" t="s">
         <v>416</v>
       </c>
-      <c r="H84" s="57" t="s">
+      <c r="H84" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="I84" s="57" t="s">
+      <c r="I84" s="42" t="s">
         <v>418</v>
       </c>
-      <c r="J84" s="57" t="s">
+      <c r="J84" s="42" t="s">
         <v>419</v>
       </c>
     </row>
@@ -7589,7 +8335,7 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="81" width="36.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="77" width="36.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="90.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="77.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="65.07"/>
@@ -7598,725 +8344,725 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="83" t="s">
+      <c r="F1" s="79" t="s">
         <v>420</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81" t="s">
         <v>421</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="81" t="s">
         <v>422</v>
       </c>
-      <c r="F2" s="86"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="84"/>
-      <c r="B3" s="85" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="83" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="81" t="s">
         <v>422</v>
       </c>
-      <c r="F3" s="86"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="84"/>
-      <c r="B4" s="85" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81" t="s">
         <v>425</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="83" t="s">
         <v>426</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="D4" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="81" t="s">
         <v>427</v>
       </c>
-      <c r="F4" s="86"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="C5" s="83" t="s">
         <v>424</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="81" t="s">
         <v>427</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="81" t="s">
         <v>422</v>
       </c>
-      <c r="F5" s="86"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="84"/>
-      <c r="B6" s="85" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81" t="s">
         <v>429</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="83" t="s">
         <v>430</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="81" t="s">
         <v>427</v>
       </c>
-      <c r="E6" s="87" t="s">
+      <c r="E6" s="83" t="s">
         <v>431</v>
       </c>
-      <c r="F6" s="86"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="80" t="s">
         <v>432</v>
       </c>
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="84" t="s">
         <v>433</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="C7" s="85" t="s">
         <v>434</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="85" t="s">
         <v>435</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="85" t="s">
         <v>436</v>
       </c>
-      <c r="F7" s="86"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="84" t="s">
         <v>437</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D8" s="89" t="s">
+      <c r="D8" s="85" t="s">
         <v>435</v>
       </c>
-      <c r="E8" s="89" t="s">
+      <c r="E8" s="85" t="s">
         <v>439</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="84" t="s">
         <v>440</v>
       </c>
-      <c r="C9" s="89" t="s">
+      <c r="C9" s="85" t="s">
         <v>434</v>
       </c>
-      <c r="D9" s="89" t="s">
+      <c r="D9" s="85" t="s">
         <v>439</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="85" t="s">
         <v>441</v>
       </c>
-      <c r="F9" s="86"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="87" t="s">
         <v>442</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="88" t="s">
         <v>443</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="88" t="s">
         <v>435</v>
       </c>
-      <c r="E10" s="92" t="s">
+      <c r="E10" s="88" t="s">
         <v>444</v>
       </c>
       <c r="F10" s="24"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="90" t="s">
         <v>445</v>
       </c>
-      <c r="C11" s="95" t="s">
+      <c r="C11" s="91" t="s">
         <v>434</v>
       </c>
-      <c r="D11" s="95" t="s">
+      <c r="D11" s="91" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="95" t="s">
+      <c r="E11" s="91" t="s">
         <v>446</v>
       </c>
-      <c r="F11" s="96"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="91" t="s">
         <v>447</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="91" t="s">
         <v>448</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="91" t="s">
         <v>449</v>
       </c>
-      <c r="E12" s="95"/>
-      <c r="F12" s="97" t="s">
+      <c r="E12" s="91"/>
+      <c r="F12" s="93" t="s">
         <v>450</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="91" t="s">
         <v>451</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="91" t="s">
         <v>452</v>
       </c>
-      <c r="D13" s="95" t="s">
+      <c r="D13" s="91" t="s">
         <v>453</v>
       </c>
-      <c r="E13" s="95"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="101"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
+      <c r="A15" s="97"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="92" t="s">
+      <c r="B16" s="88" t="s">
         <v>454</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="88" t="s">
         <v>438</v>
       </c>
-      <c r="D16" s="92" t="s">
+      <c r="D16" s="88" t="s">
         <v>455</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="88" t="s">
         <v>456</v>
       </c>
-      <c r="F16" s="104"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="91" t="s">
         <v>457</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="91" t="s">
         <v>434</v>
       </c>
-      <c r="D17" s="95" t="s">
+      <c r="D17" s="91" t="s">
         <v>456</v>
       </c>
-      <c r="E17" s="95" t="s">
+      <c r="E17" s="91" t="s">
         <v>458</v>
       </c>
-      <c r="F17" s="97"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="102" t="s">
         <v>459</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="102" t="s">
         <v>448</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D18" s="102" t="s">
         <v>460</v>
       </c>
-      <c r="E18" s="106"/>
-      <c r="F18" s="107" t="s">
+      <c r="E18" s="102"/>
+      <c r="F18" s="103" t="s">
         <v>461</v>
       </c>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="98" t="s">
+      <c r="A19" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="95" t="s">
         <v>462</v>
       </c>
-      <c r="C19" s="99" t="s">
+      <c r="C19" s="95" t="s">
         <v>452</v>
       </c>
-      <c r="D19" s="99" t="s">
+      <c r="D19" s="95" t="s">
         <v>463</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="98"/>
-      <c r="B20" s="99"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="108"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="91" t="s">
+      <c r="B22" s="87" t="s">
         <v>464</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="88" t="s">
         <v>443</v>
       </c>
-      <c r="D22" s="92" t="s">
+      <c r="D22" s="88" t="s">
         <v>435</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="E22" s="88" t="s">
         <v>465</v>
       </c>
       <c r="F22" s="24"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="90" t="s">
         <v>466</v>
       </c>
-      <c r="C23" s="95" t="s">
+      <c r="C23" s="91" t="s">
         <v>434</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="91" t="s">
         <v>465</v>
       </c>
-      <c r="E23" s="95" t="s">
+      <c r="E23" s="91" t="s">
         <v>467</v>
       </c>
-      <c r="F23" s="96"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="106" t="s">
+      <c r="B24" s="102" t="s">
         <v>468</v>
       </c>
-      <c r="C24" s="106" t="s">
+      <c r="C24" s="102" t="s">
         <v>448</v>
       </c>
-      <c r="D24" s="106" t="s">
+      <c r="D24" s="102" t="s">
         <v>469</v>
       </c>
-      <c r="E24" s="106"/>
-      <c r="F24" s="107" t="s">
+      <c r="E24" s="102"/>
+      <c r="F24" s="103" t="s">
         <v>470</v>
       </c>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="98" t="s">
+      <c r="A25" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="99" t="s">
+      <c r="B25" s="95" t="s">
         <v>471</v>
       </c>
-      <c r="C25" s="99" t="s">
+      <c r="C25" s="95" t="s">
         <v>452</v>
       </c>
-      <c r="D25" s="99" t="s">
+      <c r="D25" s="95" t="s">
         <v>472</v>
       </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="98"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="101"/>
-      <c r="B27" s="102"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
+      <c r="A27" s="97"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="92" t="s">
+      <c r="B28" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="C28" s="92" t="s">
+      <c r="C28" s="88" t="s">
         <v>438</v>
       </c>
-      <c r="D28" s="92" t="s">
+      <c r="D28" s="88" t="s">
         <v>474</v>
       </c>
-      <c r="E28" s="92" t="s">
+      <c r="E28" s="88" t="s">
         <v>475</v>
       </c>
-      <c r="F28" s="104"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="93" t="s">
+      <c r="A29" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="91" t="s">
         <v>476</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="91" t="s">
         <v>434</v>
       </c>
-      <c r="D29" s="95" t="s">
+      <c r="D29" s="91" t="s">
         <v>475</v>
       </c>
-      <c r="E29" s="95" t="s">
+      <c r="E29" s="91" t="s">
         <v>477</v>
       </c>
-      <c r="F29" s="97"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="106" t="s">
+      <c r="B30" s="102" t="s">
         <v>478</v>
       </c>
-      <c r="C30" s="106" t="s">
+      <c r="C30" s="102" t="s">
         <v>448</v>
       </c>
-      <c r="D30" s="106" t="s">
+      <c r="D30" s="102" t="s">
         <v>479</v>
       </c>
-      <c r="E30" s="106"/>
-      <c r="F30" s="107" t="s">
+      <c r="E30" s="102"/>
+      <c r="F30" s="103" t="s">
         <v>480</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="98" t="s">
+      <c r="A31" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="99" t="s">
+      <c r="B31" s="95" t="s">
         <v>481</v>
       </c>
-      <c r="C31" s="99" t="s">
+      <c r="C31" s="95" t="s">
         <v>452</v>
       </c>
-      <c r="D31" s="99" t="s">
+      <c r="D31" s="95" t="s">
         <v>482</v>
       </c>
-      <c r="E31" s="99"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="98"/>
-      <c r="B32" s="99"/>
-      <c r="C32" s="99"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
+      <c r="A32" s="94"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="95"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="101"/>
-      <c r="B33" s="111"/>
-      <c r="C33" s="111"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="111"/>
-      <c r="F33" s="112"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="62"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62"/>
-      <c r="K42" s="62"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8339,46 +9085,45 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="35" width="28.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="41.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="30.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="17.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="18.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="35" width="25.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="35" width="33.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="35" width="24.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="26.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="35" width="18.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="20.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="35" width="16.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="35" width="17.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="35" width="16.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="15.85"/>
   </cols>
   <sheetData>
-    <row r="1" s="113" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
+    <row r="1" s="110" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="64" t="s">
         <v>483</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="64" t="s">
         <v>484</v>
       </c>
-      <c r="F1" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="37" t="s">
+      <c r="F1" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="G1" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="H1" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="I1" s="109" t="s">
         <v>58</v>
       </c>
+      <c r="XFC1" s="0"/>
       <c r="XFD1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8391,14 +9136,14 @@
       <c r="C2" s="42" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="46" t="n">
-        <v>1785037</v>
-      </c>
-      <c r="E2" s="42" t="n">
-        <v>1428029</v>
+      <c r="D2" s="111" t="n">
+        <v>1715048</v>
+      </c>
+      <c r="E2" s="111" t="n">
+        <v>1372038</v>
       </c>
       <c r="F2" s="46" t="n">
-        <v>1427700</v>
+        <v>10000</v>
       </c>
       <c r="G2" s="46" t="n">
         <v>10000</v>
@@ -8406,12 +9151,10 @@
       <c r="H2" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="I2" s="46" t="n">
+      <c r="I2" s="44" t="n">
         <v>10000</v>
       </c>
-      <c r="J2" s="44" t="n">
-        <v>10000</v>
-      </c>
+      <c r="J2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
@@ -8423,27 +9166,25 @@
       <c r="C3" s="42" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="46" t="n">
-        <v>346201</v>
+      <c r="D3" s="111" t="n">
+        <v>346143</v>
       </c>
       <c r="E3" s="42" t="n">
         <v>276961</v>
       </c>
       <c r="F3" s="46" t="n">
-        <v>275565</v>
+        <v>10000</v>
       </c>
       <c r="G3" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H3" s="46" t="n">
+      <c r="H3" s="111" t="n">
+        <v>9168</v>
+      </c>
+      <c r="I3" s="44" t="n">
         <v>10000</v>
       </c>
-      <c r="I3" s="42" t="n">
-        <v>9549</v>
-      </c>
-      <c r="J3" s="44" t="n">
-        <v>10000</v>
-      </c>
+      <c r="J3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
@@ -8455,27 +9196,25 @@
       <c r="C4" s="42" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="46" t="n">
+      <c r="D4" s="111" t="n">
         <v>161323</v>
       </c>
       <c r="E4" s="42" t="n">
         <v>129058</v>
       </c>
       <c r="F4" s="46" t="n">
-        <v>129044</v>
+        <v>10000</v>
       </c>
       <c r="G4" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H4" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I4" s="42" t="n">
-        <v>9994</v>
-      </c>
-      <c r="J4" s="44" t="n">
-        <v>9992</v>
-      </c>
+      <c r="H4" s="111" t="n">
+        <v>9973</v>
+      </c>
+      <c r="I4" s="112" t="n">
+        <v>9972</v>
+      </c>
+      <c r="J4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
@@ -8487,27 +9226,25 @@
       <c r="C5" s="42" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="111" t="n">
         <v>95729</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>76583</v>
       </c>
       <c r="F5" s="46" t="n">
-        <v>75502</v>
+        <v>10000</v>
       </c>
       <c r="G5" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H5" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I5" s="42" t="n">
-        <v>9593</v>
-      </c>
-      <c r="J5" s="44" t="n">
-        <v>9989</v>
-      </c>
+      <c r="H5" s="111" t="n">
+        <v>9376</v>
+      </c>
+      <c r="I5" s="112" t="n">
+        <v>9988</v>
+      </c>
+      <c r="J5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
@@ -8519,27 +9256,25 @@
       <c r="C6" s="42" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="111" t="n">
         <v>9531</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>7625</v>
       </c>
       <c r="F6" s="46" t="n">
-        <v>7608</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="42" t="n">
-        <v>9990</v>
-      </c>
-      <c r="J6" s="44" t="n">
-        <v>9999</v>
-      </c>
+      <c r="H6" s="111" t="n">
+        <v>9978</v>
+      </c>
+      <c r="I6" s="112" t="n">
+        <v>9996</v>
+      </c>
+      <c r="J6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
@@ -8551,27 +9286,25 @@
       <c r="C7" s="42" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="111" t="n">
         <v>8364</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>6691</v>
       </c>
       <c r="F7" s="46" t="n">
-        <v>6423</v>
+        <v>10000</v>
       </c>
       <c r="G7" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H7" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I7" s="42" t="n">
-        <v>9781</v>
-      </c>
-      <c r="J7" s="44" t="n">
-        <v>9944</v>
-      </c>
+      <c r="H7" s="111" t="n">
+        <v>9351</v>
+      </c>
+      <c r="I7" s="112" t="n">
+        <v>9625</v>
+      </c>
+      <c r="J7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
@@ -8590,20 +9323,18 @@
         <v>5485</v>
       </c>
       <c r="F8" s="46" t="n">
-        <v>5325</v>
+        <v>10000</v>
       </c>
       <c r="G8" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>9873</v>
-      </c>
-      <c r="J8" s="44" t="n">
-        <v>9880</v>
-      </c>
+      <c r="H8" s="111" t="n">
+        <v>9571</v>
+      </c>
+      <c r="I8" s="112" t="n">
+        <v>9632</v>
+      </c>
+      <c r="J8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
@@ -8622,20 +9353,18 @@
         <v>4759</v>
       </c>
       <c r="F9" s="46" t="n">
-        <v>4732</v>
+        <v>10000</v>
       </c>
       <c r="G9" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>9983</v>
-      </c>
-      <c r="J9" s="44" t="n">
-        <v>9992</v>
-      </c>
+      <c r="H9" s="111" t="n">
+        <v>9947</v>
+      </c>
+      <c r="I9" s="112" t="n">
+        <v>9981</v>
+      </c>
+      <c r="J9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
@@ -8654,20 +9383,18 @@
         <v>4406</v>
       </c>
       <c r="F10" s="46" t="n">
-        <v>4393</v>
+        <v>10000</v>
       </c>
       <c r="G10" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>9995</v>
-      </c>
-      <c r="J10" s="44" t="n">
-        <v>9995</v>
-      </c>
+      <c r="H10" s="111" t="n">
+        <v>9991</v>
+      </c>
+      <c r="I10" s="112" t="n">
+        <v>9993</v>
+      </c>
+      <c r="J10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
@@ -8680,26 +9407,24 @@
         <v>5177</v>
       </c>
       <c r="D11" s="46" t="n">
-        <v>5123</v>
+        <v>5122</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>4098</v>
       </c>
       <c r="F11" s="46" t="n">
-        <v>3980</v>
+        <v>10000</v>
       </c>
       <c r="G11" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H11" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>9868</v>
-      </c>
-      <c r="J11" s="44" t="n">
-        <v>9881</v>
-      </c>
+      <c r="H11" s="111" t="n">
+        <v>9620</v>
+      </c>
+      <c r="I11" s="112" t="n">
+        <v>8581</v>
+      </c>
+      <c r="J11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
@@ -8718,20 +9443,18 @@
         <v>2187</v>
       </c>
       <c r="F12" s="46" t="n">
-        <v>2176</v>
+        <v>10000</v>
       </c>
       <c r="G12" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>9971</v>
-      </c>
-      <c r="J12" s="44" t="n">
-        <v>9971</v>
-      </c>
+      <c r="H12" s="111" t="n">
+        <v>8106</v>
+      </c>
+      <c r="I12" s="112" t="n">
+        <v>8117</v>
+      </c>
+      <c r="J12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
@@ -8750,20 +9473,18 @@
         <v>1086</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>1076</v>
+        <v>10000</v>
       </c>
       <c r="G13" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H13" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>9971</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <v>9971</v>
-      </c>
+      <c r="H13" s="111" t="n">
+        <v>6944</v>
+      </c>
+      <c r="I13" s="112" t="n">
+        <v>6907</v>
+      </c>
+      <c r="J13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
@@ -8782,23 +9503,21 @@
         <v>19</v>
       </c>
       <c r="F14" s="46" t="n">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="G14" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H14" s="46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="42" t="n">
-        <v>9998</v>
-      </c>
-      <c r="J14" s="44" t="n">
-        <v>9998</v>
-      </c>
+      <c r="H14" s="111" t="n">
+        <v>9811</v>
+      </c>
+      <c r="I14" s="112" t="n">
+        <v>9824</v>
+      </c>
+      <c r="J14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="113" t="s">
         <v>168</v>
       </c>
       <c r="B15" s="48" t="n">
@@ -8814,20 +9533,18 @@
         <v>10</v>
       </c>
       <c r="F15" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="H15" s="51" t="n">
+      <c r="G15" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="I15" s="49" t="n">
-        <v>9995</v>
-      </c>
-      <c r="J15" s="52" t="n">
-        <v>9995</v>
-      </c>
+      <c r="H15" s="114" t="n">
+        <v>9974</v>
+      </c>
+      <c r="I15" s="115" t="n">
+        <v>7946</v>
+      </c>
+      <c r="J15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="35" t="n">
@@ -8836,15 +9553,15 @@
       </c>
       <c r="D16" s="35" t="n">
         <f aca="false">SUM(D2:D15)</f>
-        <v>2433747</v>
+        <v>2363699</v>
       </c>
       <c r="E16" s="35" t="n">
         <f aca="false">SUM(E2:E15)</f>
-        <v>1946997</v>
+        <v>1891006</v>
       </c>
       <c r="F16" s="35" t="n">
         <f aca="false">SUM(F2:F15)</f>
-        <v>1943539</v>
+        <v>140000</v>
       </c>
       <c r="G16" s="35" t="n">
         <f aca="false">SUM(G2:G15)</f>
@@ -8852,24 +9569,22 @@
       </c>
       <c r="H16" s="35" t="n">
         <f aca="false">SUM(H2:H15)</f>
-        <v>140000</v>
+        <v>131810</v>
       </c>
       <c r="I16" s="35" t="n">
         <f aca="false">SUM(I2:I15)</f>
-        <v>138561</v>
-      </c>
-      <c r="J16" s="35" t="n">
-        <f aca="false">SUM(J2:J15)</f>
-        <v>139607</v>
-      </c>
+        <v>130562</v>
+      </c>
+      <c r="J16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="53"/>
       <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
+      <c r="J18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="35" t="s">
@@ -8884,18 +9599,16 @@
       <c r="E19" s="41" t="n">
         <v>48</v>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F19" s="35" t="n">
         <v>48</v>
       </c>
       <c r="G19" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="H19" s="35" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="1"/>
+      <c r="J19" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -8927,69 +9640,117 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-    </row>
-    <row r="26" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="111" t="s">
+        <v>496</v>
+      </c>
+      <c r="D25" s="111" t="s">
+        <v>497</v>
+      </c>
+      <c r="E25" s="111" t="s">
+        <v>498</v>
+      </c>
+      <c r="F25" s="111" t="s">
+        <v>499</v>
+      </c>
+      <c r="G25" s="111" t="s">
+        <v>500</v>
+      </c>
+      <c r="H25" s="111" t="s">
+        <v>501</v>
+      </c>
+      <c r="I25" s="111" t="s">
+        <v>502</v>
+      </c>
+      <c r="J25" s="111" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-    </row>
-    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="111" t="s">
+        <v>504</v>
+      </c>
+      <c r="D26" s="111" t="s">
+        <v>505</v>
+      </c>
+      <c r="E26" s="111" t="s">
+        <v>506</v>
+      </c>
+      <c r="F26" s="111" t="s">
+        <v>507</v>
+      </c>
+      <c r="G26" s="111" t="s">
+        <v>508</v>
+      </c>
+      <c r="H26" s="111" t="s">
+        <v>509</v>
+      </c>
+      <c r="I26" s="111" t="s">
+        <v>510</v>
+      </c>
+      <c r="J26" s="111" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
         <v>3</v>
       </c>
       <c r="B27" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="59"/>
-    </row>
-    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="58"/>
+    </row>
+    <row r="28" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B28" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
+      <c r="C28" s="111" t="s">
+        <v>512</v>
+      </c>
+      <c r="D28" s="111" t="s">
+        <v>513</v>
+      </c>
+      <c r="E28" s="111" t="s">
+        <v>512</v>
+      </c>
+      <c r="F28" s="111" t="s">
+        <v>514</v>
+      </c>
+      <c r="G28" s="111" t="s">
+        <v>515</v>
+      </c>
+      <c r="H28" s="111" t="s">
+        <v>516</v>
+      </c>
+      <c r="I28" s="111" t="s">
+        <v>517</v>
+      </c>
+      <c r="J28" s="111" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
@@ -8998,30 +9759,62 @@
       <c r="B29" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-    </row>
-    <row r="30" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="111" t="s">
+        <v>519</v>
+      </c>
+      <c r="D29" s="111" t="s">
+        <v>520</v>
+      </c>
+      <c r="E29" s="111" t="s">
+        <v>519</v>
+      </c>
+      <c r="F29" s="111" t="s">
+        <v>521</v>
+      </c>
+      <c r="G29" s="111" t="s">
+        <v>520</v>
+      </c>
+      <c r="H29" s="111" t="s">
+        <v>519</v>
+      </c>
+      <c r="I29" s="111" t="s">
+        <v>521</v>
+      </c>
+      <c r="J29" s="111" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
+      <c r="C30" s="111" t="s">
+        <v>523</v>
+      </c>
+      <c r="D30" s="111" t="s">
+        <v>524</v>
+      </c>
+      <c r="E30" s="111" t="s">
+        <v>523</v>
+      </c>
+      <c r="F30" s="111" t="s">
+        <v>525</v>
+      </c>
+      <c r="G30" s="111" t="s">
+        <v>524</v>
+      </c>
+      <c r="H30" s="111" t="s">
+        <v>523</v>
+      </c>
+      <c r="I30" s="111" t="s">
+        <v>525</v>
+      </c>
+      <c r="J30" s="111" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
@@ -9030,14 +9823,30 @@
       <c r="B31" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
+      <c r="C31" s="111" t="s">
+        <v>527</v>
+      </c>
+      <c r="D31" s="111" t="s">
+        <v>528</v>
+      </c>
+      <c r="E31" s="111" t="s">
+        <v>527</v>
+      </c>
+      <c r="F31" s="111" t="s">
+        <v>529</v>
+      </c>
+      <c r="G31" s="111" t="s">
+        <v>528</v>
+      </c>
+      <c r="H31" s="111" t="s">
+        <v>527</v>
+      </c>
+      <c r="I31" s="111" t="s">
+        <v>529</v>
+      </c>
+      <c r="J31" s="111" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
@@ -9046,14 +9855,30 @@
       <c r="B32" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
+      <c r="C32" s="111" t="s">
+        <v>531</v>
+      </c>
+      <c r="D32" s="111" t="s">
+        <v>532</v>
+      </c>
+      <c r="E32" s="111" t="s">
+        <v>531</v>
+      </c>
+      <c r="F32" s="111" t="s">
+        <v>533</v>
+      </c>
+      <c r="G32" s="111" t="s">
+        <v>532</v>
+      </c>
+      <c r="H32" s="111" t="s">
+        <v>531</v>
+      </c>
+      <c r="I32" s="111" t="s">
+        <v>533</v>
+      </c>
+      <c r="J32" s="111" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
@@ -9062,30 +9887,62 @@
       <c r="B33" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-    </row>
-    <row r="34" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="111" t="s">
+        <v>535</v>
+      </c>
+      <c r="D33" s="111" t="s">
+        <v>536</v>
+      </c>
+      <c r="E33" s="111" t="s">
+        <v>535</v>
+      </c>
+      <c r="F33" s="111" t="s">
+        <v>537</v>
+      </c>
+      <c r="G33" s="111" t="s">
+        <v>536</v>
+      </c>
+      <c r="H33" s="111" t="s">
+        <v>535</v>
+      </c>
+      <c r="I33" s="111" t="s">
+        <v>537</v>
+      </c>
+      <c r="J33" s="111" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
+      <c r="C34" s="111" t="s">
+        <v>539</v>
+      </c>
+      <c r="D34" s="111" t="s">
+        <v>540</v>
+      </c>
+      <c r="E34" s="111" t="s">
+        <v>539</v>
+      </c>
+      <c r="F34" s="111" t="s">
+        <v>541</v>
+      </c>
+      <c r="G34" s="111" t="s">
+        <v>540</v>
+      </c>
+      <c r="H34" s="111" t="s">
+        <v>539</v>
+      </c>
+      <c r="I34" s="111" t="s">
+        <v>541</v>
+      </c>
+      <c r="J34" s="111" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
@@ -9094,14 +9951,30 @@
       <c r="B35" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
+      <c r="C35" s="111" t="s">
+        <v>543</v>
+      </c>
+      <c r="D35" s="111" t="s">
+        <v>544</v>
+      </c>
+      <c r="E35" s="111" t="s">
+        <v>543</v>
+      </c>
+      <c r="F35" s="111" t="s">
+        <v>545</v>
+      </c>
+      <c r="G35" s="111" t="s">
+        <v>544</v>
+      </c>
+      <c r="H35" s="111" t="s">
+        <v>543</v>
+      </c>
+      <c r="I35" s="111" t="s">
+        <v>546</v>
+      </c>
+      <c r="J35" s="111" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
@@ -9110,250 +9983,394 @@
       <c r="B36" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-    </row>
-    <row r="37" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="111" t="s">
+        <v>548</v>
+      </c>
+      <c r="D36" s="111" t="s">
+        <v>549</v>
+      </c>
+      <c r="E36" s="111" t="s">
+        <v>548</v>
+      </c>
+      <c r="F36" s="111" t="s">
+        <v>550</v>
+      </c>
+      <c r="G36" s="111" t="s">
+        <v>549</v>
+      </c>
+      <c r="H36" s="111" t="s">
+        <v>548</v>
+      </c>
+      <c r="I36" s="111" t="s">
+        <v>550</v>
+      </c>
+      <c r="J36" s="111" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B37" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-    </row>
-    <row r="38" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="111" t="s">
+        <v>552</v>
+      </c>
+      <c r="D37" s="111" t="s">
+        <v>553</v>
+      </c>
+      <c r="E37" s="111" t="s">
+        <v>552</v>
+      </c>
+      <c r="F37" s="111" t="s">
+        <v>554</v>
+      </c>
+      <c r="G37" s="111" t="s">
+        <v>555</v>
+      </c>
+      <c r="H37" s="111" t="s">
+        <v>556</v>
+      </c>
+      <c r="I37" s="111" t="s">
+        <v>557</v>
+      </c>
+      <c r="J37" s="111" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-    </row>
-    <row r="39" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C38" s="111" t="s">
+        <v>559</v>
+      </c>
+      <c r="D38" s="111" t="s">
+        <v>560</v>
+      </c>
+      <c r="E38" s="111" t="s">
+        <v>559</v>
+      </c>
+      <c r="F38" s="111" t="s">
+        <v>561</v>
+      </c>
+      <c r="G38" s="111" t="s">
+        <v>562</v>
+      </c>
+      <c r="H38" s="111" t="s">
+        <v>563</v>
+      </c>
+      <c r="I38" s="111" t="s">
+        <v>564</v>
+      </c>
+      <c r="J38" s="111" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>15</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-    </row>
-    <row r="40" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C39" s="111" t="s">
+        <v>566</v>
+      </c>
+      <c r="D39" s="111" t="s">
+        <v>567</v>
+      </c>
+      <c r="E39" s="111" t="s">
+        <v>566</v>
+      </c>
+      <c r="F39" s="111" t="s">
+        <v>568</v>
+      </c>
+      <c r="G39" s="111" t="s">
+        <v>569</v>
+      </c>
+      <c r="H39" s="111" t="s">
+        <v>570</v>
+      </c>
+      <c r="I39" s="111" t="s">
+        <v>571</v>
+      </c>
+      <c r="J39" s="111" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B40" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-    </row>
-    <row r="41" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="111" t="s">
+        <v>573</v>
+      </c>
+      <c r="D40" s="111" t="s">
+        <v>574</v>
+      </c>
+      <c r="E40" s="111" t="s">
+        <v>573</v>
+      </c>
+      <c r="F40" s="111" t="s">
+        <v>575</v>
+      </c>
+      <c r="G40" s="111" t="s">
+        <v>576</v>
+      </c>
+      <c r="H40" s="111" t="s">
+        <v>577</v>
+      </c>
+      <c r="I40" s="111" t="s">
+        <v>578</v>
+      </c>
+      <c r="J40" s="111" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B41" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-    </row>
-    <row r="42" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="111" t="s">
+        <v>580</v>
+      </c>
+      <c r="D41" s="111" t="s">
+        <v>581</v>
+      </c>
+      <c r="E41" s="111" t="s">
+        <v>580</v>
+      </c>
+      <c r="F41" s="111" t="s">
+        <v>582</v>
+      </c>
+      <c r="G41" s="111" t="s">
+        <v>583</v>
+      </c>
+      <c r="H41" s="111" t="s">
+        <v>584</v>
+      </c>
+      <c r="I41" s="111" t="s">
+        <v>585</v>
+      </c>
+      <c r="J41" s="111" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-    </row>
-    <row r="43" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C42" s="111" t="s">
+        <v>587</v>
+      </c>
+      <c r="D42" s="111" t="s">
+        <v>588</v>
+      </c>
+      <c r="E42" s="111" t="s">
+        <v>587</v>
+      </c>
+      <c r="F42" s="111" t="s">
+        <v>589</v>
+      </c>
+      <c r="G42" s="111" t="s">
+        <v>590</v>
+      </c>
+      <c r="H42" s="111" t="s">
+        <v>591</v>
+      </c>
+      <c r="I42" s="111" t="s">
+        <v>592</v>
+      </c>
+      <c r="J42" s="111" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="56" t="n">
         <v>19</v>
       </c>
       <c r="B43" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-    </row>
-    <row r="44" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="111" t="s">
+        <v>594</v>
+      </c>
+      <c r="D43" s="111" t="s">
+        <v>595</v>
+      </c>
+      <c r="E43" s="111" t="s">
+        <v>596</v>
+      </c>
+      <c r="F43" s="111" t="s">
+        <v>597</v>
+      </c>
+      <c r="G43" s="111" t="s">
+        <v>598</v>
+      </c>
+      <c r="H43" s="111" t="s">
+        <v>599</v>
+      </c>
+      <c r="I43" s="111" t="s">
+        <v>600</v>
+      </c>
+      <c r="J43" s="111" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B44" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
+      <c r="C44" s="111" t="s">
+        <v>602</v>
+      </c>
+      <c r="D44" s="111" t="s">
+        <v>603</v>
+      </c>
+      <c r="E44" s="111" t="s">
+        <v>602</v>
+      </c>
+      <c r="F44" s="111" t="s">
+        <v>604</v>
+      </c>
+      <c r="G44" s="111" t="s">
+        <v>605</v>
+      </c>
+      <c r="H44" s="111" t="s">
+        <v>606</v>
+      </c>
+      <c r="I44" s="111" t="s">
+        <v>607</v>
+      </c>
+      <c r="J44" s="111" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="59"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="59"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="59"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="59"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="58"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="59"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="58"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="59"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="58"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="59"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="58"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="42"/>
@@ -9443,7 +10460,7 @@
       <c r="H61" s="42"/>
       <c r="I61" s="42"/>
     </row>
-    <row r="62" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="54" t="s">
         <v>91</v>
       </c>
@@ -9475,325 +10492,629 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B63" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="57"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="57"/>
-    </row>
-    <row r="64" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C63" s="111" t="s">
+        <v>609</v>
+      </c>
+      <c r="D63" s="111" t="s">
+        <v>610</v>
+      </c>
+      <c r="E63" s="111" t="s">
+        <v>609</v>
+      </c>
+      <c r="F63" s="111" t="s">
+        <v>611</v>
+      </c>
+      <c r="G63" s="111" t="s">
+        <v>612</v>
+      </c>
+      <c r="H63" s="111" t="s">
+        <v>613</v>
+      </c>
+      <c r="I63" s="111" t="s">
+        <v>614</v>
+      </c>
+      <c r="J63" s="111" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B64" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
-    </row>
-    <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="D64" s="42" t="s">
+        <v>617</v>
+      </c>
+      <c r="E64" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="F64" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="G64" s="42" t="s">
+        <v>619</v>
+      </c>
+      <c r="H64" s="42" t="s">
+        <v>620</v>
+      </c>
+      <c r="I64" s="42" t="s">
+        <v>621</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
         <v>3</v>
       </c>
       <c r="B65" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="59"/>
-    </row>
-    <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="58"/>
+    </row>
+    <row r="66" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B66" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C66" s="57"/>
-      <c r="D66" s="57"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="57"/>
-      <c r="J66" s="57"/>
-    </row>
-    <row r="67" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C66" s="42" t="s">
+        <v>623</v>
+      </c>
+      <c r="D66" s="42" t="s">
+        <v>624</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>623</v>
+      </c>
+      <c r="F66" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="G66" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="H66" s="42" t="s">
+        <v>627</v>
+      </c>
+      <c r="I66" s="42" t="s">
+        <v>628</v>
+      </c>
+      <c r="J66" s="42" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B67" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
-      <c r="J67" s="57"/>
-    </row>
-    <row r="68" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="42" t="s">
+        <v>630</v>
+      </c>
+      <c r="D67" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="E67" s="42" t="s">
+        <v>630</v>
+      </c>
+      <c r="F67" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>633</v>
+      </c>
+      <c r="H67" s="42" t="s">
+        <v>634</v>
+      </c>
+      <c r="I67" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="J67" s="42" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B68" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="57"/>
-    </row>
-    <row r="69" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C68" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="D68" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="E68" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="F68" s="42" t="s">
+        <v>639</v>
+      </c>
+      <c r="G68" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="H68" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="I68" s="42" t="s">
+        <v>642</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
         <v>7</v>
       </c>
       <c r="B69" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="57"/>
-      <c r="J69" s="57"/>
-    </row>
-    <row r="70" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="42" t="s">
+        <v>644</v>
+      </c>
+      <c r="D69" s="42" t="s">
+        <v>645</v>
+      </c>
+      <c r="E69" s="42" t="s">
+        <v>644</v>
+      </c>
+      <c r="F69" s="42" t="s">
+        <v>646</v>
+      </c>
+      <c r="G69" s="42" t="s">
+        <v>647</v>
+      </c>
+      <c r="H69" s="42" t="s">
+        <v>648</v>
+      </c>
+      <c r="I69" s="42" t="s">
+        <v>649</v>
+      </c>
+      <c r="J69" s="42" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B70" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
-    </row>
-    <row r="71" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C70" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="D70" s="42" t="s">
+        <v>652</v>
+      </c>
+      <c r="E70" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="F70" s="42" t="s">
+        <v>653</v>
+      </c>
+      <c r="G70" s="42" t="s">
+        <v>654</v>
+      </c>
+      <c r="H70" s="42" t="s">
+        <v>655</v>
+      </c>
+      <c r="I70" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="J70" s="42" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B71" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
-      <c r="I71" s="57"/>
-      <c r="J71" s="57"/>
-    </row>
-    <row r="72" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>659</v>
+      </c>
+      <c r="E71" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="F71" s="42" t="s">
+        <v>660</v>
+      </c>
+      <c r="G71" s="42" t="s">
+        <v>661</v>
+      </c>
+      <c r="H71" s="42" t="s">
+        <v>662</v>
+      </c>
+      <c r="I71" s="42" t="s">
+        <v>663</v>
+      </c>
+      <c r="J71" s="42" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B72" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
-    </row>
-    <row r="73" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="42" t="s">
+        <v>665</v>
+      </c>
+      <c r="D72" s="42" t="s">
+        <v>666</v>
+      </c>
+      <c r="E72" s="42" t="s">
+        <v>665</v>
+      </c>
+      <c r="F72" s="42" t="s">
+        <v>667</v>
+      </c>
+      <c r="G72" s="42" t="s">
+        <v>668</v>
+      </c>
+      <c r="H72" s="42" t="s">
+        <v>669</v>
+      </c>
+      <c r="I72" s="42" t="s">
+        <v>670</v>
+      </c>
+      <c r="J72" s="42" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
         <v>11</v>
       </c>
       <c r="B73" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="57"/>
-      <c r="J73" s="57"/>
-    </row>
-    <row r="74" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C73" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>673</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="F73" s="42" t="s">
+        <v>674</v>
+      </c>
+      <c r="G73" s="42" t="s">
+        <v>675</v>
+      </c>
+      <c r="H73" s="42" t="s">
+        <v>676</v>
+      </c>
+      <c r="I73" s="42" t="s">
+        <v>677</v>
+      </c>
+      <c r="J73" s="42" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B74" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
-    </row>
-    <row r="75" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>680</v>
+      </c>
+      <c r="E74" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="F74" s="42" t="s">
+        <v>681</v>
+      </c>
+      <c r="G74" s="42" t="s">
+        <v>682</v>
+      </c>
+      <c r="H74" s="42" t="s">
+        <v>683</v>
+      </c>
+      <c r="I74" s="42" t="s">
+        <v>684</v>
+      </c>
+      <c r="J74" s="42" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B75" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C75" s="57"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
-    </row>
-    <row r="76" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="42" t="s">
+        <v>686</v>
+      </c>
+      <c r="D75" s="42" t="s">
+        <v>687</v>
+      </c>
+      <c r="E75" s="42" t="s">
+        <v>686</v>
+      </c>
+      <c r="F75" s="42" t="s">
+        <v>688</v>
+      </c>
+      <c r="G75" s="42" t="s">
+        <v>689</v>
+      </c>
+      <c r="H75" s="42" t="s">
+        <v>690</v>
+      </c>
+      <c r="I75" s="42" t="s">
+        <v>691</v>
+      </c>
+      <c r="J75" s="42" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B76" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="57"/>
-      <c r="D76" s="57"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="57"/>
-    </row>
-    <row r="77" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="42" t="s">
+        <v>693</v>
+      </c>
+      <c r="D76" s="42" t="s">
+        <v>694</v>
+      </c>
+      <c r="E76" s="42" t="s">
+        <v>693</v>
+      </c>
+      <c r="F76" s="42" t="s">
+        <v>695</v>
+      </c>
+      <c r="G76" s="42" t="s">
+        <v>696</v>
+      </c>
+      <c r="H76" s="42" t="s">
+        <v>697</v>
+      </c>
+      <c r="I76" s="42" t="s">
+        <v>698</v>
+      </c>
+      <c r="J76" s="42" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="56" t="n">
         <v>15</v>
       </c>
       <c r="B77" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="57"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="57"/>
-    </row>
-    <row r="78" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="D77" s="42" t="s">
+        <v>701</v>
+      </c>
+      <c r="E77" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="F77" s="42" t="s">
+        <v>702</v>
+      </c>
+      <c r="G77" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="H77" s="42" t="s">
+        <v>704</v>
+      </c>
+      <c r="I77" s="42" t="s">
+        <v>705</v>
+      </c>
+      <c r="J77" s="42" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B78" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C78" s="57"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="57"/>
-    </row>
-    <row r="79" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="42" t="s">
+        <v>707</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>708</v>
+      </c>
+      <c r="E78" s="42" t="s">
+        <v>707</v>
+      </c>
+      <c r="F78" s="42" t="s">
+        <v>709</v>
+      </c>
+      <c r="G78" s="42" t="s">
+        <v>710</v>
+      </c>
+      <c r="H78" s="42" t="s">
+        <v>711</v>
+      </c>
+      <c r="I78" s="42" t="s">
+        <v>712</v>
+      </c>
+      <c r="J78" s="42" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B79" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C79" s="57"/>
-      <c r="D79" s="57"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="57"/>
-    </row>
-    <row r="80" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="116" t="s">
+        <v>714</v>
+      </c>
+      <c r="D79" s="116" t="s">
+        <v>715</v>
+      </c>
+      <c r="E79" s="116" t="s">
+        <v>714</v>
+      </c>
+      <c r="F79" s="116" t="s">
+        <v>716</v>
+      </c>
+      <c r="G79" s="116" t="s">
+        <v>717</v>
+      </c>
+      <c r="H79" s="116" t="s">
+        <v>718</v>
+      </c>
+      <c r="I79" s="116" t="s">
+        <v>719</v>
+      </c>
+      <c r="J79" s="116" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B80" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="57"/>
-      <c r="D80" s="57"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57"/>
-      <c r="I80" s="57"/>
-      <c r="J80" s="57"/>
-    </row>
-    <row r="81" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C80" s="42" t="s">
+        <v>721</v>
+      </c>
+      <c r="D80" s="42" t="s">
+        <v>722</v>
+      </c>
+      <c r="E80" s="42" t="s">
+        <v>721</v>
+      </c>
+      <c r="F80" s="42" t="s">
+        <v>723</v>
+      </c>
+      <c r="G80" s="42" t="s">
+        <v>724</v>
+      </c>
+      <c r="H80" s="42" t="s">
+        <v>725</v>
+      </c>
+      <c r="I80" s="42" t="s">
+        <v>726</v>
+      </c>
+      <c r="J80" s="42" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="56" t="n">
         <v>19</v>
       </c>
       <c r="B81" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
-    </row>
-    <row r="82" customFormat="false" ht="46.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C81" s="42" t="s">
+        <v>728</v>
+      </c>
+      <c r="D81" s="42" t="s">
+        <v>729</v>
+      </c>
+      <c r="E81" s="42" t="s">
+        <v>728</v>
+      </c>
+      <c r="F81" s="42" t="s">
+        <v>730</v>
+      </c>
+      <c r="G81" s="42" t="s">
+        <v>731</v>
+      </c>
+      <c r="H81" s="42" t="s">
+        <v>732</v>
+      </c>
+      <c r="I81" s="42" t="s">
+        <v>733</v>
+      </c>
+      <c r="J81" s="42" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B82" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
-      <c r="I82" s="57"/>
-      <c r="J82" s="57"/>
+      <c r="C82" s="42" t="s">
+        <v>735</v>
+      </c>
+      <c r="D82" s="42" t="s">
+        <v>736</v>
+      </c>
+      <c r="E82" s="42" t="s">
+        <v>735</v>
+      </c>
+      <c r="F82" s="42" t="s">
+        <v>737</v>
+      </c>
+      <c r="G82" s="42" t="s">
+        <v>738</v>
+      </c>
+      <c r="H82" s="42" t="s">
+        <v>739</v>
+      </c>
+      <c r="I82" s="42" t="s">
+        <v>740</v>
+      </c>
+      <c r="J82" s="42" t="s">
+        <v>741</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -2387,25 +2387,25 @@
     <t xml:space="preserve">0.662073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2429094216694166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9286091784228083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3065005314829971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24640036109307917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7456257814915517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.18999128346892563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24161345245704607</t>
+    <t xml:space="preserve">0.242909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.241613</t>
   </si>
   <si>
     <t xml:space="preserve">0.223220</t>
@@ -2790,7 +2790,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="113">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3235,27 +3235,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9095,7 +9079,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="15.85"/>
   </cols>
   <sheetData>
-    <row r="1" s="110" customFormat="true" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="110" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
@@ -9123,7 +9107,7 @@
       <c r="I1" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="XFC1" s="0"/>
+      <c r="XFC1" s="1"/>
       <c r="XFD1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9136,10 +9120,10 @@
       <c r="C2" s="42" t="n">
         <v>1786239</v>
       </c>
-      <c r="D2" s="111" t="n">
+      <c r="D2" s="42" t="n">
         <v>1715048</v>
       </c>
-      <c r="E2" s="111" t="n">
+      <c r="E2" s="42" t="n">
         <v>1372038</v>
       </c>
       <c r="F2" s="46" t="n">
@@ -9154,7 +9138,7 @@
       <c r="I2" s="44" t="n">
         <v>10000</v>
       </c>
-      <c r="J2" s="0"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
@@ -9166,7 +9150,7 @@
       <c r="C3" s="42" t="n">
         <v>349240</v>
       </c>
-      <c r="D3" s="111" t="n">
+      <c r="D3" s="42" t="n">
         <v>346143</v>
       </c>
       <c r="E3" s="42" t="n">
@@ -9178,13 +9162,13 @@
       <c r="G3" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H3" s="111" t="n">
+      <c r="H3" s="42" t="n">
         <v>9168</v>
       </c>
       <c r="I3" s="44" t="n">
         <v>10000</v>
       </c>
-      <c r="J3" s="0"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
@@ -9196,7 +9180,7 @@
       <c r="C4" s="42" t="n">
         <v>161323</v>
       </c>
-      <c r="D4" s="111" t="n">
+      <c r="D4" s="42" t="n">
         <v>161323</v>
       </c>
       <c r="E4" s="42" t="n">
@@ -9208,13 +9192,13 @@
       <c r="G4" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H4" s="111" t="n">
+      <c r="H4" s="42" t="n">
         <v>9973</v>
       </c>
-      <c r="I4" s="112" t="n">
+      <c r="I4" s="44" t="n">
         <v>9972</v>
       </c>
-      <c r="J4" s="0"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
@@ -9226,7 +9210,7 @@
       <c r="C5" s="42" t="n">
         <v>95733</v>
       </c>
-      <c r="D5" s="111" t="n">
+      <c r="D5" s="42" t="n">
         <v>95729</v>
       </c>
       <c r="E5" s="42" t="n">
@@ -9238,13 +9222,13 @@
       <c r="G5" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H5" s="111" t="n">
+      <c r="H5" s="42" t="n">
         <v>9376</v>
       </c>
-      <c r="I5" s="112" t="n">
+      <c r="I5" s="44" t="n">
         <v>9988</v>
       </c>
-      <c r="J5" s="0"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
@@ -9256,7 +9240,7 @@
       <c r="C6" s="42" t="n">
         <v>9531</v>
       </c>
-      <c r="D6" s="111" t="n">
+      <c r="D6" s="42" t="n">
         <v>9531</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -9268,13 +9252,13 @@
       <c r="G6" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H6" s="111" t="n">
+      <c r="H6" s="42" t="n">
         <v>9978</v>
       </c>
-      <c r="I6" s="112" t="n">
+      <c r="I6" s="44" t="n">
         <v>9996</v>
       </c>
-      <c r="J6" s="0"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
@@ -9286,7 +9270,7 @@
       <c r="C7" s="42" t="n">
         <v>8364</v>
       </c>
-      <c r="D7" s="111" t="n">
+      <c r="D7" s="42" t="n">
         <v>8364</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -9298,13 +9282,13 @@
       <c r="G7" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H7" s="111" t="n">
+      <c r="H7" s="42" t="n">
         <v>9351</v>
       </c>
-      <c r="I7" s="112" t="n">
+      <c r="I7" s="44" t="n">
         <v>9625</v>
       </c>
-      <c r="J7" s="0"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
@@ -9328,13 +9312,13 @@
       <c r="G8" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="111" t="n">
+      <c r="H8" s="42" t="n">
         <v>9571</v>
       </c>
-      <c r="I8" s="112" t="n">
+      <c r="I8" s="44" t="n">
         <v>9632</v>
       </c>
-      <c r="J8" s="0"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
@@ -9358,13 +9342,13 @@
       <c r="G9" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="111" t="n">
+      <c r="H9" s="42" t="n">
         <v>9947</v>
       </c>
-      <c r="I9" s="112" t="n">
+      <c r="I9" s="44" t="n">
         <v>9981</v>
       </c>
-      <c r="J9" s="0"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
@@ -9388,13 +9372,13 @@
       <c r="G10" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H10" s="111" t="n">
+      <c r="H10" s="42" t="n">
         <v>9991</v>
       </c>
-      <c r="I10" s="112" t="n">
+      <c r="I10" s="44" t="n">
         <v>9993</v>
       </c>
-      <c r="J10" s="0"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
@@ -9418,13 +9402,13 @@
       <c r="G11" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H11" s="111" t="n">
+      <c r="H11" s="42" t="n">
         <v>9620</v>
       </c>
-      <c r="I11" s="112" t="n">
+      <c r="I11" s="44" t="n">
         <v>8581</v>
       </c>
-      <c r="J11" s="0"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
@@ -9448,13 +9432,13 @@
       <c r="G12" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H12" s="111" t="n">
+      <c r="H12" s="42" t="n">
         <v>8106</v>
       </c>
-      <c r="I12" s="112" t="n">
+      <c r="I12" s="44" t="n">
         <v>8117</v>
       </c>
-      <c r="J12" s="0"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
@@ -9478,13 +9462,13 @@
       <c r="G13" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H13" s="111" t="n">
+      <c r="H13" s="42" t="n">
         <v>6944</v>
       </c>
-      <c r="I13" s="112" t="n">
+      <c r="I13" s="44" t="n">
         <v>6907</v>
       </c>
-      <c r="J13" s="0"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
@@ -9508,16 +9492,16 @@
       <c r="G14" s="46" t="n">
         <v>10000</v>
       </c>
-      <c r="H14" s="111" t="n">
+      <c r="H14" s="42" t="n">
         <v>9811</v>
       </c>
-      <c r="I14" s="112" t="n">
+      <c r="I14" s="44" t="n">
         <v>9824</v>
       </c>
-      <c r="J14" s="0"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="111" t="s">
         <v>168</v>
       </c>
       <c r="B15" s="48" t="n">
@@ -9538,13 +9522,13 @@
       <c r="G15" s="51" t="n">
         <v>10000</v>
       </c>
-      <c r="H15" s="114" t="n">
+      <c r="H15" s="49" t="n">
         <v>9974</v>
       </c>
-      <c r="I15" s="115" t="n">
+      <c r="I15" s="52" t="n">
         <v>7946</v>
       </c>
-      <c r="J15" s="0"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="35" t="n">
@@ -9575,16 +9559,16 @@
         <f aca="false">SUM(I2:I15)</f>
         <v>130562</v>
       </c>
-      <c r="J16" s="0"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="1"/>
-      <c r="J17" s="0"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="53"/>
       <c r="F18" s="41"/>
-      <c r="J18" s="0"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="35" t="s">
@@ -9606,7 +9590,7 @@
         <v>48</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="J19" s="0"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
@@ -9640,67 +9624,67 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="111" t="s">
+      <c r="C25" s="42" t="s">
         <v>496</v>
       </c>
-      <c r="D25" s="111" t="s">
+      <c r="D25" s="42" t="s">
         <v>497</v>
       </c>
-      <c r="E25" s="111" t="s">
+      <c r="E25" s="42" t="s">
         <v>498</v>
       </c>
-      <c r="F25" s="111" t="s">
+      <c r="F25" s="42" t="s">
         <v>499</v>
       </c>
-      <c r="G25" s="111" t="s">
+      <c r="G25" s="42" t="s">
         <v>500</v>
       </c>
-      <c r="H25" s="111" t="s">
+      <c r="H25" s="42" t="s">
         <v>501</v>
       </c>
-      <c r="I25" s="111" t="s">
+      <c r="I25" s="42" t="s">
         <v>502</v>
       </c>
-      <c r="J25" s="111" t="s">
+      <c r="J25" s="42" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="111" t="s">
+      <c r="C26" s="42" t="s">
         <v>504</v>
       </c>
-      <c r="D26" s="111" t="s">
+      <c r="D26" s="42" t="s">
         <v>505</v>
       </c>
-      <c r="E26" s="111" t="s">
+      <c r="E26" s="42" t="s">
         <v>506</v>
       </c>
-      <c r="F26" s="111" t="s">
+      <c r="F26" s="42" t="s">
         <v>507</v>
       </c>
-      <c r="G26" s="111" t="s">
+      <c r="G26" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="H26" s="111" t="s">
+      <c r="H26" s="42" t="s">
         <v>509</v>
       </c>
-      <c r="I26" s="111" t="s">
+      <c r="I26" s="42" t="s">
         <v>510</v>
       </c>
-      <c r="J26" s="111" t="s">
+      <c r="J26" s="42" t="s">
         <v>511</v>
       </c>
     </row>
@@ -9720,547 +9704,547 @@
       <c r="I27" s="57"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B28" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="111" t="s">
+      <c r="C28" s="42" t="s">
         <v>512</v>
       </c>
-      <c r="D28" s="111" t="s">
+      <c r="D28" s="42" t="s">
         <v>513</v>
       </c>
-      <c r="E28" s="111" t="s">
+      <c r="E28" s="42" t="s">
         <v>512</v>
       </c>
-      <c r="F28" s="111" t="s">
+      <c r="F28" s="42" t="s">
         <v>514</v>
       </c>
-      <c r="G28" s="111" t="s">
+      <c r="G28" s="42" t="s">
         <v>515</v>
       </c>
-      <c r="H28" s="111" t="s">
+      <c r="H28" s="42" t="s">
         <v>516</v>
       </c>
-      <c r="I28" s="111" t="s">
+      <c r="I28" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="J28" s="111" t="s">
+      <c r="J28" s="42" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="111" t="s">
+      <c r="C29" s="42" t="s">
         <v>519</v>
       </c>
-      <c r="D29" s="111" t="s">
+      <c r="D29" s="42" t="s">
         <v>520</v>
       </c>
-      <c r="E29" s="111" t="s">
+      <c r="E29" s="42" t="s">
         <v>519</v>
       </c>
-      <c r="F29" s="111" t="s">
+      <c r="F29" s="42" t="s">
         <v>521</v>
       </c>
-      <c r="G29" s="111" t="s">
+      <c r="G29" s="42" t="s">
         <v>520</v>
       </c>
-      <c r="H29" s="111" t="s">
+      <c r="H29" s="42" t="s">
         <v>519</v>
       </c>
-      <c r="I29" s="111" t="s">
+      <c r="I29" s="42" t="s">
         <v>521</v>
       </c>
-      <c r="J29" s="111" t="s">
+      <c r="J29" s="42" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="111" t="s">
+      <c r="C30" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="D30" s="111" t="s">
+      <c r="D30" s="42" t="s">
         <v>524</v>
       </c>
-      <c r="E30" s="111" t="s">
+      <c r="E30" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="F30" s="111" t="s">
+      <c r="F30" s="42" t="s">
         <v>525</v>
       </c>
-      <c r="G30" s="111" t="s">
+      <c r="G30" s="42" t="s">
         <v>524</v>
       </c>
-      <c r="H30" s="111" t="s">
+      <c r="H30" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="I30" s="111" t="s">
+      <c r="I30" s="42" t="s">
         <v>525</v>
       </c>
-      <c r="J30" s="111" t="s">
+      <c r="J30" s="42" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
         <v>7</v>
       </c>
       <c r="B31" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="111" t="s">
+      <c r="C31" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="D31" s="111" t="s">
+      <c r="D31" s="42" t="s">
         <v>528</v>
       </c>
-      <c r="E31" s="111" t="s">
+      <c r="E31" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="F31" s="111" t="s">
+      <c r="F31" s="42" t="s">
         <v>529</v>
       </c>
-      <c r="G31" s="111" t="s">
+      <c r="G31" s="42" t="s">
         <v>528</v>
       </c>
-      <c r="H31" s="111" t="s">
+      <c r="H31" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="I31" s="111" t="s">
+      <c r="I31" s="42" t="s">
         <v>529</v>
       </c>
-      <c r="J31" s="111" t="s">
+      <c r="J31" s="42" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B32" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="111" t="s">
+      <c r="C32" s="42" t="s">
         <v>531</v>
       </c>
-      <c r="D32" s="111" t="s">
+      <c r="D32" s="42" t="s">
         <v>532</v>
       </c>
-      <c r="E32" s="111" t="s">
+      <c r="E32" s="42" t="s">
         <v>531</v>
       </c>
-      <c r="F32" s="111" t="s">
+      <c r="F32" s="42" t="s">
         <v>533</v>
       </c>
-      <c r="G32" s="111" t="s">
+      <c r="G32" s="42" t="s">
         <v>532</v>
       </c>
-      <c r="H32" s="111" t="s">
+      <c r="H32" s="42" t="s">
         <v>531</v>
       </c>
-      <c r="I32" s="111" t="s">
+      <c r="I32" s="42" t="s">
         <v>533</v>
       </c>
-      <c r="J32" s="111" t="s">
+      <c r="J32" s="42" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B33" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="111" t="s">
+      <c r="C33" s="42" t="s">
         <v>535</v>
       </c>
-      <c r="D33" s="111" t="s">
+      <c r="D33" s="42" t="s">
         <v>536</v>
       </c>
-      <c r="E33" s="111" t="s">
+      <c r="E33" s="42" t="s">
         <v>535</v>
       </c>
-      <c r="F33" s="111" t="s">
+      <c r="F33" s="42" t="s">
         <v>537</v>
       </c>
-      <c r="G33" s="111" t="s">
+      <c r="G33" s="42" t="s">
         <v>536</v>
       </c>
-      <c r="H33" s="111" t="s">
+      <c r="H33" s="42" t="s">
         <v>535</v>
       </c>
-      <c r="I33" s="111" t="s">
+      <c r="I33" s="42" t="s">
         <v>537</v>
       </c>
-      <c r="J33" s="111" t="s">
+      <c r="J33" s="42" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="111" t="s">
+      <c r="C34" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="D34" s="111" t="s">
+      <c r="D34" s="42" t="s">
         <v>540</v>
       </c>
-      <c r="E34" s="111" t="s">
+      <c r="E34" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="F34" s="111" t="s">
+      <c r="F34" s="42" t="s">
         <v>541</v>
       </c>
-      <c r="G34" s="111" t="s">
+      <c r="G34" s="42" t="s">
         <v>540</v>
       </c>
-      <c r="H34" s="111" t="s">
+      <c r="H34" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="I34" s="111" t="s">
+      <c r="I34" s="42" t="s">
         <v>541</v>
       </c>
-      <c r="J34" s="111" t="s">
+      <c r="J34" s="42" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
         <v>11</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="111" t="s">
+      <c r="C35" s="42" t="s">
         <v>543</v>
       </c>
-      <c r="D35" s="111" t="s">
+      <c r="D35" s="42" t="s">
         <v>544</v>
       </c>
-      <c r="E35" s="111" t="s">
+      <c r="E35" s="42" t="s">
         <v>543</v>
       </c>
-      <c r="F35" s="111" t="s">
+      <c r="F35" s="42" t="s">
         <v>545</v>
       </c>
-      <c r="G35" s="111" t="s">
+      <c r="G35" s="42" t="s">
         <v>544</v>
       </c>
-      <c r="H35" s="111" t="s">
+      <c r="H35" s="42" t="s">
         <v>543</v>
       </c>
-      <c r="I35" s="111" t="s">
+      <c r="I35" s="42" t="s">
         <v>546</v>
       </c>
-      <c r="J35" s="111" t="s">
+      <c r="J35" s="42" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B36" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="111" t="s">
+      <c r="C36" s="42" t="s">
         <v>548</v>
       </c>
-      <c r="D36" s="111" t="s">
+      <c r="D36" s="42" t="s">
         <v>549</v>
       </c>
-      <c r="E36" s="111" t="s">
+      <c r="E36" s="42" t="s">
         <v>548</v>
       </c>
-      <c r="F36" s="111" t="s">
+      <c r="F36" s="42" t="s">
         <v>550</v>
       </c>
-      <c r="G36" s="111" t="s">
+      <c r="G36" s="42" t="s">
         <v>549</v>
       </c>
-      <c r="H36" s="111" t="s">
+      <c r="H36" s="42" t="s">
         <v>548</v>
       </c>
-      <c r="I36" s="111" t="s">
+      <c r="I36" s="42" t="s">
         <v>550</v>
       </c>
-      <c r="J36" s="111" t="s">
+      <c r="J36" s="42" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B37" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="111" t="s">
+      <c r="C37" s="42" t="s">
         <v>552</v>
       </c>
-      <c r="D37" s="111" t="s">
+      <c r="D37" s="42" t="s">
         <v>553</v>
       </c>
-      <c r="E37" s="111" t="s">
+      <c r="E37" s="42" t="s">
         <v>552</v>
       </c>
-      <c r="F37" s="111" t="s">
+      <c r="F37" s="42" t="s">
         <v>554</v>
       </c>
-      <c r="G37" s="111" t="s">
+      <c r="G37" s="42" t="s">
         <v>555</v>
       </c>
-      <c r="H37" s="111" t="s">
+      <c r="H37" s="42" t="s">
         <v>556</v>
       </c>
-      <c r="I37" s="111" t="s">
+      <c r="I37" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="J37" s="111" t="s">
+      <c r="J37" s="42" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="111" t="s">
+      <c r="C38" s="42" t="s">
         <v>559</v>
       </c>
-      <c r="D38" s="111" t="s">
+      <c r="D38" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="E38" s="111" t="s">
+      <c r="E38" s="42" t="s">
         <v>559</v>
       </c>
-      <c r="F38" s="111" t="s">
+      <c r="F38" s="42" t="s">
         <v>561</v>
       </c>
-      <c r="G38" s="111" t="s">
+      <c r="G38" s="42" t="s">
         <v>562</v>
       </c>
-      <c r="H38" s="111" t="s">
+      <c r="H38" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="I38" s="111" t="s">
+      <c r="I38" s="42" t="s">
         <v>564</v>
       </c>
-      <c r="J38" s="111" t="s">
+      <c r="J38" s="42" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>15</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="111" t="s">
+      <c r="C39" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="D39" s="111" t="s">
+      <c r="D39" s="42" t="s">
         <v>567</v>
       </c>
-      <c r="E39" s="111" t="s">
+      <c r="E39" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="F39" s="111" t="s">
+      <c r="F39" s="42" t="s">
         <v>568</v>
       </c>
-      <c r="G39" s="111" t="s">
+      <c r="G39" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="H39" s="111" t="s">
+      <c r="H39" s="42" t="s">
         <v>570</v>
       </c>
-      <c r="I39" s="111" t="s">
+      <c r="I39" s="42" t="s">
         <v>571</v>
       </c>
-      <c r="J39" s="111" t="s">
+      <c r="J39" s="42" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B40" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="111" t="s">
+      <c r="C40" s="42" t="s">
         <v>573</v>
       </c>
-      <c r="D40" s="111" t="s">
+      <c r="D40" s="42" t="s">
         <v>574</v>
       </c>
-      <c r="E40" s="111" t="s">
+      <c r="E40" s="42" t="s">
         <v>573</v>
       </c>
-      <c r="F40" s="111" t="s">
+      <c r="F40" s="42" t="s">
         <v>575</v>
       </c>
-      <c r="G40" s="111" t="s">
+      <c r="G40" s="42" t="s">
         <v>576</v>
       </c>
-      <c r="H40" s="111" t="s">
+      <c r="H40" s="42" t="s">
         <v>577</v>
       </c>
-      <c r="I40" s="111" t="s">
+      <c r="I40" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="J40" s="111" t="s">
+      <c r="J40" s="42" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B41" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="111" t="s">
+      <c r="C41" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="D41" s="111" t="s">
+      <c r="D41" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="E41" s="111" t="s">
+      <c r="E41" s="42" t="s">
         <v>580</v>
       </c>
-      <c r="F41" s="111" t="s">
+      <c r="F41" s="42" t="s">
         <v>582</v>
       </c>
-      <c r="G41" s="111" t="s">
+      <c r="G41" s="42" t="s">
         <v>583</v>
       </c>
-      <c r="H41" s="111" t="s">
+      <c r="H41" s="42" t="s">
         <v>584</v>
       </c>
-      <c r="I41" s="111" t="s">
+      <c r="I41" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="J41" s="111" t="s">
+      <c r="J41" s="42" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="111" t="s">
+      <c r="C42" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="D42" s="111" t="s">
+      <c r="D42" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="E42" s="111" t="s">
+      <c r="E42" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="F42" s="111" t="s">
+      <c r="F42" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="G42" s="111" t="s">
+      <c r="G42" s="42" t="s">
         <v>590</v>
       </c>
-      <c r="H42" s="111" t="s">
+      <c r="H42" s="42" t="s">
         <v>591</v>
       </c>
-      <c r="I42" s="111" t="s">
+      <c r="I42" s="42" t="s">
         <v>592</v>
       </c>
-      <c r="J42" s="111" t="s">
+      <c r="J42" s="42" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="56" t="n">
         <v>19</v>
       </c>
       <c r="B43" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="111" t="s">
+      <c r="C43" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="D43" s="111" t="s">
+      <c r="D43" s="42" t="s">
         <v>595</v>
       </c>
-      <c r="E43" s="111" t="s">
+      <c r="E43" s="42" t="s">
         <v>596</v>
       </c>
-      <c r="F43" s="111" t="s">
+      <c r="F43" s="42" t="s">
         <v>597</v>
       </c>
-      <c r="G43" s="111" t="s">
+      <c r="G43" s="42" t="s">
         <v>598</v>
       </c>
-      <c r="H43" s="111" t="s">
+      <c r="H43" s="42" t="s">
         <v>599</v>
       </c>
-      <c r="I43" s="111" t="s">
+      <c r="I43" s="42" t="s">
         <v>600</v>
       </c>
-      <c r="J43" s="111" t="s">
+      <c r="J43" s="42" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B44" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="111" t="s">
+      <c r="C44" s="42" t="s">
         <v>602</v>
       </c>
-      <c r="D44" s="111" t="s">
+      <c r="D44" s="42" t="s">
         <v>603</v>
       </c>
-      <c r="E44" s="111" t="s">
+      <c r="E44" s="42" t="s">
         <v>602</v>
       </c>
-      <c r="F44" s="111" t="s">
+      <c r="F44" s="42" t="s">
         <v>604</v>
       </c>
-      <c r="G44" s="111" t="s">
+      <c r="G44" s="42" t="s">
         <v>605</v>
       </c>
-      <c r="H44" s="111" t="s">
+      <c r="H44" s="42" t="s">
         <v>606</v>
       </c>
-      <c r="I44" s="111" t="s">
+      <c r="I44" s="42" t="s">
         <v>607</v>
       </c>
-      <c r="J44" s="111" t="s">
+      <c r="J44" s="42" t="s">
         <v>608</v>
       </c>
     </row>
@@ -10499,32 +10483,32 @@
       <c r="B63" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="111" t="s">
+      <c r="C63" s="42" t="s">
         <v>609</v>
       </c>
-      <c r="D63" s="111" t="s">
+      <c r="D63" s="42" t="s">
         <v>610</v>
       </c>
-      <c r="E63" s="111" t="s">
+      <c r="E63" s="42" t="s">
         <v>609</v>
       </c>
-      <c r="F63" s="111" t="s">
+      <c r="F63" s="42" t="s">
         <v>611</v>
       </c>
-      <c r="G63" s="111" t="s">
+      <c r="G63" s="42" t="s">
         <v>612</v>
       </c>
-      <c r="H63" s="111" t="s">
+      <c r="H63" s="42" t="s">
         <v>613</v>
       </c>
-      <c r="I63" s="111" t="s">
+      <c r="I63" s="42" t="s">
         <v>614</v>
       </c>
-      <c r="J63" s="111" t="s">
+      <c r="J63" s="42" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
         <v>2</v>
       </c>
@@ -10556,7 +10540,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
         <v>3</v>
       </c>
@@ -10572,7 +10556,7 @@
       <c r="I65" s="57"/>
       <c r="J65" s="58"/>
     </row>
-    <row r="66" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
         <v>4</v>
       </c>
@@ -10604,7 +10588,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
         <v>5</v>
       </c>
@@ -10636,7 +10620,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>6</v>
       </c>
@@ -10668,7 +10652,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
         <v>7</v>
       </c>
@@ -10700,7 +10684,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>8</v>
       </c>
@@ -10732,7 +10716,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
         <v>9</v>
       </c>
@@ -10764,7 +10748,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>10</v>
       </c>
@@ -10796,7 +10780,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
         <v>11</v>
       </c>
@@ -10828,7 +10812,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
         <v>12</v>
       </c>
@@ -10860,7 +10844,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="56" t="n">
         <v>13</v>
       </c>
@@ -10892,7 +10876,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="56" t="n">
         <v>14</v>
       </c>
@@ -10924,7 +10908,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="56" t="n">
         <v>15</v>
       </c>
@@ -10956,7 +10940,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="56" t="n">
         <v>16</v>
       </c>
@@ -10988,39 +10972,39 @@
         <v>713</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="34.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B79" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C79" s="116" t="s">
+      <c r="C79" s="112" t="s">
         <v>714</v>
       </c>
-      <c r="D79" s="116" t="s">
+      <c r="D79" s="112" t="s">
         <v>715</v>
       </c>
-      <c r="E79" s="116" t="s">
+      <c r="E79" s="112" t="s">
         <v>714</v>
       </c>
-      <c r="F79" s="116" t="s">
+      <c r="F79" s="112" t="s">
         <v>716</v>
       </c>
-      <c r="G79" s="116" t="s">
+      <c r="G79" s="112" t="s">
         <v>717</v>
       </c>
-      <c r="H79" s="116" t="s">
+      <c r="H79" s="112" t="s">
         <v>718</v>
       </c>
-      <c r="I79" s="116" t="s">
+      <c r="I79" s="112" t="s">
         <v>719</v>
       </c>
-      <c r="J79" s="116" t="s">
+      <c r="J79" s="112" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="31.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="56" t="n">
         <v>18</v>
       </c>
@@ -11052,7 +11036,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="56" t="n">
         <v>19</v>
       </c>
@@ -11084,7 +11068,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="45.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="56" t="n">
         <v>20</v>
       </c>

--- a/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="577">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -549,6 +549,9 @@
     <t xml:space="preserve">Heartbleed</t>
   </si>
   <si>
+    <t xml:space="preserve">AUC-ROC</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.992326 ± 0.000240</t>
   </si>
   <si>
@@ -570,6 +573,9 @@
     <t xml:space="preserve">0.974495 ± 0.000803</t>
   </si>
   <si>
+    <t xml:space="preserve">0.996422 ± 0.000287</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.480807 ± 0.000607</t>
   </si>
   <si>
@@ -591,6 +597,9 @@
     <t xml:space="preserve">0.335315 ± 0.000921</t>
   </si>
   <si>
+    <t xml:space="preserve">0.864660 ± 0.001599</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.979422 ± 0.001286</t>
   </si>
   <si>
@@ -612,6 +621,9 @@
     <t xml:space="preserve">0.931971 ± 0.005098</t>
   </si>
   <si>
+    <t xml:space="preserve">0.997793 ± 0.000228</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.960407 ± 0.001027</t>
   </si>
   <si>
@@ -630,6 +642,9 @@
     <t xml:space="preserve">0.957595 ± 0.001099</t>
   </si>
   <si>
+    <t xml:space="preserve">0.993453 ± 0.000476 </t>
+  </si>
+  <si>
     <t xml:space="preserve">0.659407 ± 0.002899</t>
   </si>
   <si>
@@ -645,16 +660,7 @@
     <t xml:space="preserve">0.638208 ± 0.002932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871133 ± 0.001441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887064 ± 0.003622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851962 ± 0.002301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.865160 ± 0.001498</t>
+    <t xml:space="preserve">0.945022 ± 0.000729 </t>
   </si>
   <si>
     <t xml:space="preserve">0.922893 ± 0.004223</t>
@@ -669,6 +675,9 @@
     <t xml:space="preserve">0.917796 ± 0.004422 </t>
   </si>
   <si>
+    <t xml:space="preserve">0.994686 ± 0.000510</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.966813 ± 0.000860</t>
   </si>
   <si>
@@ -681,6 +690,9 @@
     <t xml:space="preserve">0.964451 ± 0.000920</t>
   </si>
   <si>
+    <t xml:space="preserve">0.995000 ± 0.000217</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.719947 ± 0.002086 </t>
   </si>
   <si>
@@ -696,22 +708,7 @@
     <t xml:space="preserve">0.703450 ± 0.002188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904787 ± 0.001190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926574 ± 0.001288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889006 ± 0.001355 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926574 ± 0.001288 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889006 ± 0.001355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901142 ± 0.001261</t>
+    <t xml:space="preserve">0.958805 ± 0.000648</t>
   </si>
   <si>
     <t xml:space="preserve">0.935973 ± 0.002390 </t>
@@ -729,6 +726,9 @@
     <t xml:space="preserve">0.932078 ± 0.002491</t>
   </si>
   <si>
+    <t xml:space="preserve">0.995889 ± 0.000173</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.991281 ± 0.000450 </t>
   </si>
   <si>
@@ -753,6 +753,9 @@
     <t xml:space="preserve">0.990659 ± 0.000481</t>
   </si>
   <si>
+    <t xml:space="preserve">0.997928 ± 0.000177</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.671528 ± 0.002847</t>
   </si>
   <si>
@@ -774,25 +777,7 @@
     <t xml:space="preserve">0.651515 ± 0.003038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.900685 ± 0.001256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.908517 ± 0.001641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891683 ± 0.001449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897662 ± 0.001776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881641 ± 0.001442 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.869672 ± 0.001690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894533 ± 0.001357</t>
+    <t xml:space="preserve">0.952099 ± 0.000449</t>
   </si>
   <si>
     <t xml:space="preserve">0.953238 ± 0.004658</t>
@@ -816,6 +801,9 @@
     <t xml:space="preserve">0.950052 ± 0.004978</t>
   </si>
   <si>
+    <t xml:space="preserve">0.997745 ± 0.000353</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.996580 ± 0.000351</t>
   </si>
   <si>
@@ -837,6 +825,9 @@
     <t xml:space="preserve">0.996330 ± 0.000377</t>
   </si>
   <si>
+    <t xml:space="preserve">0.998706 ± 0.000118</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.690374 ± 0.003137</t>
   </si>
   <si>
@@ -858,28 +849,7 @@
     <t xml:space="preserve">0.670670 ± 0.003781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.935121 ± 0.001009 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946633 ± 0.000976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.935121 ± 0.001009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927735 ± 0.001414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934417 ± 0.001642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914862 ± 0.001313 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903830 ± 0.001878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931530 ± 0.001059</t>
+    <t xml:space="preserve">0.963132 ± 0.000670 </t>
   </si>
   <si>
     <t xml:space="preserve">0.966743 ± 0.001533</t>
@@ -924,6 +894,9 @@
     <t xml:space="preserve">0.976482</t>
   </si>
   <si>
+    <t xml:space="preserve">0.996627</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.481399</t>
   </si>
   <si>
@@ -945,6 +918,9 @@
     <t xml:space="preserve">0.335471</t>
   </si>
   <si>
+    <t xml:space="preserve">0.865633</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.977523</t>
   </si>
   <si>
@@ -966,6 +942,9 @@
     <t xml:space="preserve">0.926978</t>
   </si>
   <si>
+    <t xml:space="preserve">0.997408</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.934356</t>
   </si>
   <si>
@@ -987,6 +966,9 @@
     <t xml:space="preserve">0.827932</t>
   </si>
   <si>
+    <t xml:space="preserve">0.983358</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.492500</t>
   </si>
   <si>
@@ -1008,25 +990,7 @@
     <t xml:space="preserve">0.383232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.732083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.847500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556093</t>
+    <t xml:space="preserve">0.876308</t>
   </si>
   <si>
     <t xml:space="preserve">0.832865</t>
@@ -1050,6 +1014,9 @@
     <t xml:space="preserve">0.664453</t>
   </si>
   <si>
+    <t xml:space="preserve">0.988178</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.171816</t>
   </si>
   <si>
@@ -1071,6 +1038,9 @@
     <t xml:space="preserve">0.234454</t>
   </si>
   <si>
+    <t xml:space="preserve">0.582715</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.115204</t>
   </si>
   <si>
@@ -1092,25 +1062,7 @@
     <t xml:space="preserve">0.021136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.209884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.223396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.202151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.211025</t>
+    <t xml:space="preserve">0.348923</t>
   </si>
   <si>
     <t xml:space="preserve">0.166481</t>
@@ -1134,6 +1086,9 @@
     <t xml:space="preserve">0.198667</t>
   </si>
   <si>
+    <t xml:space="preserve">0.603053</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.941001</t>
   </si>
   <si>
@@ -1155,6 +1110,9 @@
     <t xml:space="preserve">0.841194</t>
   </si>
   <si>
+    <t xml:space="preserve">0.983252</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.491957</t>
   </si>
   <si>
@@ -1176,25 +1134,7 @@
     <t xml:space="preserve">0.378679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.847445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550370</t>
+    <t xml:space="preserve">0.890447</t>
   </si>
   <si>
     <t xml:space="preserve">0.890485</t>
@@ -1218,6 +1158,9 @@
     <t xml:space="preserve">0.744371</t>
   </si>
   <si>
+    <t xml:space="preserve">0.990532</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.171067</t>
   </si>
   <si>
@@ -1239,6 +1182,9 @@
     <t xml:space="preserve">0.234380</t>
   </si>
   <si>
+    <t xml:space="preserve">0.532977</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.113861</t>
   </si>
   <si>
@@ -1260,25 +1206,7 @@
     <t xml:space="preserve">0.015257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.211850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.216263</t>
+    <t xml:space="preserve">0.363976</t>
   </si>
   <si>
     <t xml:space="preserve">0.177315</t>
@@ -1739,10 +1667,7 @@
     <t xml:space="preserve">0.995839 ± 0.000130</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995868 ± 0.000121 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995841 ± 0.000128 </t>
+    <t xml:space="preserve">0.995841 ± 0.000128</t>
   </si>
   <si>
     <t xml:space="preserve">0.898896 ± 0.022358</t>
@@ -1754,18 +1679,18 @@
     <t xml:space="preserve">0.895331 ± 0.011207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.990731 ± 0.000273 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514280 ± 0.022613 </t>
+    <t xml:space="preserve">0.990731 ± 0.000273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998705 ± 0.000082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514280 ± 0.022613</t>
   </si>
   <si>
     <t xml:space="preserve">0.888197 ± 0.025505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514280 ± 0.022613</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.625090 ± 0.024717</t>
   </si>
   <si>
@@ -1781,13 +1706,16 @@
     <t xml:space="preserve">0.351127 ± 0.024124</t>
   </si>
   <si>
+    <t xml:space="preserve">0.908154 ± 0.003732</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.987224 ± 0.002190</t>
   </si>
   <si>
     <t xml:space="preserve">0.985747 ± 0.001933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.985792 ± 0.002183</t>
+    <t xml:space="preserve">0.985792 ± 0.002183 </t>
   </si>
   <si>
     <t xml:space="preserve">0.707422 ± 0.030732</t>
@@ -1802,6 +1730,9 @@
     <t xml:space="preserve">0.971206 ± 0.004882</t>
   </si>
   <si>
+    <t xml:space="preserve">0.997978 ± 0.000554</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.968107 ± 0.000838</t>
   </si>
   <si>
@@ -1814,52 +1745,61 @@
     <t xml:space="preserve">0.965659 ± 0.000902 </t>
   </si>
   <si>
+    <t xml:space="preserve">0.994845 ± 0.000122</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.514057 ± 0.009289</t>
   </si>
   <si>
+    <t xml:space="preserve">0.500307 ± 0.021506 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473830 ± 0.016348</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.500307 ± 0.021506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473830 ± 0.016348</t>
+    <t xml:space="preserve">0.514057 ± 0.009289 </t>
   </si>
   <si>
     <t xml:space="preserve">0.484033 ± 0.009249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814750 ± 0.001998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855801 ± 0.003429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.794574 ± 0.001846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805856 ± 0.002186</t>
+    <t xml:space="preserve">0.897853 ± 0.001551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854229 ± 0.010053 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883069 ± 0.009629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834791 ± 0.009221</t>
   </si>
   <si>
     <t xml:space="preserve">0.854229 ± 0.010053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.883069 ± 0.009629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834791 ± 0.009221</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.847535 ± 0.010621</t>
   </si>
   <si>
+    <t xml:space="preserve">0.986676 ± 0.000757</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.974014 ± 0.000831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973910 ± 0.000830</t>
+    <t xml:space="preserve">0.973910 ± 0.000830 </t>
   </si>
   <si>
     <t xml:space="preserve">0.973949 ± 0.000832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.972018 ± 0.000894</t>
+    <t xml:space="preserve">0.972018 ± 0.000894 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996127 ± 0.000425</t>
   </si>
   <si>
     <t xml:space="preserve">0.548421 ± 0.038528</t>
@@ -1868,210 +1808,6 @@
     <t xml:space="preserve">0.580192 ± 0.054245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531145 ± 0.049220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520565 ± 0.042029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.770086 ± 0.011077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799011 ± 0.039992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738468 ± 0.021009 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738468 ± 0.021009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761543 ± 0.011257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812079 ± 0.001702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867410 ± 0.014507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798277 ± 0.008138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804013 ± 0.004247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989538 ± 0.000804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989512 ± 0.000808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989494 ± 0.000803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989000 ± 0.000882 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989072 ± 0.000865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989006 ± 0.000869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988731 ± 0.000867 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544799 ± 0.019849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538258 ± 0.022955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516132 ± 0.020815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530277 ± 0.021688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543483 ± 0.019082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511733 ± 0.019666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513974 ± 0.021501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829854 ± 0.002401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850454 ± 0.002953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828617 ± 0.002553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838479 ± 0.002937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821283 ± 0.002277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818002 ± 0.002488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818751 ± 0.002578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870108 ± 0.007763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889796 ± 0.010851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860209 ± 0.009683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880297 ± 0.013872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857686 ± 0.008532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844756 ± 0.012759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862313 ± 0.008312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994210 ± 0.000283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994205 ± 0.000290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.994200 ± 0.000285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993844 ± 0.000324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993636 ± 0.000448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993731 ± 0.000384 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.993760 ± 0.000306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505476 ± 0.018710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533130 ± 0.015803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480020 ± 0.019237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517856 ± 0.015697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492066 ± 0.017530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466882 ± 0.018453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473179 ± 0.019621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810274 ± 0.001528 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838628 ± 0.000987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810274 ± 0.001528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805702 ± 0.001476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828687 ± 0.000902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802993 ± 0.001524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796573 ± 0.001371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799473 ± 0.001612 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.844365 ± 0.002965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882828 ± 0.002619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837768 ± 0.003225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870813 ± 0.002574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836126 ± 0.003035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827704 ± 0.003207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.836279 ± 0.003146</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.996078</t>
   </si>
   <si>
@@ -2093,6 +1829,9 @@
     <t xml:space="preserve">0.991202</t>
   </si>
   <si>
+    <t xml:space="preserve">0.998864</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.520292</t>
   </si>
   <si>
@@ -2114,6 +1853,9 @@
     <t xml:space="preserve">0.355227</t>
   </si>
   <si>
+    <t xml:space="preserve">0.904174</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.988611</t>
   </si>
   <si>
@@ -2135,6 +1877,9 @@
     <t xml:space="preserve">0.974311</t>
   </si>
   <si>
+    <t xml:space="preserve">0.998588</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.954573</t>
   </si>
   <si>
@@ -2156,6 +1901,9 @@
     <t xml:space="preserve">0.908297</t>
   </si>
   <si>
+    <t xml:space="preserve">0.989250</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.552378</t>
   </si>
   <si>
@@ -2177,25 +1925,7 @@
     <t xml:space="preserve">0.355979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.707141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.750818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595358</t>
+    <t xml:space="preserve">0.874995</t>
   </si>
   <si>
     <t xml:space="preserve">0.761002</t>
@@ -2219,6 +1949,9 @@
     <t xml:space="preserve">0.648468</t>
   </si>
   <si>
+    <t xml:space="preserve">0.969081</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.251341</t>
   </si>
   <si>
@@ -2240,244 +1973,15 @@
     <t xml:space="preserve">0.257268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.211344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.192183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.201434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.204746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.202750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.957560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.888656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.248046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.928609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.241613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.223220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.215866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.180215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.248695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.212510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.228247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.195029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.205379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.187273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.195647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.648311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.198577</t>
+    <t xml:space="preserve">0.629703</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2790,7 +2294,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3099,6 +2603,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3239,8 +2747,8 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3928,7 +3436,7 @@
       <c r="E34" s="34"/>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
         <v>58</v>
       </c>
@@ -3978,7 +3486,7 @@
       <c r="E38" s="34"/>
       <c r="F38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
         <v>64</v>
       </c>
@@ -4023,8 +3531,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5035,7 +4543,7 @@
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
         <v>17</v>
       </c>
@@ -5071,7 +4579,7 @@
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="56" t="n">
         <v>19</v>
       </c>
@@ -5089,7 +4597,7 @@
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="56" t="n">
         <v>20</v>
       </c>
@@ -5599,7 +5107,7 @@
       <c r="I78" s="42"/>
       <c r="J78" s="42"/>
     </row>
-    <row r="79" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="56" t="n">
         <v>17</v>
       </c>
@@ -5631,7 +5139,7 @@
       <c r="I80" s="42"/>
       <c r="J80" s="42"/>
     </row>
-    <row r="81" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="56" t="n">
         <v>19</v>
       </c>
@@ -5647,7 +5155,7 @@
       <c r="I81" s="42"/>
       <c r="J81" s="42"/>
     </row>
-    <row r="82" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="56" t="n">
         <v>20</v>
       </c>
@@ -5668,8 +5176,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6271,8 +5779,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6282,11 +5790,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD84"/>
+  <dimension ref="A1:XFD74"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="42" width="29.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="42" width="45.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="42" width="45.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="42" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="42" width="21.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="42" width="19.74"/>
@@ -6295,11 +5803,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="42" width="21.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="42" width="21.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="35" width="14.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="35" width="19.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="35" width="15.57"/>
   </cols>
   <sheetData>
-    <row r="1" s="69" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="69" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
@@ -6331,7 +5839,7 @@
       <c r="XFC1" s="1"/>
       <c r="XFD1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="70" t="s">
         <v>75</v>
       </c>
@@ -6362,7 +5870,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="70" t="s">
         <v>156</v>
       </c>
@@ -6393,7 +5901,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="70" t="s">
         <v>157</v>
       </c>
@@ -6424,7 +5932,7 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="70" t="s">
         <v>158</v>
       </c>
@@ -6455,7 +5963,7 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="70" t="s">
         <v>159</v>
       </c>
@@ -6486,7 +5994,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="70" t="s">
         <v>160</v>
       </c>
@@ -6517,7 +6025,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="70" t="s">
         <v>161</v>
       </c>
@@ -6548,7 +6056,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="70" t="s">
         <v>162</v>
       </c>
@@ -6579,7 +6087,7 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="70" t="s">
         <v>163</v>
       </c>
@@ -6610,7 +6118,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="70" t="s">
         <v>79</v>
       </c>
@@ -6641,7 +6149,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="70" t="s">
         <v>164</v>
       </c>
@@ -6672,7 +6180,7 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="70" t="s">
         <v>165</v>
       </c>
@@ -6703,7 +6211,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="70" t="s">
         <v>166</v>
       </c>
@@ -6734,7 +6242,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="70" t="s">
         <v>167</v>
       </c>
@@ -6765,7 +6273,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="73" t="s">
         <v>168</v>
       </c>
@@ -6796,7 +6304,7 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="42" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>2830743</v>
@@ -6840,7 +6348,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="76" t="s">
         <v>90</v>
       </c>
@@ -6878,7 +6386,7 @@
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L25" s="1"/>
     </row>
-    <row r="26" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="54" t="s">
         <v>91</v>
       </c>
@@ -6909,10 +6417,13 @@
       <c r="J26" s="55" t="s">
         <v>100</v>
       </c>
+      <c r="K26" s="55" t="s">
+        <v>169</v>
+      </c>
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
         <v>1</v>
       </c>
@@ -6920,31 +6431,34 @@
         <v>101</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D27" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="E27" s="42" t="s">
-        <v>169</v>
-      </c>
       <c r="F27" s="42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G27" s="42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H27" s="42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>176</v>
+      </c>
+      <c r="K27" s="77" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
         <v>2</v>
       </c>
@@ -6952,591 +6466,549 @@
         <v>102</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H28" s="42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="29" s="35" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+      <c r="K28" s="77" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="58"/>
-    </row>
-    <row r="30" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="K29" s="77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I30" s="42" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="31" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>199</v>
+      </c>
+      <c r="K30" s="77" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G31" s="42" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H31" s="42" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>205</v>
+      </c>
+      <c r="K31" s="77" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="32" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G32" s="42" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I32" s="42" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>210</v>
+      </c>
+      <c r="K32" s="77" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G33" s="42" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="34" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>215</v>
+      </c>
+      <c r="K33" s="77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G34" s="42" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="I34" s="42" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="35" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>221</v>
+      </c>
+      <c r="K34" s="77" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G35" s="42" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="36" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>227</v>
+      </c>
+      <c r="K35" s="77" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+      <c r="K36" s="77" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="G37" s="42" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="H37" s="42" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="38" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>244</v>
+      </c>
+      <c r="K37" s="77" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="G38" s="42" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="H38" s="42" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="I38" s="42" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="39" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+      <c r="K38" s="77" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="G39" s="42" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="40" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+      <c r="K39" s="77" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="G40" s="42" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="H40" s="42" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="I40" s="42" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="41" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>268</v>
+      </c>
+      <c r="K40" s="77" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="G41" s="42" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="H41" s="42" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="I41" s="42" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="42" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B42" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="E42" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>253</v>
-      </c>
-      <c r="G42" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="H42" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="I42" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="J42" s="42" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B43" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="D43" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="E43" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="F43" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="G43" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="K41" s="77" t="s">
         <v>261</v>
       </c>
-      <c r="H43" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="I43" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="J43" s="42" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="44" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B44" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="E44" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="F44" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="G44" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="H44" s="42" t="s">
-        <v>269</v>
-      </c>
-      <c r="I44" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="J44" s="42" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="45" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B45" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="D45" s="42" t="s">
-        <v>273</v>
-      </c>
-      <c r="E45" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="F45" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="G45" s="42" t="s">
-        <v>276</v>
-      </c>
-      <c r="H45" s="42" t="s">
-        <v>277</v>
-      </c>
-      <c r="I45" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="J45" s="42" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C46" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="D46" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="E46" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="F46" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="G46" s="42" t="s">
-        <v>283</v>
-      </c>
-      <c r="H46" s="42" t="s">
-        <v>284</v>
-      </c>
-      <c r="I46" s="42" t="s">
-        <v>285</v>
-      </c>
-      <c r="J46" s="42" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="47" s="35" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="42" s="35" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="58"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="58"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="58"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="58"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="58"/>
+    </row>
+    <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="57"/>
       <c r="B47" s="57"/>
       <c r="C47" s="57"/>
@@ -7584,720 +7056,564 @@
       <c r="I50" s="57"/>
       <c r="J50" s="58"/>
     </row>
-    <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="58"/>
-    </row>
-    <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="57"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="58"/>
-    </row>
-    <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="57"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="58"/>
-    </row>
-    <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="57"/>
-      <c r="B54" s="57"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="58"/>
-    </row>
-    <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="57"/>
-      <c r="B55" s="57"/>
-      <c r="C55" s="57"/>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="58"/>
-    </row>
-    <row r="64" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="54" t="s">
+    <row r="59" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="B64" s="54" t="s">
+      <c r="B59" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="C64" s="54" t="s">
+      <c r="C59" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="54" t="s">
+      <c r="D59" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="E64" s="54" t="s">
+      <c r="E59" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="F64" s="54" t="s">
+      <c r="F59" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="G64" s="54" t="s">
+      <c r="G59" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="H64" s="54" t="s">
+      <c r="H59" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I64" s="54" t="s">
+      <c r="I59" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="J64" s="55" t="s">
+      <c r="J59" s="55" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" s="55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="D60" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="F60" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="G60" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="H60" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="I60" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="J60" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="K60" s="77" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="D61" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="E61" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="F61" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="G61" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="H61" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="I61" s="42" t="s">
+        <v>290</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="K61" s="77" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="F62" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="G62" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="H62" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="I62" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="J62" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="K62" s="77" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B63" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="D63" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="E63" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="F63" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="G63" s="42" t="s">
+        <v>304</v>
+      </c>
+      <c r="H63" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="I63" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="J63" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="K63" s="77" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B64" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="D64" s="42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E64" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="F64" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="G64" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="H64" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="I64" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>315</v>
+      </c>
+      <c r="K64" s="77" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="D65" s="42" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="E65" s="42" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="F65" s="42" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="G65" s="42" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="H65" s="42" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="I65" s="42" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>323</v>
+      </c>
+      <c r="K65" s="77" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="E66" s="42" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="G66" s="42" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="H66" s="42" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="I66" s="42" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>331</v>
+      </c>
+      <c r="K66" s="77" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
-      <c r="J67" s="58"/>
-    </row>
-    <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="D67" s="42" t="s">
+        <v>334</v>
+      </c>
+      <c r="E67" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="F67" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="H67" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="I67" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="J67" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="K67" s="77" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C68" s="42" t="s">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="E68" s="42" t="s">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="F68" s="42" t="s">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="G68" s="42" t="s">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="H68" s="42" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="I68" s="42" t="s">
-        <v>306</v>
+        <v>346</v>
       </c>
       <c r="J68" s="42" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+      <c r="K68" s="77" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="H69" s="42" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="I69" s="42" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="J69" s="42" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>355</v>
+      </c>
+      <c r="K69" s="77" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="F70" s="42" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
       <c r="G70" s="42" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="H70" s="42" t="s">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="I70" s="42" t="s">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="J70" s="42" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>363</v>
+      </c>
+      <c r="K70" s="77" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C71" s="42" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>323</v>
+        <v>366</v>
       </c>
       <c r="E71" s="42" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="F71" s="42" t="s">
-        <v>324</v>
+        <v>367</v>
       </c>
       <c r="G71" s="42" t="s">
-        <v>325</v>
+        <v>368</v>
       </c>
       <c r="H71" s="42" t="s">
-        <v>326</v>
+        <v>369</v>
       </c>
       <c r="I71" s="42" t="s">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="J71" s="42" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>371</v>
+      </c>
+      <c r="K71" s="77" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="I72" s="42" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+      <c r="K72" s="77" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C73" s="42" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="E73" s="42" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="F73" s="42" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="G73" s="42" t="s">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="H73" s="42" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="I73" s="42" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="J73" s="42" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>387</v>
+      </c>
+      <c r="K73" s="77" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C74" s="42" t="s">
-        <v>343</v>
+        <v>389</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="E74" s="42" t="s">
-        <v>343</v>
+        <v>389</v>
       </c>
       <c r="F74" s="42" t="s">
-        <v>345</v>
+        <v>391</v>
       </c>
       <c r="G74" s="42" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="H74" s="42" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="I74" s="42" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="J74" s="42" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="56" t="n">
-        <v>11</v>
-      </c>
-      <c r="B75" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="D75" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="E75" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="F75" s="42" t="s">
-        <v>352</v>
-      </c>
-      <c r="G75" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="H75" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="I75" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="J75" s="42" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="56" t="n">
-        <v>12</v>
-      </c>
-      <c r="B76" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C76" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="D76" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="E76" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="F76" s="42" t="s">
-        <v>359</v>
-      </c>
-      <c r="G76" s="42" t="s">
-        <v>360</v>
-      </c>
-      <c r="H76" s="42" t="s">
-        <v>361</v>
-      </c>
-      <c r="I76" s="42" t="s">
-        <v>362</v>
-      </c>
-      <c r="J76" s="42" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="56" t="n">
-        <v>13</v>
-      </c>
-      <c r="B77" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C77" s="42" t="s">
-        <v>364</v>
-      </c>
-      <c r="D77" s="42" t="s">
-        <v>365</v>
-      </c>
-      <c r="E77" s="42" t="s">
-        <v>364</v>
-      </c>
-      <c r="F77" s="42" t="s">
-        <v>366</v>
-      </c>
-      <c r="G77" s="42" t="s">
-        <v>367</v>
-      </c>
-      <c r="H77" s="42" t="s">
-        <v>368</v>
-      </c>
-      <c r="I77" s="42" t="s">
-        <v>369</v>
-      </c>
-      <c r="J77" s="42" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="56" t="n">
-        <v>14</v>
-      </c>
-      <c r="B78" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C78" s="42" t="s">
-        <v>371</v>
-      </c>
-      <c r="D78" s="42" t="s">
-        <v>372</v>
-      </c>
-      <c r="E78" s="42" t="s">
-        <v>371</v>
-      </c>
-      <c r="F78" s="42" t="s">
-        <v>373</v>
-      </c>
-      <c r="G78" s="42" t="s">
-        <v>374</v>
-      </c>
-      <c r="H78" s="42" t="s">
-        <v>375</v>
-      </c>
-      <c r="I78" s="42" t="s">
-        <v>376</v>
-      </c>
-      <c r="J78" s="42" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="56" t="n">
-        <v>15</v>
-      </c>
-      <c r="B79" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C79" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="D79" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="E79" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="F79" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="K74" s="77" t="s">
         <v>380</v>
-      </c>
-      <c r="G79" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="H79" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="I79" s="42" t="s">
-        <v>383</v>
-      </c>
-      <c r="J79" s="42" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B80" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C80" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="D80" s="42" t="s">
-        <v>386</v>
-      </c>
-      <c r="E80" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="F80" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="G80" s="42" t="s">
-        <v>388</v>
-      </c>
-      <c r="H80" s="42" t="s">
-        <v>389</v>
-      </c>
-      <c r="I80" s="42" t="s">
-        <v>390</v>
-      </c>
-      <c r="J80" s="42" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B81" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C81" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="D81" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="E81" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="F81" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="G81" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="H81" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="I81" s="42" t="s">
-        <v>397</v>
-      </c>
-      <c r="J81" s="42" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B82" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C82" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="D82" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="E82" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="F82" s="42" t="s">
-        <v>401</v>
-      </c>
-      <c r="G82" s="42" t="s">
-        <v>402</v>
-      </c>
-      <c r="H82" s="42" t="s">
-        <v>403</v>
-      </c>
-      <c r="I82" s="42" t="s">
-        <v>404</v>
-      </c>
-      <c r="J82" s="42" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B83" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D83" s="42" t="s">
-        <v>407</v>
-      </c>
-      <c r="E83" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="F83" s="42" t="s">
-        <v>408</v>
-      </c>
-      <c r="G83" s="42" t="s">
-        <v>409</v>
-      </c>
-      <c r="H83" s="42" t="s">
-        <v>410</v>
-      </c>
-      <c r="I83" s="42" t="s">
-        <v>411</v>
-      </c>
-      <c r="J83" s="42" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B84" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C84" s="42" t="s">
-        <v>413</v>
-      </c>
-      <c r="D84" s="42" t="s">
-        <v>414</v>
-      </c>
-      <c r="E84" s="42" t="s">
-        <v>413</v>
-      </c>
-      <c r="F84" s="42" t="s">
-        <v>415</v>
-      </c>
-      <c r="G84" s="42" t="s">
-        <v>416</v>
-      </c>
-      <c r="H84" s="42" t="s">
-        <v>417</v>
-      </c>
-      <c r="I84" s="42" t="s">
-        <v>418</v>
-      </c>
-      <c r="J84" s="42" t="s">
-        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -8305,8 +7621,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -8319,7 +7635,7 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="77" width="36.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="78" width="36.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="90.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="77.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="65.07"/>
@@ -8328,23 +7644,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="E1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="79" t="s">
-        <v>420</v>
+      <c r="F1" s="80" t="s">
+        <v>396</v>
       </c>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
@@ -8353,18 +7669,18 @@
       <c r="K1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81" t="s">
-        <v>421</v>
-      </c>
-      <c r="D2" s="81" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="D2" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="81" t="s">
-        <v>422</v>
-      </c>
-      <c r="F2" s="82"/>
+      <c r="E2" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="F2" s="83"/>
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
@@ -8372,20 +7688,20 @@
       <c r="K2" s="61"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81" t="s">
-        <v>423</v>
-      </c>
-      <c r="C3" s="83" t="s">
-        <v>424</v>
-      </c>
-      <c r="D3" s="81" t="s">
+      <c r="A3" s="81"/>
+      <c r="B3" s="82" t="s">
+        <v>399</v>
+      </c>
+      <c r="C3" s="84" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="81" t="s">
-        <v>422</v>
-      </c>
-      <c r="F3" s="82"/>
+      <c r="E3" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="F3" s="83"/>
       <c r="G3" s="61"/>
       <c r="H3" s="61"/>
       <c r="I3" s="61"/>
@@ -8393,20 +7709,20 @@
       <c r="K3" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81" t="s">
-        <v>425</v>
-      </c>
-      <c r="C4" s="83" t="s">
-        <v>426</v>
-      </c>
-      <c r="D4" s="81" t="s">
+      <c r="A4" s="81"/>
+      <c r="B4" s="82" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="84" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="81" t="s">
-        <v>427</v>
-      </c>
-      <c r="F4" s="82"/>
+      <c r="E4" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="F4" s="83"/>
       <c r="G4" s="61"/>
       <c r="H4" s="61"/>
       <c r="I4" s="61"/>
@@ -8414,20 +7730,20 @@
       <c r="K4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81" t="s">
-        <v>428</v>
-      </c>
-      <c r="C5" s="83" t="s">
-        <v>424</v>
-      </c>
-      <c r="D5" s="81" t="s">
-        <v>427</v>
-      </c>
-      <c r="E5" s="81" t="s">
-        <v>422</v>
-      </c>
-      <c r="F5" s="82"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="82" t="s">
+        <v>404</v>
+      </c>
+      <c r="C5" s="84" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E5" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="F5" s="83"/>
       <c r="G5" s="61"/>
       <c r="H5" s="61"/>
       <c r="I5" s="61"/>
@@ -8435,20 +7751,20 @@
       <c r="K5" s="61"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81" t="s">
-        <v>429</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>430</v>
-      </c>
-      <c r="D6" s="81" t="s">
-        <v>427</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>431</v>
-      </c>
-      <c r="F6" s="82"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="82" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" s="84" t="s">
+        <v>406</v>
+      </c>
+      <c r="D6" s="82" t="s">
+        <v>403</v>
+      </c>
+      <c r="E6" s="84" t="s">
+        <v>407</v>
+      </c>
+      <c r="F6" s="83"/>
       <c r="G6" s="61"/>
       <c r="H6" s="61"/>
       <c r="I6" s="61"/>
@@ -8456,42 +7772,42 @@
       <c r="K6" s="61"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="80" t="s">
-        <v>432</v>
-      </c>
-      <c r="B7" s="84" t="s">
-        <v>433</v>
-      </c>
-      <c r="C7" s="85" t="s">
-        <v>434</v>
-      </c>
-      <c r="D7" s="85" t="s">
-        <v>435</v>
-      </c>
-      <c r="E7" s="85" t="s">
-        <v>436</v>
-      </c>
-      <c r="F7" s="82"/>
+      <c r="A7" s="81" t="s">
+        <v>408</v>
+      </c>
+      <c r="B7" s="85" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="86" t="s">
+        <v>412</v>
+      </c>
+      <c r="F7" s="83"/>
       <c r="G7" s="62"/>
       <c r="H7" s="62"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="84" t="s">
-        <v>437</v>
-      </c>
-      <c r="C8" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D8" s="85" t="s">
-        <v>435</v>
-      </c>
-      <c r="E8" s="85" t="s">
-        <v>439</v>
-      </c>
-      <c r="F8" s="82"/>
+      <c r="B8" s="85" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>414</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>411</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>415</v>
+      </c>
+      <c r="F8" s="83"/>
       <c r="G8" s="61"/>
       <c r="H8" s="61"/>
       <c r="I8" s="61"/>
@@ -8499,22 +7815,22 @@
       <c r="K8" s="61"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="84" t="s">
-        <v>440</v>
-      </c>
-      <c r="C9" s="85" t="s">
-        <v>434</v>
-      </c>
-      <c r="D9" s="85" t="s">
-        <v>439</v>
-      </c>
-      <c r="E9" s="85" t="s">
-        <v>441</v>
-      </c>
-      <c r="F9" s="82"/>
+      <c r="B9" s="85" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>415</v>
+      </c>
+      <c r="E9" s="86" t="s">
+        <v>417</v>
+      </c>
+      <c r="F9" s="83"/>
       <c r="G9" s="61"/>
       <c r="H9" s="61"/>
       <c r="I9" s="61"/>
@@ -8522,20 +7838,20 @@
       <c r="K9" s="61"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="87" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" s="88" t="s">
-        <v>443</v>
-      </c>
-      <c r="D10" s="88" t="s">
-        <v>435</v>
-      </c>
-      <c r="E10" s="88" t="s">
-        <v>444</v>
+      <c r="B10" s="88" t="s">
+        <v>418</v>
+      </c>
+      <c r="C10" s="89" t="s">
+        <v>419</v>
+      </c>
+      <c r="D10" s="89" t="s">
+        <v>411</v>
+      </c>
+      <c r="E10" s="89" t="s">
+        <v>420</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="61"/>
@@ -8545,22 +7861,22 @@
       <c r="K10" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="89" t="s">
+      <c r="A11" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="90" t="s">
-        <v>445</v>
-      </c>
-      <c r="C11" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="D11" s="91" t="s">
-        <v>444</v>
-      </c>
-      <c r="E11" s="91" t="s">
-        <v>446</v>
-      </c>
-      <c r="F11" s="92"/>
+      <c r="B11" s="91" t="s">
+        <v>421</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>410</v>
+      </c>
+      <c r="D11" s="92" t="s">
+        <v>420</v>
+      </c>
+      <c r="E11" s="92" t="s">
+        <v>422</v>
+      </c>
+      <c r="F11" s="93"/>
       <c r="G11" s="61"/>
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
@@ -8568,21 +7884,21 @@
       <c r="K11" s="61"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="91" t="s">
-        <v>447</v>
-      </c>
-      <c r="C12" s="91" t="s">
-        <v>448</v>
-      </c>
-      <c r="D12" s="91" t="s">
-        <v>449</v>
-      </c>
-      <c r="E12" s="91"/>
-      <c r="F12" s="93" t="s">
-        <v>450</v>
+      <c r="B12" s="92" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="92" t="s">
+        <v>424</v>
+      </c>
+      <c r="D12" s="92" t="s">
+        <v>425</v>
+      </c>
+      <c r="E12" s="92"/>
+      <c r="F12" s="94" t="s">
+        <v>426</v>
       </c>
       <c r="G12" s="61"/>
       <c r="H12" s="61"/>
@@ -8591,20 +7907,20 @@
       <c r="K12" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="91" t="s">
-        <v>451</v>
-      </c>
-      <c r="C13" s="91" t="s">
-        <v>452</v>
-      </c>
-      <c r="D13" s="91" t="s">
-        <v>453</v>
-      </c>
-      <c r="E13" s="91"/>
-      <c r="F13" s="93"/>
+      <c r="B13" s="92" t="s">
+        <v>427</v>
+      </c>
+      <c r="C13" s="92" t="s">
+        <v>428</v>
+      </c>
+      <c r="D13" s="92" t="s">
+        <v>429</v>
+      </c>
+      <c r="E13" s="92"/>
+      <c r="F13" s="94"/>
       <c r="G13" s="61"/>
       <c r="H13" s="61"/>
       <c r="I13" s="61"/>
@@ -8612,12 +7928,12 @@
       <c r="K13" s="61"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="96"/>
+      <c r="A14" s="95"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="97"/>
       <c r="G14" s="61"/>
       <c r="H14" s="61"/>
       <c r="I14" s="61"/>
@@ -8625,12 +7941,12 @@
       <c r="K14" s="61"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="97"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="99"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="100"/>
       <c r="G15" s="61"/>
       <c r="H15" s="61"/>
       <c r="I15" s="61"/>
@@ -8638,22 +7954,22 @@
       <c r="K15" s="61"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="88" t="s">
-        <v>454</v>
-      </c>
-      <c r="C16" s="88" t="s">
-        <v>438</v>
-      </c>
-      <c r="D16" s="88" t="s">
-        <v>455</v>
-      </c>
-      <c r="E16" s="88" t="s">
-        <v>456</v>
-      </c>
-      <c r="F16" s="100"/>
+      <c r="B16" s="89" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" s="89" t="s">
+        <v>414</v>
+      </c>
+      <c r="D16" s="89" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="89" t="s">
+        <v>432</v>
+      </c>
+      <c r="F16" s="101"/>
       <c r="G16" s="61"/>
       <c r="H16" s="61"/>
       <c r="I16" s="61"/>
@@ -8661,22 +7977,22 @@
       <c r="K16" s="61"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="91" t="s">
-        <v>457</v>
-      </c>
-      <c r="C17" s="91" t="s">
+      <c r="B17" s="92" t="s">
+        <v>433</v>
+      </c>
+      <c r="C17" s="92" t="s">
+        <v>410</v>
+      </c>
+      <c r="D17" s="92" t="s">
+        <v>432</v>
+      </c>
+      <c r="E17" s="92" t="s">
         <v>434</v>
       </c>
-      <c r="D17" s="91" t="s">
-        <v>456</v>
-      </c>
-      <c r="E17" s="91" t="s">
-        <v>458</v>
-      </c>
-      <c r="F17" s="93"/>
+      <c r="F17" s="94"/>
       <c r="G17" s="61"/>
       <c r="H17" s="61"/>
       <c r="I17" s="61"/>
@@ -8684,21 +8000,21 @@
       <c r="K17" s="61"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="101" t="s">
+      <c r="A18" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="102" t="s">
-        <v>459</v>
-      </c>
-      <c r="C18" s="102" t="s">
-        <v>448</v>
-      </c>
-      <c r="D18" s="102" t="s">
-        <v>460</v>
-      </c>
-      <c r="E18" s="102"/>
-      <c r="F18" s="103" t="s">
-        <v>461</v>
+      <c r="B18" s="103" t="s">
+        <v>435</v>
+      </c>
+      <c r="C18" s="103" t="s">
+        <v>424</v>
+      </c>
+      <c r="D18" s="103" t="s">
+        <v>436</v>
+      </c>
+      <c r="E18" s="103"/>
+      <c r="F18" s="104" t="s">
+        <v>437</v>
       </c>
       <c r="G18" s="61"/>
       <c r="H18" s="61"/>
@@ -8707,20 +8023,20 @@
       <c r="K18" s="61"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="94" t="s">
+      <c r="A19" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="95" t="s">
-        <v>462</v>
-      </c>
-      <c r="C19" s="95" t="s">
-        <v>452</v>
-      </c>
-      <c r="D19" s="95" t="s">
-        <v>463</v>
-      </c>
-      <c r="E19" s="95"/>
-      <c r="F19" s="96"/>
+      <c r="B19" s="96" t="s">
+        <v>438</v>
+      </c>
+      <c r="C19" s="96" t="s">
+        <v>428</v>
+      </c>
+      <c r="D19" s="96" t="s">
+        <v>439</v>
+      </c>
+      <c r="E19" s="96"/>
+      <c r="F19" s="97"/>
       <c r="G19" s="61"/>
       <c r="H19" s="61"/>
       <c r="I19" s="61"/>
@@ -8728,12 +8044,12 @@
       <c r="K19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="94"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="96"/>
+      <c r="A20" s="95"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="97"/>
       <c r="G20" s="61"/>
       <c r="H20" s="61"/>
       <c r="I20" s="61"/>
@@ -8741,12 +8057,12 @@
       <c r="K20" s="61"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="104"/>
-      <c r="B21" s="105"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="106"/>
+      <c r="A21" s="105"/>
+      <c r="B21" s="106"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="107"/>
       <c r="G21" s="61"/>
       <c r="H21" s="61"/>
       <c r="I21" s="61"/>
@@ -8754,20 +8070,20 @@
       <c r="K21" s="61"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="87" t="s">
-        <v>464</v>
-      </c>
-      <c r="C22" s="88" t="s">
-        <v>443</v>
-      </c>
-      <c r="D22" s="88" t="s">
-        <v>435</v>
-      </c>
-      <c r="E22" s="88" t="s">
-        <v>465</v>
+      <c r="B22" s="88" t="s">
+        <v>440</v>
+      </c>
+      <c r="C22" s="89" t="s">
+        <v>419</v>
+      </c>
+      <c r="D22" s="89" t="s">
+        <v>411</v>
+      </c>
+      <c r="E22" s="89" t="s">
+        <v>441</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="61"/>
@@ -8777,22 +8093,22 @@
       <c r="K22" s="61"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="89" t="s">
+      <c r="A23" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="90" t="s">
-        <v>466</v>
-      </c>
-      <c r="C23" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="D23" s="91" t="s">
-        <v>465</v>
-      </c>
-      <c r="E23" s="91" t="s">
-        <v>467</v>
-      </c>
-      <c r="F23" s="92"/>
+      <c r="B23" s="91" t="s">
+        <v>442</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>410</v>
+      </c>
+      <c r="D23" s="92" t="s">
+        <v>441</v>
+      </c>
+      <c r="E23" s="92" t="s">
+        <v>443</v>
+      </c>
+      <c r="F23" s="93"/>
       <c r="G23" s="61"/>
       <c r="H23" s="61"/>
       <c r="I23" s="61"/>
@@ -8800,21 +8116,21 @@
       <c r="K23" s="61"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="101" t="s">
+      <c r="A24" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="102" t="s">
-        <v>468</v>
-      </c>
-      <c r="C24" s="102" t="s">
-        <v>448</v>
-      </c>
-      <c r="D24" s="102" t="s">
-        <v>469</v>
-      </c>
-      <c r="E24" s="102"/>
-      <c r="F24" s="103" t="s">
-        <v>470</v>
+      <c r="B24" s="103" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="103" t="s">
+        <v>424</v>
+      </c>
+      <c r="D24" s="103" t="s">
+        <v>445</v>
+      </c>
+      <c r="E24" s="103"/>
+      <c r="F24" s="104" t="s">
+        <v>446</v>
       </c>
       <c r="G24" s="61"/>
       <c r="H24" s="61"/>
@@ -8823,20 +8139,20 @@
       <c r="K24" s="61"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="95" t="s">
-        <v>471</v>
-      </c>
-      <c r="C25" s="95" t="s">
-        <v>452</v>
-      </c>
-      <c r="D25" s="95" t="s">
-        <v>472</v>
-      </c>
-      <c r="E25" s="95"/>
-      <c r="F25" s="96"/>
+      <c r="B25" s="96" t="s">
+        <v>447</v>
+      </c>
+      <c r="C25" s="96" t="s">
+        <v>428</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>448</v>
+      </c>
+      <c r="E25" s="96"/>
+      <c r="F25" s="97"/>
       <c r="G25" s="61"/>
       <c r="H25" s="61"/>
       <c r="I25" s="61"/>
@@ -8844,12 +8160,12 @@
       <c r="K25" s="61"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="94"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="96"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="97"/>
       <c r="G26" s="61"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -8857,12 +8173,12 @@
       <c r="K26" s="61"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="97"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="99"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="100"/>
       <c r="G27" s="61"/>
       <c r="H27" s="61"/>
       <c r="I27" s="61"/>
@@ -8870,22 +8186,22 @@
       <c r="K27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="86" t="s">
+      <c r="A28" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="88" t="s">
-        <v>473</v>
-      </c>
-      <c r="C28" s="88" t="s">
-        <v>438</v>
-      </c>
-      <c r="D28" s="88" t="s">
-        <v>474</v>
-      </c>
-      <c r="E28" s="88" t="s">
-        <v>475</v>
-      </c>
-      <c r="F28" s="100"/>
+      <c r="B28" s="89" t="s">
+        <v>449</v>
+      </c>
+      <c r="C28" s="89" t="s">
+        <v>414</v>
+      </c>
+      <c r="D28" s="89" t="s">
+        <v>450</v>
+      </c>
+      <c r="E28" s="89" t="s">
+        <v>451</v>
+      </c>
+      <c r="F28" s="101"/>
       <c r="G28" s="61"/>
       <c r="H28" s="61"/>
       <c r="I28" s="61"/>
@@ -8893,22 +8209,22 @@
       <c r="K28" s="61"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89" t="s">
+      <c r="A29" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="91" t="s">
-        <v>476</v>
-      </c>
-      <c r="C29" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="D29" s="91" t="s">
-        <v>475</v>
-      </c>
-      <c r="E29" s="91" t="s">
-        <v>477</v>
-      </c>
-      <c r="F29" s="93"/>
+      <c r="B29" s="92" t="s">
+        <v>452</v>
+      </c>
+      <c r="C29" s="92" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="92" t="s">
+        <v>451</v>
+      </c>
+      <c r="E29" s="92" t="s">
+        <v>453</v>
+      </c>
+      <c r="F29" s="94"/>
       <c r="G29" s="61"/>
       <c r="H29" s="61"/>
       <c r="I29" s="61"/>
@@ -8916,21 +8232,21 @@
       <c r="K29" s="61"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="101" t="s">
+      <c r="A30" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="102" t="s">
-        <v>478</v>
-      </c>
-      <c r="C30" s="102" t="s">
-        <v>448</v>
-      </c>
-      <c r="D30" s="102" t="s">
-        <v>479</v>
-      </c>
-      <c r="E30" s="102"/>
-      <c r="F30" s="103" t="s">
-        <v>480</v>
+      <c r="B30" s="103" t="s">
+        <v>454</v>
+      </c>
+      <c r="C30" s="103" t="s">
+        <v>424</v>
+      </c>
+      <c r="D30" s="103" t="s">
+        <v>455</v>
+      </c>
+      <c r="E30" s="103"/>
+      <c r="F30" s="104" t="s">
+        <v>456</v>
       </c>
       <c r="G30" s="61"/>
       <c r="H30" s="61"/>
@@ -8939,20 +8255,20 @@
       <c r="K30" s="61"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="95" t="s">
-        <v>481</v>
-      </c>
-      <c r="C31" s="95" t="s">
-        <v>452</v>
-      </c>
-      <c r="D31" s="95" t="s">
-        <v>482</v>
-      </c>
-      <c r="E31" s="95"/>
-      <c r="F31" s="96"/>
+      <c r="B31" s="96" t="s">
+        <v>457</v>
+      </c>
+      <c r="C31" s="96" t="s">
+        <v>428</v>
+      </c>
+      <c r="D31" s="96" t="s">
+        <v>458</v>
+      </c>
+      <c r="E31" s="96"/>
+      <c r="F31" s="97"/>
       <c r="G31" s="61"/>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
@@ -8960,12 +8276,12 @@
       <c r="K31" s="61"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="94"/>
-      <c r="B32" s="95"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="96"/>
+      <c r="A32" s="95"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="97"/>
       <c r="G32" s="61"/>
       <c r="H32" s="61"/>
       <c r="I32" s="61"/>
@@ -8973,12 +8289,12 @@
       <c r="K32" s="61"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="97"/>
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="108"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="108"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="109"/>
       <c r="G33" s="61"/>
       <c r="H33" s="61"/>
       <c r="I33" s="61"/>
@@ -9053,8 +8369,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9071,15 +8387,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="41.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="17.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="18.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="35" width="18.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="35" width="18.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="20.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="35" width="16.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="35" width="17.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="35" width="16.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.47"/>
   </cols>
   <sheetData>
-    <row r="1" s="110" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="111" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="63" t="s">
         <v>68</v>
       </c>
@@ -9087,13 +8404,13 @@
         <v>69</v>
       </c>
       <c r="C1" s="64" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="D1" s="64" t="s">
         <v>71</v>
       </c>
       <c r="E1" s="64" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="F1" s="64" t="s">
         <v>25</v>
@@ -9104,7 +8421,7 @@
       <c r="H1" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="I1" s="110" t="s">
         <v>58</v>
       </c>
       <c r="XFC1" s="1"/>
@@ -9112,7 +8429,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="B2" s="41" t="n">
         <v>0</v>
@@ -9142,7 +8459,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="B3" s="41" t="n">
         <v>1</v>
@@ -9172,7 +8489,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="B4" s="41" t="n">
         <v>2</v>
@@ -9202,7 +8519,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="B5" s="41" t="n">
         <v>3</v>
@@ -9262,7 +8579,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>5</v>
@@ -9292,7 +8609,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="B8" s="41" t="n">
         <v>6</v>
@@ -9352,7 +8669,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>8</v>
@@ -9382,7 +8699,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="B11" s="41" t="n">
         <v>9</v>
@@ -9412,7 +8729,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="B12" s="41" t="n">
         <v>10</v>
@@ -9442,7 +8759,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>11</v>
@@ -9472,7 +8789,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="B14" s="41" t="n">
         <v>12</v>
@@ -9501,7 +8818,7 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="112" t="s">
         <v>168</v>
       </c>
       <c r="B15" s="48" t="n">
@@ -9592,7 +8909,7 @@
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -9623,630 +8940,599 @@
       <c r="J24" s="55" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="37.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="42" t="s">
-        <v>496</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>497</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>498</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>499</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>500</v>
-      </c>
-      <c r="H25" s="42" t="s">
-        <v>501</v>
-      </c>
-      <c r="I25" s="42" t="s">
-        <v>502</v>
-      </c>
-      <c r="J25" s="42" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="113" t="s">
+        <v>472</v>
+      </c>
+      <c r="D25" s="113" t="s">
+        <v>473</v>
+      </c>
+      <c r="E25" s="113" t="s">
+        <v>472</v>
+      </c>
+      <c r="F25" s="113" t="s">
+        <v>474</v>
+      </c>
+      <c r="G25" s="113" t="s">
+        <v>475</v>
+      </c>
+      <c r="H25" s="113" t="s">
+        <v>476</v>
+      </c>
+      <c r="I25" s="113" t="s">
+        <v>477</v>
+      </c>
+      <c r="J25" s="113" t="s">
+        <v>478</v>
+      </c>
+      <c r="K25" s="113" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="113" t="s">
+        <v>480</v>
+      </c>
+      <c r="D26" s="113" t="s">
+        <v>481</v>
+      </c>
+      <c r="E26" s="113" t="s">
+        <v>480</v>
+      </c>
+      <c r="F26" s="113" t="s">
+        <v>482</v>
+      </c>
+      <c r="G26" s="113" t="s">
+        <v>483</v>
+      </c>
+      <c r="H26" s="113" t="s">
+        <v>484</v>
+      </c>
+      <c r="I26" s="113" t="s">
+        <v>485</v>
+      </c>
+      <c r="J26" s="113" t="s">
+        <v>486</v>
+      </c>
+      <c r="K26" s="113" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="113" t="s">
+        <v>488</v>
+      </c>
+      <c r="D27" s="113" t="s">
+        <v>489</v>
+      </c>
+      <c r="E27" s="113" t="s">
+        <v>488</v>
+      </c>
+      <c r="F27" s="113" t="s">
+        <v>490</v>
+      </c>
+      <c r="G27" s="113" t="s">
+        <v>491</v>
+      </c>
+      <c r="H27" s="113" t="s">
+        <v>492</v>
+      </c>
+      <c r="I27" s="113" t="s">
+        <v>493</v>
+      </c>
+      <c r="J27" s="113" t="s">
+        <v>494</v>
+      </c>
+      <c r="K27" s="113" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="113" t="s">
+        <v>496</v>
+      </c>
+      <c r="D28" s="113" t="s">
+        <v>497</v>
+      </c>
+      <c r="E28" s="113" t="s">
+        <v>496</v>
+      </c>
+      <c r="F28" s="113" t="s">
+        <v>498</v>
+      </c>
+      <c r="G28" s="113" t="s">
+        <v>497</v>
+      </c>
+      <c r="H28" s="113" t="s">
+        <v>496</v>
+      </c>
+      <c r="I28" s="113" t="s">
+        <v>498</v>
+      </c>
+      <c r="J28" s="113" t="s">
+        <v>499</v>
+      </c>
+      <c r="K28" s="113" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="38.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="113" t="s">
+        <v>501</v>
+      </c>
+      <c r="D29" s="113" t="s">
+        <v>502</v>
+      </c>
+      <c r="E29" s="113" t="s">
+        <v>501</v>
+      </c>
+      <c r="F29" s="113" t="s">
+        <v>503</v>
+      </c>
+      <c r="G29" s="113" t="s">
         <v>504</v>
       </c>
-      <c r="D26" s="42" t="s">
+      <c r="H29" s="113" t="s">
         <v>505</v>
       </c>
-      <c r="E26" s="42" t="s">
+      <c r="I29" s="113" t="s">
+        <v>503</v>
+      </c>
+      <c r="J29" s="113" t="s">
         <v>506</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="K29" s="113" t="s">
         <v>507</v>
       </c>
-      <c r="G26" s="42" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="38.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="56" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="113" t="s">
         <v>508</v>
       </c>
-      <c r="H26" s="42" t="s">
+      <c r="D30" s="113" t="s">
         <v>509</v>
       </c>
-      <c r="I26" s="42" t="s">
+      <c r="E30" s="113" t="s">
+        <v>508</v>
+      </c>
+      <c r="F30" s="113" t="s">
         <v>510</v>
       </c>
-      <c r="J26" s="42" t="s">
+      <c r="G30" s="113" t="s">
+        <v>509</v>
+      </c>
+      <c r="H30" s="113" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="58"/>
-    </row>
-    <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="56" t="n">
-        <v>4</v>
-      </c>
-      <c r="B28" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="42" t="s">
+      <c r="I30" s="113" t="s">
+        <v>510</v>
+      </c>
+      <c r="J30" s="113" t="s">
         <v>512</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="K30" s="113" t="s">
         <v>513</v>
       </c>
-      <c r="E28" s="42" t="s">
-        <v>512</v>
-      </c>
-      <c r="F28" s="42" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="113" t="s">
         <v>514</v>
       </c>
-      <c r="G28" s="42" t="s">
+      <c r="D31" s="113" t="s">
         <v>515</v>
       </c>
-      <c r="H28" s="42" t="s">
+      <c r="E31" s="113" t="s">
+        <v>514</v>
+      </c>
+      <c r="F31" s="113" t="s">
         <v>516</v>
       </c>
-      <c r="I28" s="42" t="s">
+      <c r="G31" s="113" t="s">
+        <v>515</v>
+      </c>
+      <c r="H31" s="113" t="s">
+        <v>514</v>
+      </c>
+      <c r="I31" s="113" t="s">
+        <v>516</v>
+      </c>
+      <c r="J31" s="113" t="s">
         <v>517</v>
       </c>
-      <c r="J28" s="42" t="s">
+      <c r="K31" s="113" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="56" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="42" t="s">
+    <row r="32" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="113" t="s">
         <v>519</v>
       </c>
-      <c r="D29" s="42" t="s">
+      <c r="D32" s="113" t="s">
         <v>520</v>
       </c>
-      <c r="E29" s="42" t="s">
-        <v>519</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>521</v>
-      </c>
-      <c r="G29" s="42" t="s">
-        <v>520</v>
-      </c>
-      <c r="H29" s="42" t="s">
-        <v>519</v>
-      </c>
-      <c r="I29" s="42" t="s">
-        <v>521</v>
-      </c>
-      <c r="J29" s="42" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="56" t="n">
-        <v>6</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="D30" s="42" t="s">
-        <v>524</v>
-      </c>
-      <c r="E30" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>525</v>
-      </c>
-      <c r="G30" s="42" t="s">
-        <v>524</v>
-      </c>
-      <c r="H30" s="42" t="s">
-        <v>523</v>
-      </c>
-      <c r="I30" s="42" t="s">
-        <v>525</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="56" t="n">
-        <v>7</v>
-      </c>
-      <c r="B31" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>527</v>
-      </c>
-      <c r="D31" s="42" t="s">
-        <v>528</v>
-      </c>
-      <c r="E31" s="42" t="s">
-        <v>527</v>
-      </c>
-      <c r="F31" s="42" t="s">
-        <v>529</v>
-      </c>
-      <c r="G31" s="42" t="s">
-        <v>528</v>
-      </c>
-      <c r="H31" s="42" t="s">
-        <v>527</v>
-      </c>
-      <c r="I31" s="42" t="s">
-        <v>529</v>
-      </c>
-      <c r="J31" s="42" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="56" t="n">
-        <v>8</v>
-      </c>
-      <c r="B32" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>531</v>
-      </c>
-      <c r="D32" s="42" t="s">
-        <v>532</v>
-      </c>
       <c r="E32" s="42" t="s">
-        <v>531</v>
+        <v>219</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>533</v>
+        <v>220</v>
       </c>
       <c r="G32" s="42" t="s">
-        <v>532</v>
+        <v>218</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>531</v>
+        <v>219</v>
       </c>
       <c r="I32" s="42" t="s">
-        <v>533</v>
+        <v>220</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>221</v>
+      </c>
+      <c r="K32" s="77" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>535</v>
+        <v>223</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>536</v>
+        <v>224</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>535</v>
+        <v>225</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>537</v>
+        <v>226</v>
       </c>
       <c r="G33" s="42" t="s">
-        <v>536</v>
+        <v>224</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>535</v>
+        <v>225</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>537</v>
+        <v>226</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>227</v>
+      </c>
+      <c r="K33" s="77" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>539</v>
+        <v>229</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>540</v>
+        <v>230</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>539</v>
+        <v>231</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>541</v>
+        <v>232</v>
       </c>
       <c r="G34" s="42" t="s">
-        <v>540</v>
+        <v>233</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>539</v>
+        <v>234</v>
       </c>
       <c r="I34" s="42" t="s">
-        <v>541</v>
+        <v>235</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+      <c r="K34" s="77" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="42.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>543</v>
+        <v>238</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>544</v>
+        <v>239</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>543</v>
+        <v>238</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>545</v>
+        <v>240</v>
       </c>
       <c r="G35" s="42" t="s">
-        <v>544</v>
+        <v>241</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>543</v>
+        <v>242</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>546</v>
+        <v>243</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>244</v>
+      </c>
+      <c r="K35" s="77" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="37.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>548</v>
+        <v>246</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>549</v>
+        <v>247</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>548</v>
+        <v>246</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>549</v>
+        <v>249</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>548</v>
+        <v>250</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>550</v>
+        <v>251</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+      <c r="K36" s="77" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="34.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>552</v>
+        <v>254</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>553</v>
+        <v>255</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>552</v>
+        <v>254</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>554</v>
+        <v>256</v>
       </c>
       <c r="G37" s="42" t="s">
-        <v>555</v>
+        <v>257</v>
       </c>
       <c r="H37" s="42" t="s">
-        <v>556</v>
+        <v>258</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>557</v>
+        <v>259</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+      <c r="K37" s="77" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="64.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>559</v>
+        <v>262</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>560</v>
+        <v>263</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>559</v>
+        <v>262</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>561</v>
+        <v>264</v>
       </c>
       <c r="G38" s="42" t="s">
-        <v>562</v>
+        <v>265</v>
       </c>
       <c r="H38" s="42" t="s">
-        <v>563</v>
+        <v>266</v>
       </c>
       <c r="I38" s="42" t="s">
-        <v>564</v>
+        <v>267</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>268</v>
+      </c>
+      <c r="K38" s="77" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="64.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>566</v>
+        <v>270</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>567</v>
+        <v>271</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>566</v>
+        <v>270</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>568</v>
+        <v>272</v>
       </c>
       <c r="G39" s="42" t="s">
-        <v>569</v>
+        <v>273</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>570</v>
+        <v>274</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>571</v>
+        <v>275</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B40" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>573</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>574</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>573</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>575</v>
-      </c>
-      <c r="G40" s="42" t="s">
-        <v>576</v>
-      </c>
-      <c r="H40" s="42" t="s">
-        <v>577</v>
-      </c>
-      <c r="I40" s="42" t="s">
-        <v>578</v>
-      </c>
-      <c r="J40" s="42" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>580</v>
-      </c>
-      <c r="D41" s="42" t="s">
-        <v>581</v>
-      </c>
-      <c r="E41" s="42" t="s">
-        <v>580</v>
-      </c>
-      <c r="F41" s="42" t="s">
-        <v>582</v>
-      </c>
-      <c r="G41" s="42" t="s">
-        <v>583</v>
-      </c>
-      <c r="H41" s="42" t="s">
-        <v>584</v>
-      </c>
-      <c r="I41" s="42" t="s">
-        <v>585</v>
-      </c>
-      <c r="J41" s="42" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="42" t="s">
-        <v>587</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>588</v>
-      </c>
-      <c r="E42" s="42" t="s">
-        <v>587</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>589</v>
-      </c>
-      <c r="G42" s="42" t="s">
-        <v>590</v>
-      </c>
-      <c r="H42" s="42" t="s">
-        <v>591</v>
-      </c>
-      <c r="I42" s="42" t="s">
-        <v>592</v>
-      </c>
-      <c r="J42" s="42" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B43" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>594</v>
-      </c>
-      <c r="D43" s="42" t="s">
-        <v>595</v>
-      </c>
-      <c r="E43" s="42" t="s">
-        <v>596</v>
-      </c>
-      <c r="F43" s="42" t="s">
-        <v>597</v>
-      </c>
-      <c r="G43" s="42" t="s">
-        <v>598</v>
-      </c>
-      <c r="H43" s="42" t="s">
-        <v>599</v>
-      </c>
-      <c r="I43" s="42" t="s">
-        <v>600</v>
-      </c>
-      <c r="J43" s="42" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>602</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>603</v>
-      </c>
-      <c r="E44" s="42" t="s">
-        <v>602</v>
-      </c>
-      <c r="F44" s="42" t="s">
-        <v>604</v>
-      </c>
-      <c r="G44" s="42" t="s">
-        <v>605</v>
-      </c>
-      <c r="H44" s="42" t="s">
-        <v>606</v>
-      </c>
-      <c r="I44" s="42" t="s">
-        <v>607</v>
-      </c>
-      <c r="J44" s="42" t="s">
-        <v>608</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="K39" s="77" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="35"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="35"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="35"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="35"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="57"/>
@@ -10259,6 +9545,7 @@
       <c r="H45" s="57"/>
       <c r="I45" s="57"/>
       <c r="J45" s="58"/>
+      <c r="K45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="57"/>
@@ -10271,6 +9558,7 @@
       <c r="H46" s="57"/>
       <c r="I46" s="57"/>
       <c r="J46" s="58"/>
+      <c r="K46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="57"/>
@@ -10283,6 +9571,7 @@
       <c r="H47" s="57"/>
       <c r="I47" s="57"/>
       <c r="J47" s="58"/>
+      <c r="K47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="57"/>
@@ -10295,66 +9584,67 @@
       <c r="H48" s="57"/>
       <c r="I48" s="57"/>
       <c r="J48" s="58"/>
+      <c r="K48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="57"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="58"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="K49" s="35"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="57"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="58"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="K50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="58"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="K51" s="35"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="57"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="58"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="K52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="57"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="58"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="42"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="K53" s="35"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="42"/>
@@ -10366,6 +9656,7 @@
       <c r="G54" s="42"/>
       <c r="H54" s="42"/>
       <c r="I54" s="42"/>
+      <c r="K54" s="35"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
@@ -10377,6 +9668,7 @@
       <c r="G55" s="42"/>
       <c r="H55" s="42"/>
       <c r="I55" s="42"/>
+      <c r="K55" s="35"/>
     </row>
     <row r="56" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
@@ -10388,725 +9680,578 @@
       <c r="G56" s="42"/>
       <c r="H56" s="42"/>
       <c r="I56" s="42"/>
-    </row>
-    <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-    </row>
-    <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="42"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-    </row>
-    <row r="59" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-    </row>
-    <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-    </row>
-    <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="42"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="42"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
+      <c r="K56" s="35"/>
+    </row>
+    <row r="57" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="H57" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I57" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J57" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="K57" s="55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="113" t="s">
+        <v>521</v>
+      </c>
+      <c r="D58" s="113" t="s">
+        <v>522</v>
+      </c>
+      <c r="E58" s="113" t="s">
+        <v>521</v>
+      </c>
+      <c r="F58" s="113" t="s">
+        <v>523</v>
+      </c>
+      <c r="G58" s="113" t="s">
+        <v>524</v>
+      </c>
+      <c r="H58" s="113" t="s">
+        <v>525</v>
+      </c>
+      <c r="I58" s="113" t="s">
+        <v>526</v>
+      </c>
+      <c r="J58" s="113" t="s">
+        <v>527</v>
+      </c>
+      <c r="K58" s="113" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="113" t="s">
+        <v>529</v>
+      </c>
+      <c r="D59" s="113" t="s">
+        <v>530</v>
+      </c>
+      <c r="E59" s="113" t="s">
+        <v>529</v>
+      </c>
+      <c r="F59" s="113" t="s">
+        <v>531</v>
+      </c>
+      <c r="G59" s="113" t="s">
+        <v>532</v>
+      </c>
+      <c r="H59" s="113" t="s">
+        <v>533</v>
+      </c>
+      <c r="I59" s="113" t="s">
+        <v>534</v>
+      </c>
+      <c r="J59" s="113" t="s">
+        <v>535</v>
+      </c>
+      <c r="K59" s="113" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" s="113" t="s">
+        <v>537</v>
+      </c>
+      <c r="D60" s="113" t="s">
+        <v>538</v>
+      </c>
+      <c r="E60" s="113" t="s">
+        <v>537</v>
+      </c>
+      <c r="F60" s="113" t="s">
+        <v>539</v>
+      </c>
+      <c r="G60" s="113" t="s">
+        <v>540</v>
+      </c>
+      <c r="H60" s="113" t="s">
+        <v>541</v>
+      </c>
+      <c r="I60" s="113" t="s">
+        <v>542</v>
+      </c>
+      <c r="J60" s="113" t="s">
+        <v>543</v>
+      </c>
+      <c r="K60" s="113" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="113" t="s">
+        <v>545</v>
+      </c>
+      <c r="D61" s="113" t="s">
+        <v>546</v>
+      </c>
+      <c r="E61" s="113" t="s">
+        <v>545</v>
+      </c>
+      <c r="F61" s="113" t="s">
+        <v>547</v>
+      </c>
+      <c r="G61" s="113" t="s">
+        <v>548</v>
+      </c>
+      <c r="H61" s="113" t="s">
+        <v>549</v>
+      </c>
+      <c r="I61" s="113" t="s">
+        <v>550</v>
+      </c>
+      <c r="J61" s="113" t="s">
+        <v>551</v>
+      </c>
+      <c r="K61" s="113" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="B62" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="D62" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="E62" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="F62" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="G62" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="H62" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="I62" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="J62" s="55" t="s">
-        <v>100</v>
+      <c r="A62" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B62" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="113" t="s">
+        <v>553</v>
+      </c>
+      <c r="D62" s="113" t="s">
+        <v>554</v>
+      </c>
+      <c r="E62" s="113" t="s">
+        <v>553</v>
+      </c>
+      <c r="F62" s="113" t="s">
+        <v>555</v>
+      </c>
+      <c r="G62" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="H62" s="113" t="s">
+        <v>557</v>
+      </c>
+      <c r="I62" s="113" t="s">
+        <v>558</v>
+      </c>
+      <c r="J62" s="113" t="s">
+        <v>559</v>
+      </c>
+      <c r="K62" s="113" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" s="42" t="s">
-        <v>609</v>
-      </c>
-      <c r="D63" s="42" t="s">
-        <v>610</v>
-      </c>
-      <c r="E63" s="42" t="s">
-        <v>609</v>
-      </c>
-      <c r="F63" s="42" t="s">
-        <v>611</v>
-      </c>
-      <c r="G63" s="42" t="s">
-        <v>612</v>
-      </c>
-      <c r="H63" s="42" t="s">
-        <v>613</v>
-      </c>
-      <c r="I63" s="42" t="s">
-        <v>614</v>
-      </c>
-      <c r="J63" s="42" t="s">
-        <v>615</v>
+        <v>108</v>
+      </c>
+      <c r="C63" s="113" t="s">
+        <v>561</v>
+      </c>
+      <c r="D63" s="113" t="s">
+        <v>562</v>
+      </c>
+      <c r="E63" s="113" t="s">
+        <v>561</v>
+      </c>
+      <c r="F63" s="113" t="s">
+        <v>563</v>
+      </c>
+      <c r="G63" s="113" t="s">
+        <v>564</v>
+      </c>
+      <c r="H63" s="113" t="s">
+        <v>565</v>
+      </c>
+      <c r="I63" s="113" t="s">
+        <v>566</v>
+      </c>
+      <c r="J63" s="113" t="s">
+        <v>567</v>
+      </c>
+      <c r="K63" s="113" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C64" s="42" t="s">
-        <v>616</v>
-      </c>
-      <c r="D64" s="42" t="s">
-        <v>617</v>
-      </c>
-      <c r="E64" s="42" t="s">
-        <v>616</v>
-      </c>
-      <c r="F64" s="42" t="s">
-        <v>618</v>
-      </c>
-      <c r="G64" s="42" t="s">
-        <v>619</v>
-      </c>
-      <c r="H64" s="42" t="s">
-        <v>620</v>
-      </c>
-      <c r="I64" s="42" t="s">
-        <v>621</v>
-      </c>
-      <c r="J64" s="42" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+      <c r="C64" s="113" t="s">
+        <v>569</v>
+      </c>
+      <c r="D64" s="113" t="s">
+        <v>570</v>
+      </c>
+      <c r="E64" s="113" t="s">
+        <v>569</v>
+      </c>
+      <c r="F64" s="113" t="s">
+        <v>571</v>
+      </c>
+      <c r="G64" s="113" t="s">
+        <v>572</v>
+      </c>
+      <c r="H64" s="113" t="s">
+        <v>573</v>
+      </c>
+      <c r="I64" s="113" t="s">
+        <v>574</v>
+      </c>
+      <c r="J64" s="113" t="s">
+        <v>575</v>
+      </c>
+      <c r="K64" s="113" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C65" s="57"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="57"/>
-      <c r="J65" s="58"/>
-    </row>
-    <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="D65" s="42" t="s">
+        <v>334</v>
+      </c>
+      <c r="E65" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="F65" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="G65" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="H65" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="I65" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="J65" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="K65" s="77" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>623</v>
+        <v>341</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>624</v>
+        <v>342</v>
       </c>
       <c r="E66" s="42" t="s">
-        <v>623</v>
+        <v>341</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>625</v>
+        <v>343</v>
       </c>
       <c r="G66" s="42" t="s">
-        <v>626</v>
+        <v>344</v>
       </c>
       <c r="H66" s="42" t="s">
-        <v>627</v>
+        <v>345</v>
       </c>
       <c r="I66" s="42" t="s">
-        <v>628</v>
+        <v>346</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+      <c r="K66" s="77" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C67" s="42" t="s">
-        <v>630</v>
+        <v>349</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>631</v>
+        <v>350</v>
       </c>
       <c r="E67" s="42" t="s">
-        <v>630</v>
+        <v>349</v>
       </c>
       <c r="F67" s="42" t="s">
-        <v>632</v>
+        <v>351</v>
       </c>
       <c r="G67" s="42" t="s">
-        <v>633</v>
+        <v>352</v>
       </c>
       <c r="H67" s="42" t="s">
-        <v>634</v>
+        <v>353</v>
       </c>
       <c r="I67" s="42" t="s">
-        <v>635</v>
+        <v>354</v>
       </c>
       <c r="J67" s="42" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>355</v>
+      </c>
+      <c r="K67" s="77" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C68" s="42" t="s">
-        <v>637</v>
+        <v>357</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>638</v>
+        <v>358</v>
       </c>
       <c r="E68" s="42" t="s">
-        <v>637</v>
+        <v>357</v>
       </c>
       <c r="F68" s="42" t="s">
-        <v>639</v>
+        <v>359</v>
       </c>
       <c r="G68" s="42" t="s">
-        <v>640</v>
+        <v>360</v>
       </c>
       <c r="H68" s="42" t="s">
-        <v>641</v>
+        <v>361</v>
       </c>
       <c r="I68" s="42" t="s">
-        <v>642</v>
+        <v>362</v>
       </c>
       <c r="J68" s="42" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>363</v>
+      </c>
+      <c r="K68" s="77" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>644</v>
+        <v>365</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>645</v>
+        <v>366</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>644</v>
+        <v>365</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>646</v>
+        <v>367</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>647</v>
+        <v>368</v>
       </c>
       <c r="H69" s="42" t="s">
-        <v>648</v>
+        <v>369</v>
       </c>
       <c r="I69" s="42" t="s">
-        <v>649</v>
+        <v>370</v>
       </c>
       <c r="J69" s="42" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>371</v>
+      </c>
+      <c r="K69" s="77" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>651</v>
+        <v>373</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>652</v>
+        <v>374</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>651</v>
+        <v>373</v>
       </c>
       <c r="F70" s="42" t="s">
-        <v>653</v>
+        <v>375</v>
       </c>
       <c r="G70" s="42" t="s">
-        <v>654</v>
+        <v>376</v>
       </c>
       <c r="H70" s="42" t="s">
-        <v>655</v>
+        <v>377</v>
       </c>
       <c r="I70" s="42" t="s">
-        <v>656</v>
+        <v>378</v>
       </c>
       <c r="J70" s="42" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>379</v>
+      </c>
+      <c r="K70" s="77" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C71" s="42" t="s">
-        <v>658</v>
+        <v>381</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>659</v>
+        <v>382</v>
       </c>
       <c r="E71" s="42" t="s">
-        <v>658</v>
+        <v>381</v>
       </c>
       <c r="F71" s="42" t="s">
-        <v>660</v>
+        <v>383</v>
       </c>
       <c r="G71" s="42" t="s">
-        <v>661</v>
+        <v>384</v>
       </c>
       <c r="H71" s="42" t="s">
-        <v>662</v>
+        <v>385</v>
       </c>
       <c r="I71" s="42" t="s">
-        <v>663</v>
+        <v>386</v>
       </c>
       <c r="J71" s="42" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>387</v>
+      </c>
+      <c r="K71" s="77" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>665</v>
+        <v>389</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>666</v>
+        <v>390</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>665</v>
+        <v>389</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>667</v>
+        <v>391</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>668</v>
+        <v>392</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>669</v>
+        <v>393</v>
       </c>
       <c r="I72" s="42" t="s">
-        <v>670</v>
+        <v>394</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="56" t="n">
-        <v>11</v>
-      </c>
-      <c r="B73" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C73" s="42" t="s">
-        <v>672</v>
-      </c>
-      <c r="D73" s="42" t="s">
-        <v>673</v>
-      </c>
-      <c r="E73" s="42" t="s">
-        <v>672</v>
-      </c>
-      <c r="F73" s="42" t="s">
-        <v>674</v>
-      </c>
-      <c r="G73" s="42" t="s">
-        <v>675</v>
-      </c>
-      <c r="H73" s="42" t="s">
-        <v>676</v>
-      </c>
-      <c r="I73" s="42" t="s">
-        <v>677</v>
-      </c>
-      <c r="J73" s="42" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="56" t="n">
-        <v>12</v>
-      </c>
-      <c r="B74" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C74" s="42" t="s">
-        <v>679</v>
-      </c>
-      <c r="D74" s="42" t="s">
-        <v>680</v>
-      </c>
-      <c r="E74" s="42" t="s">
-        <v>679</v>
-      </c>
-      <c r="F74" s="42" t="s">
-        <v>681</v>
-      </c>
-      <c r="G74" s="42" t="s">
-        <v>682</v>
-      </c>
-      <c r="H74" s="42" t="s">
-        <v>683</v>
-      </c>
-      <c r="I74" s="42" t="s">
-        <v>684</v>
-      </c>
-      <c r="J74" s="42" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="56" t="n">
-        <v>13</v>
-      </c>
-      <c r="B75" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C75" s="42" t="s">
-        <v>686</v>
-      </c>
-      <c r="D75" s="42" t="s">
-        <v>687</v>
-      </c>
-      <c r="E75" s="42" t="s">
-        <v>686</v>
-      </c>
-      <c r="F75" s="42" t="s">
-        <v>688</v>
-      </c>
-      <c r="G75" s="42" t="s">
-        <v>689</v>
-      </c>
-      <c r="H75" s="42" t="s">
-        <v>690</v>
-      </c>
-      <c r="I75" s="42" t="s">
-        <v>691</v>
-      </c>
-      <c r="J75" s="42" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="56" t="n">
-        <v>14</v>
-      </c>
-      <c r="B76" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" s="42" t="s">
-        <v>693</v>
-      </c>
-      <c r="D76" s="42" t="s">
-        <v>694</v>
-      </c>
-      <c r="E76" s="42" t="s">
-        <v>693</v>
-      </c>
-      <c r="F76" s="42" t="s">
-        <v>695</v>
-      </c>
-      <c r="G76" s="42" t="s">
-        <v>696</v>
-      </c>
-      <c r="H76" s="42" t="s">
-        <v>697</v>
-      </c>
-      <c r="I76" s="42" t="s">
-        <v>698</v>
-      </c>
-      <c r="J76" s="42" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="56" t="n">
-        <v>15</v>
-      </c>
-      <c r="B77" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="42" t="s">
-        <v>700</v>
-      </c>
-      <c r="D77" s="42" t="s">
-        <v>701</v>
-      </c>
-      <c r="E77" s="42" t="s">
-        <v>700</v>
-      </c>
-      <c r="F77" s="42" t="s">
-        <v>702</v>
-      </c>
-      <c r="G77" s="42" t="s">
-        <v>703</v>
-      </c>
-      <c r="H77" s="42" t="s">
-        <v>704</v>
-      </c>
-      <c r="I77" s="42" t="s">
-        <v>705</v>
-      </c>
-      <c r="J77" s="42" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B78" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="42" t="s">
-        <v>707</v>
-      </c>
-      <c r="D78" s="42" t="s">
-        <v>708</v>
-      </c>
-      <c r="E78" s="42" t="s">
-        <v>707</v>
-      </c>
-      <c r="F78" s="42" t="s">
-        <v>709</v>
-      </c>
-      <c r="G78" s="42" t="s">
-        <v>710</v>
-      </c>
-      <c r="H78" s="42" t="s">
-        <v>711</v>
-      </c>
-      <c r="I78" s="42" t="s">
-        <v>712</v>
-      </c>
-      <c r="J78" s="42" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="34.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B79" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="112" t="s">
-        <v>714</v>
-      </c>
-      <c r="D79" s="112" t="s">
-        <v>715</v>
-      </c>
-      <c r="E79" s="112" t="s">
-        <v>714</v>
-      </c>
-      <c r="F79" s="112" t="s">
-        <v>716</v>
-      </c>
-      <c r="G79" s="112" t="s">
-        <v>717</v>
-      </c>
-      <c r="H79" s="112" t="s">
-        <v>718</v>
-      </c>
-      <c r="I79" s="112" t="s">
-        <v>719</v>
-      </c>
-      <c r="J79" s="112" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B80" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="42" t="s">
-        <v>721</v>
-      </c>
-      <c r="D80" s="42" t="s">
-        <v>722</v>
-      </c>
-      <c r="E80" s="42" t="s">
-        <v>721</v>
-      </c>
-      <c r="F80" s="42" t="s">
-        <v>723</v>
-      </c>
-      <c r="G80" s="42" t="s">
-        <v>724</v>
-      </c>
-      <c r="H80" s="42" t="s">
-        <v>725</v>
-      </c>
-      <c r="I80" s="42" t="s">
-        <v>726</v>
-      </c>
-      <c r="J80" s="42" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B81" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C81" s="42" t="s">
-        <v>728</v>
-      </c>
-      <c r="D81" s="42" t="s">
-        <v>729</v>
-      </c>
-      <c r="E81" s="42" t="s">
-        <v>728</v>
-      </c>
-      <c r="F81" s="42" t="s">
-        <v>730</v>
-      </c>
-      <c r="G81" s="42" t="s">
-        <v>731</v>
-      </c>
-      <c r="H81" s="42" t="s">
-        <v>732</v>
-      </c>
-      <c r="I81" s="42" t="s">
-        <v>733</v>
-      </c>
-      <c r="J81" s="42" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="45.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B82" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C82" s="42" t="s">
-        <v>735</v>
-      </c>
-      <c r="D82" s="42" t="s">
-        <v>736</v>
-      </c>
-      <c r="E82" s="42" t="s">
-        <v>735</v>
-      </c>
-      <c r="F82" s="42" t="s">
-        <v>737</v>
-      </c>
-      <c r="G82" s="42" t="s">
-        <v>738</v>
-      </c>
-      <c r="H82" s="42" t="s">
-        <v>739</v>
-      </c>
-      <c r="I82" s="42" t="s">
-        <v>740</v>
-      </c>
-      <c r="J82" s="42" t="s">
-        <v>741</v>
-      </c>
-    </row>
+        <v>395</v>
+      </c>
+      <c r="K72" s="77" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="34.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="45.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts-CIC18" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="735">
   <si>
     <t xml:space="preserve">TÉCNICA</t>
   </si>
@@ -340,64 +340,721 @@
     <t xml:space="preserve">MCC</t>
   </si>
   <si>
+    <t xml:space="preserve">AUC-ROC</t>
+  </si>
+  <si>
     <t xml:space="preserve">PCA4 + KNN</t>
   </si>
   <si>
+    <t xml:space="preserve">0.981188 ± 0.000118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981630 ± 0.000131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981269 ± 0.000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906608 ± 0.003374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897246 ± 0.010076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898808 ± 0.008337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977040 ± 0.000147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995620 ± 0.000052</t>
+  </si>
+  <si>
     <t xml:space="preserve">PCA4 + Logistic Regression</t>
   </si>
   <si>
-    <t xml:space="preserve">PCA4 + SVM</t>
+    <t xml:space="preserve">0.526836 ± 0.001044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634730 ± 0.004864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549591 ± 0.001502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401240 ± 0.001124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.652658 ± 0.013585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403495 ± 0.001207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492888 ± 0.001195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877849 ± 0.001344</t>
   </si>
   <si>
     <t xml:space="preserve">PCA4 + MLP</t>
   </si>
   <si>
+    <t xml:space="preserve">0.976994 ± 0.001150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977808 ± 0.001160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977010 ± 0.001184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767893 ± 0.039440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705217 ± 0.029416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718513 ± 0.031352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972003 ± 0.001412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998477 ± 0.000140</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUS/SMOTE + PCA4 + KNN</t>
   </si>
   <si>
+    <t xml:space="preserve">0.982627 ± 0.000490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982786 ± 0.000454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982496 ± 0.000490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981416 ± 0.000521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996165 ± 0.000224</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUS/SMOTE + PCA4 + Logistic Regression</t>
   </si>
   <si>
-    <t xml:space="preserve">RUS/SMOTE + PCA4 + SVM</t>
+    <t xml:space="preserve">0.662567 ± 0.002064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655646 ± 0.001875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.652338 ± 0.001821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641318 ± 0.002207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947892 ± 0.000615</t>
   </si>
   <si>
     <t xml:space="preserve">RUS/SMOTE + PCA4 + MLP</t>
   </si>
   <si>
+    <t xml:space="preserve">0.930607 ± 0.005611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931340 ± 0.006682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928765 ± 0.006060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925990 ± 0.006037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995828 ± 0.000577</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE + PCA4 + KNN</t>
   </si>
   <si>
+    <t xml:space="preserve">0.993553 ± 0.000673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993607 ± 0.000667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993563 ± 0.000673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993095 ± 0.000720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999023 ± 0.000153</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE + PCA4 + Logistic Regression</t>
   </si>
   <si>
-    <t xml:space="preserve">NearMiss/SMOTE + PCA4 + SVM</t>
+    <t xml:space="preserve">0.850880 ± 0.003884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866056 ± 0.003914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846752 ± 0.004092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846752 ± 0.004092 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843191 ± 0.004082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987173 ± 0.000251</t>
   </si>
   <si>
     <t xml:space="preserve">NearMiss/SMOTE + PCA4 + MLP</t>
   </si>
   <si>
+    <t xml:space="preserve">0.812079 ± 0.001702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867410 ± 0.014507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798277 ± 0.008138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804013 ± 0.004247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983725 ± 0.001724</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUS/SMOTE + ENN + PCA4 + KNN</t>
   </si>
   <si>
+    <t xml:space="preserve">0.989538 ± 0.000804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989512 ± 0.000808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989494 ± 0.000803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989000 ± 0.000882 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989072 ± 0.000865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989006 ± 0.000869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988731 ± 0.000867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997501 ± 0.000164</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUS/SMOTE + ENN + PCA4 + Logistic Regression</t>
   </si>
   <si>
-    <t xml:space="preserve">RUS/SMOTE + ENN + PCA4 + SVM</t>
+    <t xml:space="preserve">0.544799 ± 0.019849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538258 ± 0.022955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516132 ± 0.020815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530277 ± 0.021688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543483 ± 0.019082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511733 ± 0.019666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513974 ± 0.021501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.898833 ± 0.001874 </t>
   </si>
   <si>
     <t xml:space="preserve">RUS/SMOTE + ENN + PCA4 + MLP</t>
   </si>
   <si>
+    <t xml:space="preserve">0.870108 ± 0.007763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889796 ± 0.010851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860209 ± 0.009683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880297 ± 0.013872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857686 ± 0.008532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844756 ± 0.012759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862313 ± 0.008312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989935 ± 0.001167</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA4 + KNN</t>
   </si>
   <si>
+    <t xml:space="preserve">0.994210 ± 0.000283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994205 ± 0.000290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994200 ± 0.000285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993844 ± 0.000324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993636 ± 0.000448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993731 ± 0.000384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993760 ± 0.000306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998595 ± 0.000099</t>
+  </si>
+  <si>
     <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA4 + Logistic Regression</t>
   </si>
   <si>
-    <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA4 + SVM</t>
+    <t xml:space="preserve">0.505476 ± 0.018710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533130 ± 0.015803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480020 ± 0.019237 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517856 ± 0.015697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492066 ± 0.017530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466882 ± 0.018453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473179 ± 0.019621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896051 ± 0.006005</t>
   </si>
   <si>
     <t xml:space="preserve">NearMiss/SMOTE + ENN + PCA4 + MLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844365 ± 0.002965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882828 ± 0.002619 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.837768 ± 0.003225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870813 ± 0.002574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836126 ± 0.003035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827704 ± 0.003207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.836279 ± 0.003146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988048 ± 0.001281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.885009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.724868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.971047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.959732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.994085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.211344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.201434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.204746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.202750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.845458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.928609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.241613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.223220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.215866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.187273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.195647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.198577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686384</t>
   </si>
   <si>
     <t xml:space="preserve">CIC17__clean_dataset_v1.ipynb</t>
@@ -549,9 +1206,6 @@
     <t xml:space="preserve">Heartbleed</t>
   </si>
   <si>
-    <t xml:space="preserve">AUC-ROC</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.992326 ± 0.000240</t>
   </si>
   <si>
@@ -1230,398 +1884,6 @@
     <t xml:space="preserve">0.239928</t>
   </si>
   <si>
-    <t xml:space="preserve">MODELOS GENERADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análisis inicial de los datos básicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17_analisis_estadistico_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análisis estadístico de los datos:
-- N.º de filas.
-- N.º de columnas.
-- Distribución de clases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17_preprocessing_cleanning_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limpieza de los datos básica:
-- Homogeneización de nombres de columnas (ABCD_EFGH).
-- Eliminación de columnas inútiles (FLOW_ID, SRC_IP, SRC_PORT, DST_IP).
-- Codificación de columnas de tipo string.
-- Eliminación de columnas con valores únicos.
-- Eliminación de columnas con alta correlación &gt; 0.95.
-- Eliminación de valores infinito, vacío y nulo.
-- Eliminación de filas duplicadas.
-- Codificación de la etiqueta label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__cleanning__v1.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17_analisis_estadistico_v2.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__cleanning__v1_division_80_20_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dividir el dataset en dos datasets de forma stratified. La división es 80% para trainning y 20% para test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- BCCC17__sin_balanceo__v1__train.csv
-- BCCC17__sin_balanceo__v1__test.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIN BALANCEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divide el dataset en 5 particiones iguales de forma stratified. Además, convierte el dataset a string.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__train.csv
-BCCC17__sin_balanceo__v1__test.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__sin_balanceo__v1__train.csv
-pd_BCCC17__sin_balanceo__v1__test.csv
-pd_BCCC17__sin_balanceo__v1__train__1.csv
-pd_BCCC17__sin_balanceo__v1__val__1.csv
-pd_BCCC17__sin_balanceo__v1__train__2.csv
-pd_BCCC17__sin_balanceo__v1__val__2.csv
-pd_BCCC17__sin_balanceo__v1__train__3.csv
-pd_BCCC17__sin_balanceo__v1__val__3.csv
-pd_BCCC17__sin_balanceo__v1__train__4.csv
-pd_BCCC17__sin_balanceo__v1__val__4.csv
-pd_BCCC17__sin_balanceo__v1__train__5.csv
-Pd_BCCC17__sin_balanceo__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__ENN_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar la técnica ENN.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__ENN__v1__train.csv
-BCCC17__ENN__v1__test.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__ENN__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__ENN__v1__train.csv
-pd_BCCC17__ENN__v1__test.csv
-pd_BCCC17__ENN__v1__train__1.csv
-pd_BCCC17__ENN__v1__val__1.csv
-pd_BCCC17__ENN__v1__train__2.csv
-pd_BCCC17__ENN__v1__val__2.csv
-pd_BCCC17__ENN__v1__train__3.csv
-pd_BCCC17__ENN__v1__val__3.csv
-pd_BCCC17__ENN__v1__train__4.csv
-pd_BCCC17__ENN__v1__val__4.csv
-pd_BCCC17__ENN__v1__train__5.csv
-Pd_BCCC17__ENN__v1__val_₅.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__RUS_SMOTE_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicar la técnica RUS/SMOTE. Todo lo que este por encima de 10000 hacemos RUS y lo que este por debajo hacemos SMOTE. Hacemos dos test: uno con los datos que sobran (test_nuevo) y otro que sea el test original (test)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__train.csv
-BCCC17__RUS_SMOTE__v1__test.csv
-BCCC17__RUS_SMOTE__v1__test_nuevo.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__train.csv
-pd_BCCC17__RUS_SMOTE__v1__test.csv
-pd_BCCC17__RUS_SMOTE__v1__test_nuevo.csv
-pd_BCCC17__RUS_SMOTE__v1__train__1.csv
-pd_BCCC17__RUS_SMOTE__v1__val__1.csv
-pd_BCCC17__RUS_SMOTE__v1__train__2.csv
-pd_BCCC17__RUS_SMOTE__v1__val__2.csv
-pd_BCCC17__RUS_SMOTE__v1__train__3.csv
-pd_BCCC17__RUS_SMOTE__v1__val__3.csv
-pd_BCCC17__RUS_SMOTE__v1__train__4.csv
-pd_BCCC17__RUS_SMOTE__v1__val__4.csv
-pd_BCCC17__RUS_SMOTE__v1__train__5.csv
-Pd_BCCC17__RUS_SMOTE__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__training_v1__1_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__training_v1__2_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__training_v1__3_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__training_v1__4_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__training_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrenamiento con Simple T5.
-source_max_token_len=150,              
-target_max_token_len=3,             
-batch_size=16,             
-precision=32,             
-max_epochs=10,             
-use_gpu=True,             
-dataloader_num_workers=16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__train__1.csv
-pd_BCCC17__RUS_SMOTE__v1__train__2.csv
-pd_BCCC17__RUS_SMOTE__v1__train__3.csv
-pd_BCCC17__RUS_SMOTE__v1__train__4.csv
-pd_BCCC17__RUS_SMOTE__v1__train__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__outputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__1_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__2_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__3_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__4_5.ipynb
-pd_BCCC17__RUS_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validación de cada epoch y elección del mejor epoch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pd_BCCC17__RUS_SMOTE__v1__train__1.csv
-pd_BCCC17__RUS_SMOTE__v1__val__1.csv
-pd_BCCC17__RUS_SMOTE__v1__train__2.csv
-pd_BCCC17__RUS_SMOTE__v1__val__2.csv
-pd_BCCC17__RUS_SMOTE__v1__train__3.csv
-pd_BCCC17__RUS_SMOTE__v1__val__3.csv
-pd_BCCC17__RUS_SMOTE__v1__train__4.csv
-pd_BCCC17__RUS_SMOTE__v1__val__4.csv
-pd_BCCC17__RUS_SMOTE__v1__train__5.csv
-Pd_BCCC17__RUS_SMOTE__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__ENN_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE__v1__train.csv BCCC17__RUS_SMOTE__v1__test.csv BCCC17__RUS_SMOTE__v1__test_nuevo.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE_ENN__v1__train.csv BCCC17__RUS_SMOTE_ENN__v1__test.csv BCCC17__RUS_SMOTE_ENN__v1__test_nuevo.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__RUS_SMOTE_ENN__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__train.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__test.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__test_nuevo.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__1.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__2.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__2.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__3.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__3.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__4.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv
-Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__1_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__2_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__3_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__4_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__2.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__3.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__outputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
-pd_BCCC17__RUS_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__1.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__1.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__2.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__2.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__3.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__3.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__4.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__val__4.csv
-pd_BCCC17__RUS_SMOTE_ENN__v1__train__5.csv
-Pd_BCCC17__RUS_SMOTE_ENN__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__sin_balanceo__v1__NearMiss_SMOTE_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__train.csv
-BCCC17__NearMiss_SMOTE__v1__test.csv
-BCCC17__NearMiss_SMOTE__v1__test_nuevo.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__train.csv
-pd_BCCC17__NearMiss_SMOTE__v1__test.csv
-pd_BCCC17__NearMiss_SMOTE__v1__test_nuevo.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__1.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__2.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__2.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__3.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__3.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__4.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__4.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__5.csv
-Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__1_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__training_v1__2_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__training_v1__3_5.ipynb
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Cascadia Code PL"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__training_v1__4_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__training_v1__5_5.ipynb</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__2.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__3.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__4.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__outputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__1_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__2_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__3_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__4_5.ipynb
-pd_BCCC17__NearMiss_SMOTE__v1__validation_epochs_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pd_BCCC17__NearMiss_SMOTE__v1__train__1.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__1.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__2.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__2.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__3.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__3.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__4.csv
-pd_BCCC17__NearMiss_SMOTE__v1__val__4.csv
-pd_BCCC17__NearMiss_SMOTE__v1__train__5.csv
-Pd_BCCC17__NearMiss_SMOTE__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__ENN_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__NearMiss_SMOTE__v1__train.csv BCCC17__NearMiss_SMOTE__v1__test.csv BCCC17__NearMiss_SMOTE__v1__test_nuevo.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__NearMiss_SMOTE_ENN__v1__train.csv BCCC17__NearMiss_SMOTE_ENN__v1__test.csv BCCC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCCC17__NearMiss_SMOTE_ENN__v1__transformar_v1.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__train.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__test.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__test_nuevo.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__1.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__2.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__3.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__3.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__4.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__4.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv
-Pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__1_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__2_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__3_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__4_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__training_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__3.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__4.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__outputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__1_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__2_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__3_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__4_5.ipynb
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__validation_epochs_v1__5_5.ipynb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__1.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__1.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__2.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__2.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__3.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__3.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__4.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__4.csv
-pd_BCCC17__NearMiss_SMOTE_ENN__v1__train__5.csv
-Pd_BCCC17__NearMiss_SMOTE_ENN__v1__val__5.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">ORIGINAL (BCCC17)</t>
   </si>
   <si>
@@ -1806,6 +2068,15 @@
   </si>
   <si>
     <t xml:space="preserve">0.580192 ± 0.054245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531145 ± 0.049220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520565 ± 0.042029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899143 ± 0.018832</t>
   </si>
   <si>
     <t xml:space="preserve">0.996078</t>
@@ -1983,7 +2254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2052,23 +2323,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FFC9211E"/>
-      <name val="Cascadia Code PL"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color rgb="FFC9211E"/>
-      <name val="Cascadia Code PL"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2084,7 +2340,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2099,14 +2355,8 @@
         <bgColor rgb="FF81D41A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="23">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -2233,41 +2483,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="hair"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right/>
-      <top/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="hair"/>
-      <top/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2294,7 +2509,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2523,6 +2738,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2603,138 +2826,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2745,10 +2836,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2785,7 +2872,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -2796,7 +2883,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -2814,7 +2901,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -3436,7 +3523,7 @@
       <c r="E34" s="34"/>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
         <v>58</v>
       </c>
@@ -3486,7 +3573,7 @@
       <c r="E38" s="34"/>
       <c r="F38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
         <v>64</v>
       </c>
@@ -3531,8 +3618,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3542,20 +3629,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD82"/>
+  <dimension ref="A1:XFD72"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="35" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="35" width="31.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="43.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="21.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="28.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="31.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.59"/>
   </cols>
   <sheetData>
     <row r="1" s="39" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4223,7 +4310,7 @@
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="35"/>
     </row>
-    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -4254,474 +4341,736 @@
       <c r="J24" s="55" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="35"/>
+        <v>102</v>
+      </c>
+      <c r="C25" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="J25" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" s="57" t="s">
+        <v>110</v>
+      </c>
       <c r="L25" s="35"/>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="35"/>
+        <v>111</v>
+      </c>
+      <c r="C26" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="57" t="s">
+        <v>119</v>
+      </c>
       <c r="L26" s="35"/>
     </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="35"/>
+        <v>120</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="57" t="s">
+        <v>128</v>
+      </c>
       <c r="L27" s="35"/>
     </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="35"/>
+        <v>129</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" s="57" t="s">
+        <v>134</v>
+      </c>
       <c r="L28" s="35"/>
     </row>
-    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="35"/>
+        <v>135</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="57" t="s">
+        <v>140</v>
+      </c>
       <c r="L29" s="35"/>
     </row>
     <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="35"/>
+        <v>141</v>
+      </c>
+      <c r="C30" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="J30" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30" s="57" t="s">
+        <v>146</v>
+      </c>
       <c r="L30" s="35"/>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="35"/>
+        <v>147</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="H31" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="I31" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="J31" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="K31" s="57" t="s">
+        <v>152</v>
+      </c>
       <c r="L31" s="35"/>
     </row>
-    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="35"/>
+        <v>153</v>
+      </c>
+      <c r="C32" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="E32" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="F32" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="I32" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="J32" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="K32" s="57" t="s">
+        <v>159</v>
+      </c>
       <c r="L32" s="35"/>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="35"/>
+        <v>160</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="K33" s="58" t="s">
+        <v>165</v>
+      </c>
       <c r="L33" s="35"/>
     </row>
-    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="35"/>
+        <v>166</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="G34" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="J34" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="58" t="s">
+        <v>174</v>
+      </c>
       <c r="L34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="35"/>
+        <v>175</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="J35" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="K35" s="58" t="s">
+        <v>183</v>
+      </c>
       <c r="L35" s="35"/>
     </row>
-    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="35"/>
+        <v>184</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="J36" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="K36" s="58" t="s">
+        <v>192</v>
+      </c>
       <c r="L36" s="35"/>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="35"/>
+        <v>193</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="J37" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="K37" s="58" t="s">
+        <v>201</v>
+      </c>
       <c r="L37" s="35"/>
     </row>
-    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="35"/>
+        <v>202</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="G38" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="H38" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="J38" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="K38" s="58" t="s">
+        <v>210</v>
+      </c>
       <c r="L38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="35"/>
+        <v>211</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="H39" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="K39" s="58" t="s">
+        <v>219</v>
+      </c>
       <c r="L39" s="35"/>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B40" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="59"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
     </row>
-    <row r="41" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B41" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="59"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="60"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
     </row>
-    <row r="42" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B42" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="59"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="60"/>
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
     </row>
-    <row r="43" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B43" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="59"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="60"/>
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
     </row>
-    <row r="44" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B44" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="60"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="57"/>
-      <c r="B45" s="57"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="58"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="57"/>
-      <c r="B46" s="57"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="58"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="57"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="58"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="57"/>
-      <c r="B48" s="57"/>
-      <c r="C48" s="57"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="58"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="60"/>
+      <c r="K48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="57"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="58"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="35"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="57"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="58"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="58"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="57"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="58"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="57"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="58"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="42"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="42"/>
@@ -4734,6 +5083,7 @@
       <c r="H54" s="42"/>
       <c r="I54" s="42"/>
       <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="42"/>
@@ -4746,6 +5096,7 @@
       <c r="H55" s="42"/>
       <c r="I55" s="42"/>
       <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
     </row>
     <row r="56" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
@@ -4758,426 +5109,575 @@
       <c r="H56" s="42"/>
       <c r="I56" s="42"/>
       <c r="J56" s="35"/>
-    </row>
-    <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="35"/>
+      <c r="K56" s="35"/>
+    </row>
+    <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="H57" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I57" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J57" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="K57" s="55" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="42"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="35"/>
+      <c r="A58" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="F58" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="G58" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="H58" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="I58" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="J58" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="K58" s="57" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="35"/>
+      <c r="A59" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="E59" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="F59" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="G59" s="57" t="s">
+        <v>231</v>
+      </c>
+      <c r="H59" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="I59" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="J59" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="K59" s="57" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-      <c r="J60" s="35"/>
+      <c r="A60" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D60" s="57" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="F60" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="G60" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="H60" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="I60" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="J60" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="K60" s="57" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="42"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="42"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
-      <c r="J61" s="35"/>
+      <c r="A61" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="D61" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="E61" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="F61" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="G61" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="H61" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="I61" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="J61" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="K61" s="57" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="B62" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="D62" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="E62" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="F62" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="G62" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="H62" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="I62" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="J62" s="55" t="s">
-        <v>100</v>
+      <c r="A62" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B62" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C62" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="D62" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="E62" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="F62" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="G62" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="H62" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="I62" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="J62" s="57" t="s">
+        <v>258</v>
+      </c>
+      <c r="K62" s="57" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
+        <v>141</v>
+      </c>
+      <c r="C63" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="D63" s="57" t="s">
+        <v>261</v>
+      </c>
+      <c r="E63" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="F63" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="G63" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="H63" s="57" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" s="57" t="s">
+        <v>265</v>
+      </c>
+      <c r="J63" s="57" t="s">
+        <v>266</v>
+      </c>
+      <c r="K63" s="57" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="42"/>
-    </row>
-    <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+      <c r="C64" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="D64" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="E64" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="F64" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="G64" s="57" t="s">
+        <v>271</v>
+      </c>
+      <c r="H64" s="57" t="s">
+        <v>272</v>
+      </c>
+      <c r="I64" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="J64" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="K64" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C65" s="57"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="57"/>
-      <c r="J65" s="58"/>
+        <v>153</v>
+      </c>
+      <c r="C65" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="D65" s="58" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F65" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="G65" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H65" s="58" t="s">
+        <v>280</v>
+      </c>
+      <c r="I65" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="J65" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="K65" s="58" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42"/>
-      <c r="I66" s="42"/>
-      <c r="J66" s="42"/>
+        <v>160</v>
+      </c>
+      <c r="C66" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="58" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="F66" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="G66" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="H66" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="I66" s="58" t="s">
+        <v>289</v>
+      </c>
+      <c r="J66" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="K66" s="58" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="42"/>
-      <c r="J67" s="42"/>
-    </row>
-    <row r="68" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="C67" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="D67" s="58" t="s">
+        <v>293</v>
+      </c>
+      <c r="E67" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="F67" s="58" t="s">
+        <v>294</v>
+      </c>
+      <c r="G67" s="58" t="s">
+        <v>295</v>
+      </c>
+      <c r="H67" s="58" t="s">
+        <v>296</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>297</v>
+      </c>
+      <c r="J67" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="K67" s="58" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-      <c r="J68" s="42"/>
+        <v>175</v>
+      </c>
+      <c r="C68" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="D68" s="58" t="s">
+        <v>301</v>
+      </c>
+      <c r="E68" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="F68" s="58" t="s">
+        <v>302</v>
+      </c>
+      <c r="G68" s="58" t="s">
+        <v>303</v>
+      </c>
+      <c r="H68" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="I68" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="J68" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="K68" s="58" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
-      <c r="I69" s="42"/>
-      <c r="J69" s="42"/>
+        <v>184</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" s="58" t="s">
+        <v>309</v>
+      </c>
+      <c r="E69" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="F69" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="G69" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="H69" s="58" t="s">
+        <v>312</v>
+      </c>
+      <c r="I69" s="58" t="s">
+        <v>313</v>
+      </c>
+      <c r="J69" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="K69" s="58" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-    </row>
-    <row r="71" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>193</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70" s="58" t="s">
+        <v>317</v>
+      </c>
+      <c r="E70" s="58" t="s">
+        <v>316</v>
+      </c>
+      <c r="F70" s="58" t="s">
+        <v>318</v>
+      </c>
+      <c r="G70" s="58" t="s">
+        <v>319</v>
+      </c>
+      <c r="H70" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="I70" s="58" t="s">
+        <v>321</v>
+      </c>
+      <c r="J70" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="K70" s="58" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C71" s="42"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-      <c r="J71" s="42"/>
-    </row>
-    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>202</v>
+      </c>
+      <c r="C71" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="D71" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="E71" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="F71" s="58" t="s">
+        <v>326</v>
+      </c>
+      <c r="G71" s="58" t="s">
+        <v>327</v>
+      </c>
+      <c r="H71" s="58" t="s">
+        <v>328</v>
+      </c>
+      <c r="I71" s="58" t="s">
+        <v>329</v>
+      </c>
+      <c r="J71" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="K71" s="58" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C72" s="42"/>
-      <c r="D72" s="42"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="42"/>
-      <c r="H72" s="42"/>
-      <c r="I72" s="42"/>
-      <c r="J72" s="42"/>
-    </row>
-    <row r="73" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="56" t="n">
-        <v>11</v>
-      </c>
-      <c r="B73" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C73" s="42"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="42"/>
-      <c r="J73" s="42"/>
-    </row>
-    <row r="74" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="56" t="n">
-        <v>12</v>
-      </c>
-      <c r="B74" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C74" s="42"/>
-      <c r="D74" s="42"/>
-      <c r="E74" s="42"/>
-      <c r="F74" s="42"/>
-      <c r="G74" s="42"/>
-      <c r="H74" s="42"/>
-      <c r="I74" s="42"/>
-      <c r="J74" s="42"/>
-    </row>
-    <row r="75" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="56" t="n">
-        <v>13</v>
-      </c>
-      <c r="B75" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C75" s="42"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="42"/>
-      <c r="H75" s="42"/>
-      <c r="I75" s="42"/>
-      <c r="J75" s="42"/>
-    </row>
-    <row r="76" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="56" t="n">
-        <v>14</v>
-      </c>
-      <c r="B76" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="42"/>
-      <c r="H76" s="42"/>
-      <c r="I76" s="42"/>
-      <c r="J76" s="42"/>
-    </row>
-    <row r="77" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="56" t="n">
-        <v>15</v>
-      </c>
-      <c r="B77" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="42"/>
-      <c r="H77" s="42"/>
-      <c r="I77" s="42"/>
-      <c r="J77" s="42"/>
-    </row>
-    <row r="78" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="56" t="n">
-        <v>16</v>
-      </c>
-      <c r="B78" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="42"/>
-      <c r="D78" s="42"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
-      <c r="H78" s="42"/>
-      <c r="I78" s="42"/>
-      <c r="J78" s="42"/>
-    </row>
-    <row r="79" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="56" t="n">
-        <v>17</v>
-      </c>
-      <c r="B79" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="42"/>
-    </row>
-    <row r="80" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="56" t="n">
-        <v>18</v>
-      </c>
-      <c r="B80" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="42"/>
-      <c r="D80" s="42"/>
-      <c r="E80" s="42"/>
-      <c r="F80" s="42"/>
-      <c r="G80" s="42"/>
-      <c r="H80" s="42"/>
-      <c r="I80" s="42"/>
-      <c r="J80" s="42"/>
-    </row>
-    <row r="81" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="56" t="n">
-        <v>19</v>
-      </c>
-      <c r="B81" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C81" s="42"/>
-      <c r="D81" s="42"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="42"/>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42"/>
-      <c r="I81" s="42"/>
-      <c r="J81" s="42"/>
-    </row>
-    <row r="82" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="56" t="n">
-        <v>20</v>
-      </c>
-      <c r="B82" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C82" s="42"/>
-      <c r="D82" s="42"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="42"/>
-      <c r="H82" s="42"/>
-      <c r="I82" s="42"/>
-      <c r="J82" s="42"/>
+        <v>211</v>
+      </c>
+      <c r="C72" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="D72" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="F72" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="G72" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="H72" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="I72" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="J72" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="K72" s="58" t="s">
+        <v>339</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5198,7 +5698,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="71.46"/>
   </cols>
   <sheetData>
-    <row r="1" s="60" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="62" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5217,48 +5717,48 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>121</v>
+        <v>340</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>122</v>
+        <v>341</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>123</v>
+        <v>342</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
     </row>
     <row r="3" customFormat="false" ht="135.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>124</v>
+        <v>343</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>123</v>
+        <v>342</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" customFormat="false" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12"/>
@@ -5267,26 +5767,26 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
     </row>
     <row r="5" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>126</v>
+        <v>345</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>127</v>
+        <v>346</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
     </row>
     <row r="6" customFormat="false" ht="23.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17"/>
@@ -5295,26 +5795,26 @@
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
     </row>
     <row r="7" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>128</v>
+        <v>347</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>127</v>
+        <v>346</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17"/>
@@ -5323,26 +5823,26 @@
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="20"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
     </row>
     <row r="9" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>129</v>
+        <v>348</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>127</v>
+        <v>346</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
     </row>
     <row r="10" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17"/>
@@ -5351,28 +5851,28 @@
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>130</v>
+        <v>349</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>131</v>
+        <v>350</v>
       </c>
       <c r="F11" s="24"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25"/>
@@ -5381,26 +5881,26 @@
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="118" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>132</v>
+        <v>351</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>133</v>
+        <v>352</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="32"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33"/>
@@ -5409,26 +5909,26 @@
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="111.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>133</v>
+        <v>352</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="32"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
     </row>
     <row r="16" s="12" customFormat="true" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33"/>
@@ -5437,67 +5937,67 @@
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
     </row>
     <row r="17" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>135</v>
+        <v>354</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>133</v>
+        <v>352</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
     </row>
     <row r="19" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>136</v>
+        <v>355</v>
       </c>
       <c r="C19" s="30" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>137</v>
+        <v>356</v>
       </c>
       <c r="F19" s="32"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
     </row>
     <row r="21" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>138</v>
+        <v>357</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="E21" s="30"/>
       <c r="F21" s="32"/>
@@ -5512,13 +6012,13 @@
         <v>43</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="32"/>
@@ -5531,57 +6031,57 @@
         <v>45</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>142</v>
+        <v>361</v>
       </c>
       <c r="C27" s="30" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>143</v>
+        <v>362</v>
       </c>
       <c r="F27" s="32"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
         <v>51</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>144</v>
+        <v>363</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>145</v>
+        <v>364</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="32"/>
@@ -5596,13 +6096,13 @@
         <v>54</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>146</v>
+        <v>365</v>
       </c>
       <c r="C31" s="31" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>145</v>
+        <v>364</v>
       </c>
       <c r="E31" s="30"/>
       <c r="F31" s="32"/>
@@ -5615,172 +6115,172 @@
         <v>56</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>147</v>
+        <v>366</v>
       </c>
       <c r="C33" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>145</v>
+        <v>364</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="32"/>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
     </row>
     <row r="35" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>148</v>
+        <v>367</v>
       </c>
       <c r="C35" s="30" t="s">
         <v>49</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>149</v>
+        <v>368</v>
       </c>
       <c r="F35" s="32"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
     </row>
     <row r="37" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
         <v>61</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>150</v>
+        <v>369</v>
       </c>
       <c r="C37" s="31" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>151</v>
+        <v>370</v>
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="32"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
     </row>
     <row r="39" customFormat="false" ht="88.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
         <v>64</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>152</v>
+        <v>371</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>151</v>
+        <v>370</v>
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="32"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="33"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
     </row>
     <row r="41" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
         <v>66</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>153</v>
+        <v>372</v>
       </c>
       <c r="C41" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>151</v>
+        <v>370</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="32"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G51" s="61"/>
-      <c r="H51" s="61"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G53" s="61"/>
-      <c r="H53" s="61"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G54" s="61"/>
-      <c r="H54" s="61"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5807,49 +6307,49 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="35" width="15.57"/>
   </cols>
   <sheetData>
-    <row r="1" s="69" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
+    <row r="1" s="71" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="D1" s="64" t="s">
+      <c r="C1" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="66" t="s">
+      <c r="E1" s="67" t="s">
+        <v>374</v>
+      </c>
+      <c r="F1" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="68"/>
+      <c r="J1" s="70"/>
       <c r="XFC1" s="1"/>
       <c r="XFD1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="70" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="71" t="n">
+      <c r="B2" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="71" t="n">
+      <c r="C2" s="73" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="72" t="n">
+      <c r="D2" s="74" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="42" t="n">
@@ -5870,17 +6370,17 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="70" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="71" t="n">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72" t="s">
+        <v>375</v>
+      </c>
+      <c r="B3" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="71" t="n">
+      <c r="C3" s="73" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="72" t="n">
+      <c r="D3" s="74" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="42" t="n">
@@ -5901,17 +6401,17 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="71" t="n">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="72" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="71" t="n">
+      <c r="C4" s="73" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="72" t="n">
+      <c r="D4" s="74" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="42" t="n">
@@ -5932,17 +6432,17 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="71" t="n">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="72" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="71" t="n">
+      <c r="C5" s="73" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="72" t="n">
+      <c r="D5" s="74" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="42" t="n">
@@ -5963,17 +6463,17 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="70" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="71" t="n">
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="72" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="71" t="n">
+      <c r="C6" s="73" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="72" t="n">
+      <c r="D6" s="74" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -5994,17 +6494,17 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="70" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="71" t="n">
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="72" t="s">
+        <v>379</v>
+      </c>
+      <c r="B7" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="71" t="n">
+      <c r="C7" s="73" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="72" t="n">
+      <c r="D7" s="74" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -6025,17 +6525,17 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="71" t="n">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="72" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="71" t="n">
+      <c r="C8" s="73" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="72" t="n">
+      <c r="D8" s="74" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="42" t="n">
@@ -6056,17 +6556,17 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="B9" s="71" t="n">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="72" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="71" t="n">
+      <c r="C9" s="73" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="72" t="n">
+      <c r="D9" s="74" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="42" t="n">
@@ -6087,17 +6587,17 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="71" t="n">
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="72" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" s="73" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="71" t="n">
+      <c r="C10" s="73" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="72" t="n">
+      <c r="D10" s="74" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="42" t="n">
@@ -6118,17 +6618,17 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="70" t="s">
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="71" t="n">
+      <c r="B11" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="71" t="n">
+      <c r="C11" s="73" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="72" t="n">
+      <c r="D11" s="74" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="42" t="n">
@@ -6149,17 +6649,17 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="71" t="n">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="72" t="s">
+        <v>383</v>
+      </c>
+      <c r="B12" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="71" t="n">
+      <c r="C12" s="73" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="72" t="n">
+      <c r="D12" s="74" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="42" t="n">
@@ -6180,17 +6680,17 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="71" t="n">
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="72" t="s">
+        <v>384</v>
+      </c>
+      <c r="B13" s="73" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="71" t="n">
+      <c r="C13" s="73" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="72" t="n">
+      <c r="D13" s="74" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="42" t="n">
@@ -6211,17 +6711,17 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="B14" s="71" t="n">
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="72" t="s">
+        <v>385</v>
+      </c>
+      <c r="B14" s="73" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="71" t="n">
+      <c r="C14" s="73" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="72" t="n">
+      <c r="D14" s="74" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="42" t="n">
@@ -6242,17 +6742,17 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" s="71" t="n">
+    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="72" t="s">
+        <v>386</v>
+      </c>
+      <c r="B15" s="73" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="71" t="n">
+      <c r="C15" s="73" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="72" t="n">
+      <c r="D15" s="74" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="42" t="n">
@@ -6273,17 +6773,17 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="73" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" s="74" t="n">
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="75" t="s">
+        <v>387</v>
+      </c>
+      <c r="B16" s="76" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="74" t="n">
+      <c r="C16" s="76" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="74" t="n">
+      <c r="D16" s="76" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="49" t="n">
@@ -6304,7 +6804,7 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="42" t="n">
         <f aca="false">SUM(C2:C16)</f>
         <v>2830743</v>
@@ -6337,19 +6837,19 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="75"/>
+      <c r="E18" s="77"/>
       <c r="I18" s="35"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="75"/>
+      <c r="E19" s="77"/>
       <c r="I19" s="35"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="76" t="s">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="78" t="s">
         <v>90</v>
       </c>
       <c r="C20" s="42" t="n">
@@ -6386,7 +6886,7 @@
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L25" s="1"/>
     </row>
-    <row r="26" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="54" t="s">
         <v>91</v>
       </c>
@@ -6418,645 +6918,645 @@
         <v>100</v>
       </c>
       <c r="K26" s="55" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>170</v>
+        <v>388</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>171</v>
+        <v>389</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>170</v>
+        <v>388</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>172</v>
+        <v>390</v>
       </c>
       <c r="G27" s="42" t="s">
-        <v>173</v>
+        <v>391</v>
       </c>
       <c r="H27" s="42" t="s">
-        <v>174</v>
+        <v>392</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>175</v>
+        <v>393</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="K27" s="77" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>394</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="28" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>178</v>
+        <v>396</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>179</v>
+        <v>397</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>178</v>
+        <v>396</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>180</v>
+        <v>398</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>181</v>
+        <v>399</v>
       </c>
       <c r="H28" s="42" t="s">
-        <v>182</v>
+        <v>400</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>183</v>
+        <v>401</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="K28" s="77" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="29" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>402</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>187</v>
+        <v>405</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>188</v>
+        <v>406</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>189</v>
+        <v>407</v>
       </c>
       <c r="H29" s="42" t="s">
-        <v>190</v>
+        <v>408</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>191</v>
+        <v>409</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="K29" s="77" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="30" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>410</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="30" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>194</v>
+        <v>412</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>195</v>
+        <v>413</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>196</v>
+        <v>414</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>197</v>
+        <v>415</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>198</v>
+        <v>416</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>194</v>
+        <v>412</v>
       </c>
       <c r="I30" s="42" t="s">
-        <v>197</v>
+        <v>415</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="K30" s="77" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="31" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>417</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>201</v>
+        <v>419</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>202</v>
+        <v>420</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>201</v>
+        <v>419</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>203</v>
+        <v>421</v>
       </c>
       <c r="G31" s="42" t="s">
-        <v>202</v>
+        <v>420</v>
       </c>
       <c r="H31" s="42" t="s">
-        <v>201</v>
+        <v>419</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>204</v>
+        <v>422</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="K31" s="77" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="32" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="32" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>207</v>
+        <v>425</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>208</v>
+        <v>426</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>207</v>
+        <v>425</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>209</v>
+        <v>427</v>
       </c>
       <c r="G32" s="42" t="s">
-        <v>208</v>
+        <v>426</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>207</v>
+        <v>425</v>
       </c>
       <c r="I32" s="42" t="s">
-        <v>209</v>
+        <v>427</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="K32" s="77" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="33" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>212</v>
+        <v>430</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>213</v>
+        <v>431</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>212</v>
+        <v>430</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>214</v>
+        <v>432</v>
       </c>
       <c r="G33" s="42" t="s">
-        <v>213</v>
+        <v>431</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>212</v>
+        <v>430</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>214</v>
+        <v>432</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="K33" s="77" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>433</v>
+      </c>
+      <c r="K33" s="42" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="34" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>217</v>
+        <v>435</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>218</v>
+        <v>436</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>219</v>
+        <v>437</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>220</v>
+        <v>438</v>
       </c>
       <c r="G34" s="42" t="s">
-        <v>218</v>
+        <v>436</v>
       </c>
       <c r="H34" s="42" t="s">
-        <v>219</v>
+        <v>437</v>
       </c>
       <c r="I34" s="42" t="s">
-        <v>220</v>
+        <v>438</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="K34" s="77" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>439</v>
+      </c>
+      <c r="K34" s="42" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="35" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>223</v>
+        <v>441</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>224</v>
+        <v>442</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>225</v>
+        <v>443</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>226</v>
+        <v>444</v>
       </c>
       <c r="G35" s="42" t="s">
-        <v>224</v>
+        <v>442</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>225</v>
+        <v>443</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>226</v>
+        <v>444</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="K35" s="77" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="36" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>445</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="36" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>229</v>
+        <v>447</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>230</v>
+        <v>448</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>231</v>
+        <v>449</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>232</v>
+        <v>450</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>233</v>
+        <v>451</v>
       </c>
       <c r="H36" s="42" t="s">
-        <v>234</v>
+        <v>452</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>235</v>
+        <v>453</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="K36" s="77" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="37" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+      <c r="K36" s="42" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="37" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>238</v>
+        <v>456</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>239</v>
+        <v>457</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>238</v>
+        <v>456</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>240</v>
+        <v>458</v>
       </c>
       <c r="G37" s="42" t="s">
-        <v>241</v>
+        <v>459</v>
       </c>
       <c r="H37" s="42" t="s">
-        <v>242</v>
+        <v>460</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>243</v>
+        <v>461</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="K37" s="77" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="38" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="38" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>246</v>
+        <v>464</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>247</v>
+        <v>465</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>246</v>
+        <v>464</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>248</v>
+        <v>466</v>
       </c>
       <c r="G38" s="42" t="s">
-        <v>249</v>
+        <v>467</v>
       </c>
       <c r="H38" s="42" t="s">
-        <v>250</v>
+        <v>468</v>
       </c>
       <c r="I38" s="42" t="s">
-        <v>251</v>
+        <v>469</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="K38" s="77" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="39" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>470</v>
+      </c>
+      <c r="K38" s="42" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="39" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>254</v>
+        <v>472</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>255</v>
+        <v>473</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>254</v>
+        <v>472</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>256</v>
+        <v>474</v>
       </c>
       <c r="G39" s="42" t="s">
-        <v>257</v>
+        <v>475</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>258</v>
+        <v>476</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>259</v>
+        <v>477</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="K39" s="77" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="40" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>478</v>
+      </c>
+      <c r="K39" s="42" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>262</v>
+        <v>480</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>263</v>
+        <v>481</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>262</v>
+        <v>480</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>264</v>
+        <v>482</v>
       </c>
       <c r="G40" s="42" t="s">
-        <v>265</v>
+        <v>483</v>
       </c>
       <c r="H40" s="42" t="s">
-        <v>266</v>
+        <v>484</v>
       </c>
       <c r="I40" s="42" t="s">
-        <v>267</v>
+        <v>485</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="K40" s="77" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="41" s="35" customFormat="true" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>486</v>
+      </c>
+      <c r="K40" s="42" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="41" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>270</v>
+        <v>488</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>271</v>
+        <v>489</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>270</v>
+        <v>488</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>272</v>
+        <v>490</v>
       </c>
       <c r="G41" s="42" t="s">
-        <v>273</v>
+        <v>491</v>
       </c>
       <c r="H41" s="42" t="s">
-        <v>274</v>
+        <v>492</v>
       </c>
       <c r="I41" s="42" t="s">
-        <v>275</v>
+        <v>493</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>276</v>
-      </c>
-      <c r="K41" s="77" t="s">
-        <v>261</v>
+        <v>494</v>
+      </c>
+      <c r="K41" s="42" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="42" s="35" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="58"/>
+      <c r="A42" s="59"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="60"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="57"/>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="58"/>
+      <c r="A43" s="59"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="60"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="57"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="58"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="60"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="57"/>
-      <c r="B45" s="57"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="58"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="60"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="57"/>
-      <c r="B46" s="57"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="58"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="60"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="57"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="58"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="60"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="57"/>
-      <c r="B48" s="57"/>
-      <c r="C48" s="57"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="58"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="60"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="57"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="58"/>
+      <c r="A49" s="59"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="60"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="57"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="58"/>
-    </row>
-    <row r="59" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="59"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="60"/>
+    </row>
+    <row r="59" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="54" t="s">
         <v>91</v>
       </c>
@@ -7088,532 +7588,532 @@
         <v>100</v>
       </c>
       <c r="K59" s="55" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B60" s="56" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>277</v>
+        <v>495</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>278</v>
+        <v>496</v>
       </c>
       <c r="E60" s="42" t="s">
-        <v>277</v>
+        <v>495</v>
       </c>
       <c r="F60" s="42" t="s">
-        <v>279</v>
+        <v>497</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>280</v>
+        <v>498</v>
       </c>
       <c r="H60" s="42" t="s">
-        <v>281</v>
+        <v>499</v>
       </c>
       <c r="I60" s="42" t="s">
-        <v>282</v>
+        <v>500</v>
       </c>
       <c r="J60" s="42" t="s">
-        <v>283</v>
-      </c>
-      <c r="K60" s="77" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>501</v>
+      </c>
+      <c r="K60" s="42" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C61" s="42" t="s">
-        <v>285</v>
+        <v>503</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>286</v>
+        <v>504</v>
       </c>
       <c r="E61" s="42" t="s">
-        <v>285</v>
+        <v>503</v>
       </c>
       <c r="F61" s="42" t="s">
-        <v>287</v>
+        <v>505</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>288</v>
+        <v>506</v>
       </c>
       <c r="H61" s="42" t="s">
-        <v>289</v>
+        <v>507</v>
       </c>
       <c r="I61" s="42" t="s">
-        <v>290</v>
+        <v>508</v>
       </c>
       <c r="J61" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="K61" s="77" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>509</v>
+      </c>
+      <c r="K61" s="42" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B62" s="56" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C62" s="42" t="s">
-        <v>293</v>
+        <v>511</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>294</v>
+        <v>512</v>
       </c>
       <c r="E62" s="42" t="s">
-        <v>293</v>
+        <v>511</v>
       </c>
       <c r="F62" s="42" t="s">
-        <v>295</v>
+        <v>513</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>296</v>
+        <v>514</v>
       </c>
       <c r="H62" s="42" t="s">
-        <v>297</v>
+        <v>515</v>
       </c>
       <c r="I62" s="42" t="s">
-        <v>298</v>
+        <v>516</v>
       </c>
       <c r="J62" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="K62" s="77" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>517</v>
+      </c>
+      <c r="K62" s="42" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="C63" s="42" t="s">
-        <v>301</v>
+        <v>519</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>302</v>
+        <v>520</v>
       </c>
       <c r="E63" s="42" t="s">
-        <v>301</v>
+        <v>519</v>
       </c>
       <c r="F63" s="42" t="s">
-        <v>303</v>
+        <v>521</v>
       </c>
       <c r="G63" s="42" t="s">
-        <v>304</v>
+        <v>522</v>
       </c>
       <c r="H63" s="42" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
       <c r="I63" s="42" t="s">
-        <v>306</v>
+        <v>524</v>
       </c>
       <c r="J63" s="42" t="s">
-        <v>307</v>
-      </c>
-      <c r="K63" s="77" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>525</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C64" s="42" t="s">
-        <v>309</v>
+        <v>527</v>
       </c>
       <c r="D64" s="42" t="s">
-        <v>310</v>
+        <v>528</v>
       </c>
       <c r="E64" s="42" t="s">
-        <v>309</v>
+        <v>527</v>
       </c>
       <c r="F64" s="42" t="s">
-        <v>311</v>
+        <v>529</v>
       </c>
       <c r="G64" s="42" t="s">
-        <v>312</v>
+        <v>530</v>
       </c>
       <c r="H64" s="42" t="s">
-        <v>313</v>
+        <v>531</v>
       </c>
       <c r="I64" s="42" t="s">
-        <v>314</v>
+        <v>532</v>
       </c>
       <c r="J64" s="42" t="s">
-        <v>315</v>
-      </c>
-      <c r="K64" s="77" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>533</v>
+      </c>
+      <c r="K64" s="42" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>317</v>
+        <v>535</v>
       </c>
       <c r="D65" s="42" t="s">
-        <v>318</v>
+        <v>536</v>
       </c>
       <c r="E65" s="42" t="s">
-        <v>317</v>
+        <v>535</v>
       </c>
       <c r="F65" s="42" t="s">
-        <v>319</v>
+        <v>537</v>
       </c>
       <c r="G65" s="42" t="s">
-        <v>320</v>
+        <v>538</v>
       </c>
       <c r="H65" s="42" t="s">
-        <v>321</v>
+        <v>539</v>
       </c>
       <c r="I65" s="42" t="s">
-        <v>322</v>
+        <v>540</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>323</v>
-      </c>
-      <c r="K65" s="77" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>541</v>
+      </c>
+      <c r="K65" s="42" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>325</v>
+        <v>543</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>326</v>
+        <v>544</v>
       </c>
       <c r="E66" s="42" t="s">
-        <v>325</v>
+        <v>543</v>
       </c>
       <c r="F66" s="42" t="s">
-        <v>327</v>
+        <v>545</v>
       </c>
       <c r="G66" s="42" t="s">
-        <v>328</v>
+        <v>546</v>
       </c>
       <c r="H66" s="42" t="s">
-        <v>329</v>
+        <v>547</v>
       </c>
       <c r="I66" s="42" t="s">
-        <v>330</v>
+        <v>548</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>331</v>
-      </c>
-      <c r="K66" s="77" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>549</v>
+      </c>
+      <c r="K66" s="42" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="C67" s="42" t="s">
-        <v>333</v>
+        <v>551</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>334</v>
+        <v>552</v>
       </c>
       <c r="E67" s="42" t="s">
-        <v>333</v>
+        <v>551</v>
       </c>
       <c r="F67" s="42" t="s">
-        <v>335</v>
+        <v>553</v>
       </c>
       <c r="G67" s="42" t="s">
-        <v>336</v>
+        <v>554</v>
       </c>
       <c r="H67" s="42" t="s">
-        <v>337</v>
+        <v>555</v>
       </c>
       <c r="I67" s="42" t="s">
-        <v>338</v>
+        <v>556</v>
       </c>
       <c r="J67" s="42" t="s">
-        <v>339</v>
-      </c>
-      <c r="K67" s="77" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>557</v>
+      </c>
+      <c r="K67" s="42" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="C68" s="42" t="s">
-        <v>341</v>
+        <v>559</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>342</v>
+        <v>560</v>
       </c>
       <c r="E68" s="42" t="s">
-        <v>341</v>
+        <v>559</v>
       </c>
       <c r="F68" s="42" t="s">
-        <v>343</v>
+        <v>561</v>
       </c>
       <c r="G68" s="42" t="s">
-        <v>344</v>
+        <v>562</v>
       </c>
       <c r="H68" s="42" t="s">
-        <v>345</v>
+        <v>563</v>
       </c>
       <c r="I68" s="42" t="s">
-        <v>346</v>
+        <v>564</v>
       </c>
       <c r="J68" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="K68" s="77" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>565</v>
+      </c>
+      <c r="K68" s="42" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="C69" s="42" t="s">
-        <v>349</v>
+        <v>567</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>350</v>
+        <v>568</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>349</v>
+        <v>567</v>
       </c>
       <c r="F69" s="42" t="s">
-        <v>351</v>
+        <v>569</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>352</v>
+        <v>570</v>
       </c>
       <c r="H69" s="42" t="s">
-        <v>353</v>
+        <v>571</v>
       </c>
       <c r="I69" s="42" t="s">
-        <v>354</v>
+        <v>572</v>
       </c>
       <c r="J69" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="K69" s="77" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>573</v>
+      </c>
+      <c r="K69" s="42" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>357</v>
+        <v>575</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>358</v>
+        <v>576</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>357</v>
+        <v>575</v>
       </c>
       <c r="F70" s="42" t="s">
-        <v>359</v>
+        <v>577</v>
       </c>
       <c r="G70" s="42" t="s">
-        <v>360</v>
+        <v>578</v>
       </c>
       <c r="H70" s="42" t="s">
-        <v>361</v>
+        <v>579</v>
       </c>
       <c r="I70" s="42" t="s">
-        <v>362</v>
+        <v>580</v>
       </c>
       <c r="J70" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="K70" s="77" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>581</v>
+      </c>
+      <c r="K70" s="42" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="C71" s="42" t="s">
-        <v>365</v>
+        <v>583</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>366</v>
+        <v>584</v>
       </c>
       <c r="E71" s="42" t="s">
-        <v>365</v>
+        <v>583</v>
       </c>
       <c r="F71" s="42" t="s">
-        <v>367</v>
+        <v>585</v>
       </c>
       <c r="G71" s="42" t="s">
-        <v>368</v>
+        <v>586</v>
       </c>
       <c r="H71" s="42" t="s">
-        <v>369</v>
+        <v>587</v>
       </c>
       <c r="I71" s="42" t="s">
-        <v>370</v>
+        <v>588</v>
       </c>
       <c r="J71" s="42" t="s">
-        <v>371</v>
-      </c>
-      <c r="K71" s="77" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>589</v>
+      </c>
+      <c r="K71" s="42" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="C72" s="42" t="s">
-        <v>373</v>
+        <v>591</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>374</v>
+        <v>592</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>373</v>
+        <v>591</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>375</v>
+        <v>593</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>376</v>
+        <v>594</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>377</v>
+        <v>595</v>
       </c>
       <c r="I72" s="42" t="s">
-        <v>378</v>
+        <v>596</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="K72" s="77" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>597</v>
+      </c>
+      <c r="K72" s="42" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="C73" s="42" t="s">
-        <v>381</v>
+        <v>599</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>382</v>
+        <v>600</v>
       </c>
       <c r="E73" s="42" t="s">
-        <v>381</v>
+        <v>599</v>
       </c>
       <c r="F73" s="42" t="s">
-        <v>383</v>
+        <v>601</v>
       </c>
       <c r="G73" s="42" t="s">
-        <v>384</v>
+        <v>602</v>
       </c>
       <c r="H73" s="42" t="s">
-        <v>385</v>
+        <v>603</v>
       </c>
       <c r="I73" s="42" t="s">
-        <v>386</v>
+        <v>604</v>
       </c>
       <c r="J73" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="K73" s="77" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>605</v>
+      </c>
+      <c r="K73" s="42" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="C74" s="42" t="s">
-        <v>389</v>
+        <v>607</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>390</v>
+        <v>608</v>
       </c>
       <c r="E74" s="42" t="s">
-        <v>389</v>
+        <v>607</v>
       </c>
       <c r="F74" s="42" t="s">
-        <v>391</v>
+        <v>609</v>
       </c>
       <c r="G74" s="42" t="s">
-        <v>392</v>
+        <v>610</v>
       </c>
       <c r="H74" s="42" t="s">
-        <v>393</v>
+        <v>611</v>
       </c>
       <c r="I74" s="42" t="s">
-        <v>394</v>
+        <v>612</v>
       </c>
       <c r="J74" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="K74" s="77" t="s">
-        <v>380</v>
+        <v>613</v>
+      </c>
+      <c r="K74" s="42" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -7621,8 +8121,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -7632,745 +8132,55 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="78" width="36.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="90.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="77.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="65.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="35" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="50.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="77.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="65.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50.62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="79" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="80" t="s">
-        <v>396</v>
-      </c>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-    </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82" t="s">
-        <v>397</v>
-      </c>
-      <c r="D2" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="82" t="s">
-        <v>398</v>
-      </c>
-      <c r="F2" s="83"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-    </row>
-    <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82" t="s">
-        <v>399</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>400</v>
-      </c>
-      <c r="D3" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="82" t="s">
-        <v>398</v>
-      </c>
-      <c r="F3" s="83"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-    </row>
-    <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82" t="s">
-        <v>401</v>
-      </c>
-      <c r="C4" s="84" t="s">
-        <v>402</v>
-      </c>
-      <c r="D4" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="82" t="s">
-        <v>403</v>
-      </c>
-      <c r="F4" s="83"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-    </row>
-    <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="81"/>
-      <c r="B5" s="82" t="s">
-        <v>404</v>
-      </c>
-      <c r="C5" s="84" t="s">
-        <v>400</v>
-      </c>
-      <c r="D5" s="82" t="s">
-        <v>403</v>
-      </c>
-      <c r="E5" s="82" t="s">
-        <v>398</v>
-      </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-    </row>
-    <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81"/>
-      <c r="B6" s="82" t="s">
-        <v>405</v>
-      </c>
-      <c r="C6" s="84" t="s">
-        <v>406</v>
-      </c>
-      <c r="D6" s="82" t="s">
-        <v>403</v>
-      </c>
-      <c r="E6" s="84" t="s">
-        <v>407</v>
-      </c>
-      <c r="F6" s="83"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-    </row>
-    <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="81" t="s">
-        <v>408</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>409</v>
-      </c>
-      <c r="C7" s="86" t="s">
-        <v>410</v>
-      </c>
-      <c r="D7" s="86" t="s">
-        <v>411</v>
-      </c>
-      <c r="E7" s="86" t="s">
-        <v>412</v>
-      </c>
-      <c r="F7" s="83"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-    </row>
-    <row r="8" s="1" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="81" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>413</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>414</v>
-      </c>
-      <c r="D8" s="86" t="s">
-        <v>411</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>415</v>
-      </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" s="86" t="s">
-        <v>410</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>415</v>
-      </c>
-      <c r="E9" s="86" t="s">
-        <v>417</v>
-      </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-    </row>
-    <row r="10" s="1" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="88" t="s">
-        <v>418</v>
-      </c>
-      <c r="C10" s="89" t="s">
-        <v>419</v>
-      </c>
-      <c r="D10" s="89" t="s">
-        <v>411</v>
-      </c>
-      <c r="E10" s="89" t="s">
-        <v>420</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-    </row>
-    <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="91" t="s">
-        <v>421</v>
-      </c>
-      <c r="C11" s="92" t="s">
-        <v>410</v>
-      </c>
-      <c r="D11" s="92" t="s">
-        <v>420</v>
-      </c>
-      <c r="E11" s="92" t="s">
-        <v>422</v>
-      </c>
-      <c r="F11" s="93"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-    </row>
-    <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="92" t="s">
-        <v>423</v>
-      </c>
-      <c r="C12" s="92" t="s">
-        <v>424</v>
-      </c>
-      <c r="D12" s="92" t="s">
-        <v>425</v>
-      </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="94" t="s">
-        <v>426</v>
-      </c>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-    </row>
-    <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="92" t="s">
-        <v>427</v>
-      </c>
-      <c r="C13" s="92" t="s">
-        <v>428</v>
-      </c>
-      <c r="D13" s="92" t="s">
-        <v>429</v>
-      </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-    </row>
-    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95"/>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-    </row>
-    <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="98"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-    </row>
-    <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="89" t="s">
-        <v>430</v>
-      </c>
-      <c r="C16" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="D16" s="89" t="s">
-        <v>431</v>
-      </c>
-      <c r="E16" s="89" t="s">
-        <v>432</v>
-      </c>
-      <c r="F16" s="101"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-    </row>
-    <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="90" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="92" t="s">
-        <v>433</v>
-      </c>
-      <c r="C17" s="92" t="s">
-        <v>410</v>
-      </c>
-      <c r="D17" s="92" t="s">
-        <v>432</v>
-      </c>
-      <c r="E17" s="92" t="s">
-        <v>434</v>
-      </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-    </row>
-    <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="102" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="103" t="s">
-        <v>435</v>
-      </c>
-      <c r="C18" s="103" t="s">
-        <v>424</v>
-      </c>
-      <c r="D18" s="103" t="s">
-        <v>436</v>
-      </c>
-      <c r="E18" s="103"/>
-      <c r="F18" s="104" t="s">
-        <v>437</v>
-      </c>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-    </row>
-    <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="95" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="96" t="s">
-        <v>438</v>
-      </c>
-      <c r="C19" s="96" t="s">
-        <v>428</v>
-      </c>
-      <c r="D19" s="96" t="s">
-        <v>439</v>
-      </c>
-      <c r="E19" s="96"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-    </row>
-    <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="95"/>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-    </row>
-    <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="105"/>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-    </row>
-    <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="87" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="88" t="s">
-        <v>440</v>
-      </c>
-      <c r="C22" s="89" t="s">
-        <v>419</v>
-      </c>
-      <c r="D22" s="89" t="s">
-        <v>411</v>
-      </c>
-      <c r="E22" s="89" t="s">
-        <v>441</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
-    </row>
-    <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="90" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="91" t="s">
-        <v>442</v>
-      </c>
-      <c r="C23" s="92" t="s">
-        <v>410</v>
-      </c>
-      <c r="D23" s="92" t="s">
-        <v>441</v>
-      </c>
-      <c r="E23" s="92" t="s">
-        <v>443</v>
-      </c>
-      <c r="F23" s="93"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-    </row>
-    <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="102" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="103" t="s">
-        <v>444</v>
-      </c>
-      <c r="C24" s="103" t="s">
-        <v>424</v>
-      </c>
-      <c r="D24" s="103" t="s">
-        <v>445</v>
-      </c>
-      <c r="E24" s="103"/>
-      <c r="F24" s="104" t="s">
-        <v>446</v>
-      </c>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-    </row>
-    <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="96" t="s">
-        <v>447</v>
-      </c>
-      <c r="C25" s="96" t="s">
-        <v>428</v>
-      </c>
-      <c r="D25" s="96" t="s">
-        <v>448</v>
-      </c>
-      <c r="E25" s="96"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
-    </row>
-    <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="95"/>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-    </row>
-    <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="98"/>
-      <c r="B27" s="99"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="61"/>
-    </row>
-    <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="87" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="89" t="s">
-        <v>449</v>
-      </c>
-      <c r="C28" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="D28" s="89" t="s">
-        <v>450</v>
-      </c>
-      <c r="E28" s="89" t="s">
-        <v>451</v>
-      </c>
-      <c r="F28" s="101"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-    </row>
-    <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="90" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="92" t="s">
-        <v>452</v>
-      </c>
-      <c r="C29" s="92" t="s">
-        <v>410</v>
-      </c>
-      <c r="D29" s="92" t="s">
-        <v>451</v>
-      </c>
-      <c r="E29" s="92" t="s">
-        <v>453</v>
-      </c>
-      <c r="F29" s="94"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="61"/>
-    </row>
-    <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="102" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="103" t="s">
-        <v>454</v>
-      </c>
-      <c r="C30" s="103" t="s">
-        <v>424</v>
-      </c>
-      <c r="D30" s="103" t="s">
-        <v>455</v>
-      </c>
-      <c r="E30" s="103"/>
-      <c r="F30" s="104" t="s">
-        <v>456</v>
-      </c>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-    </row>
-    <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="96" t="s">
-        <v>457</v>
-      </c>
-      <c r="C31" s="96" t="s">
-        <v>428</v>
-      </c>
-      <c r="D31" s="96" t="s">
-        <v>458</v>
-      </c>
-      <c r="E31" s="96"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-    </row>
-    <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="95"/>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-    </row>
-    <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="98"/>
-      <c r="B33" s="108"/>
-      <c r="C33" s="108"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
-    </row>
-    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-    </row>
-    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="61"/>
-    </row>
-    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-    </row>
-    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-    </row>
-    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-    </row>
-    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-    </row>
-    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-    </row>
-    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
-    </row>
-    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-    </row>
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -8393,35 +8203,35 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="35" width="17.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="35" width="16.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.47"/>
   </cols>
   <sheetData>
-    <row r="1" s="111" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
+    <row r="1" s="80" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="64" t="s">
-        <v>459</v>
-      </c>
-      <c r="D1" s="64" t="s">
+      <c r="C1" s="66" t="s">
+        <v>614</v>
+      </c>
+      <c r="D1" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="64" t="s">
-        <v>460</v>
-      </c>
-      <c r="F1" s="64" t="s">
+      <c r="E1" s="66" t="s">
+        <v>615</v>
+      </c>
+      <c r="F1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="79" t="s">
         <v>58</v>
       </c>
       <c r="XFC1" s="1"/>
@@ -8429,7 +8239,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>461</v>
+        <v>616</v>
       </c>
       <c r="B2" s="41" t="n">
         <v>0</v>
@@ -8459,7 +8269,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>462</v>
+        <v>617</v>
       </c>
       <c r="B3" s="41" t="n">
         <v>1</v>
@@ -8489,7 +8299,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>463</v>
+        <v>618</v>
       </c>
       <c r="B4" s="41" t="n">
         <v>2</v>
@@ -8519,7 +8329,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>464</v>
+        <v>619</v>
       </c>
       <c r="B5" s="41" t="n">
         <v>3</v>
@@ -8549,7 +8359,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>160</v>
+        <v>379</v>
       </c>
       <c r="B6" s="41" t="n">
         <v>4</v>
@@ -8579,7 +8389,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>465</v>
+        <v>620</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>5</v>
@@ -8609,7 +8419,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>466</v>
+        <v>621</v>
       </c>
       <c r="B8" s="41" t="n">
         <v>6</v>
@@ -8639,7 +8449,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>163</v>
+        <v>382</v>
       </c>
       <c r="B9" s="41" t="n">
         <v>7</v>
@@ -8669,7 +8479,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>467</v>
+        <v>622</v>
       </c>
       <c r="B10" s="41" t="n">
         <v>8</v>
@@ -8699,7 +8509,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>468</v>
+        <v>623</v>
       </c>
       <c r="B11" s="41" t="n">
         <v>9</v>
@@ -8729,7 +8539,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>469</v>
+        <v>624</v>
       </c>
       <c r="B12" s="41" t="n">
         <v>10</v>
@@ -8759,7 +8569,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>470</v>
+        <v>625</v>
       </c>
       <c r="B13" s="41" t="n">
         <v>11</v>
@@ -8789,7 +8599,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>471</v>
+        <v>626</v>
       </c>
       <c r="B14" s="41" t="n">
         <v>12</v>
@@ -8818,8 +8628,8 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="112" t="s">
-        <v>168</v>
+      <c r="A15" s="81" t="s">
+        <v>387</v>
       </c>
       <c r="B15" s="48" t="n">
         <v>13</v>
@@ -8909,7 +8719,7 @@
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
         <v>91</v>
       </c>
@@ -8941,7 +8751,7 @@
         <v>100</v>
       </c>
       <c r="K24" s="55" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="37.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8949,34 +8759,34 @@
         <v>1</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="113" t="s">
-        <v>472</v>
-      </c>
-      <c r="D25" s="113" t="s">
-        <v>473</v>
-      </c>
-      <c r="E25" s="113" t="s">
-        <v>472</v>
-      </c>
-      <c r="F25" s="113" t="s">
-        <v>474</v>
-      </c>
-      <c r="G25" s="113" t="s">
-        <v>475</v>
-      </c>
-      <c r="H25" s="113" t="s">
-        <v>476</v>
-      </c>
-      <c r="I25" s="113" t="s">
-        <v>477</v>
-      </c>
-      <c r="J25" s="113" t="s">
-        <v>478</v>
-      </c>
-      <c r="K25" s="113" t="s">
-        <v>479</v>
+        <v>102</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>627</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>628</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>627</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>629</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>630</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="I25" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>633</v>
+      </c>
+      <c r="K25" s="42" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="36.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8984,34 +8794,34 @@
         <v>2</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="113" t="s">
-        <v>480</v>
-      </c>
-      <c r="D26" s="113" t="s">
-        <v>481</v>
-      </c>
-      <c r="E26" s="113" t="s">
-        <v>480</v>
-      </c>
-      <c r="F26" s="113" t="s">
-        <v>482</v>
-      </c>
-      <c r="G26" s="113" t="s">
-        <v>483</v>
-      </c>
-      <c r="H26" s="113" t="s">
-        <v>484</v>
-      </c>
-      <c r="I26" s="113" t="s">
-        <v>485</v>
-      </c>
-      <c r="J26" s="113" t="s">
-        <v>486</v>
-      </c>
-      <c r="K26" s="113" t="s">
-        <v>487</v>
+        <v>111</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>636</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>639</v>
+      </c>
+      <c r="I26" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="J26" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9019,34 +8829,34 @@
         <v>4</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="113" t="s">
-        <v>488</v>
-      </c>
-      <c r="D27" s="113" t="s">
-        <v>489</v>
-      </c>
-      <c r="E27" s="113" t="s">
-        <v>488</v>
-      </c>
-      <c r="F27" s="113" t="s">
-        <v>490</v>
-      </c>
-      <c r="G27" s="113" t="s">
-        <v>491</v>
-      </c>
-      <c r="H27" s="113" t="s">
-        <v>492</v>
-      </c>
-      <c r="I27" s="113" t="s">
-        <v>493</v>
-      </c>
-      <c r="J27" s="113" t="s">
-        <v>494</v>
-      </c>
-      <c r="K27" s="113" t="s">
-        <v>495</v>
+        <v>120</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>644</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>645</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>646</v>
+      </c>
+      <c r="H27" s="42" t="s">
+        <v>647</v>
+      </c>
+      <c r="I27" s="42" t="s">
+        <v>648</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>649</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9054,34 +8864,34 @@
         <v>5</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="113" t="s">
-        <v>496</v>
-      </c>
-      <c r="D28" s="113" t="s">
-        <v>497</v>
-      </c>
-      <c r="E28" s="113" t="s">
-        <v>496</v>
-      </c>
-      <c r="F28" s="113" t="s">
-        <v>498</v>
-      </c>
-      <c r="G28" s="113" t="s">
-        <v>497</v>
-      </c>
-      <c r="H28" s="113" t="s">
-        <v>496</v>
-      </c>
-      <c r="I28" s="113" t="s">
-        <v>498</v>
-      </c>
-      <c r="J28" s="113" t="s">
-        <v>499</v>
-      </c>
-      <c r="K28" s="113" t="s">
-        <v>500</v>
+        <v>129</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>652</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>653</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>652</v>
+      </c>
+      <c r="H28" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="I28" s="42" t="s">
+        <v>653</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>654</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="38.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9089,34 +8899,34 @@
         <v>6</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="113" t="s">
-        <v>501</v>
-      </c>
-      <c r="D29" s="113" t="s">
-        <v>502</v>
-      </c>
-      <c r="E29" s="113" t="s">
-        <v>501</v>
-      </c>
-      <c r="F29" s="113" t="s">
-        <v>503</v>
-      </c>
-      <c r="G29" s="113" t="s">
-        <v>504</v>
-      </c>
-      <c r="H29" s="113" t="s">
-        <v>505</v>
-      </c>
-      <c r="I29" s="113" t="s">
-        <v>503</v>
-      </c>
-      <c r="J29" s="113" t="s">
-        <v>506</v>
-      </c>
-      <c r="K29" s="113" t="s">
-        <v>507</v>
+        <v>135</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>659</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>660</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>661</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="38.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9124,34 +8934,34 @@
         <v>8</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="113" t="s">
-        <v>508</v>
-      </c>
-      <c r="D30" s="113" t="s">
-        <v>509</v>
-      </c>
-      <c r="E30" s="113" t="s">
-        <v>508</v>
-      </c>
-      <c r="F30" s="113" t="s">
-        <v>510</v>
-      </c>
-      <c r="G30" s="113" t="s">
-        <v>509</v>
-      </c>
-      <c r="H30" s="113" t="s">
-        <v>511</v>
-      </c>
-      <c r="I30" s="113" t="s">
-        <v>510</v>
-      </c>
-      <c r="J30" s="113" t="s">
-        <v>512</v>
-      </c>
-      <c r="K30" s="113" t="s">
-        <v>513</v>
+        <v>141</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>663</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>664</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>663</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>665</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>664</v>
+      </c>
+      <c r="H30" s="42" t="s">
+        <v>666</v>
+      </c>
+      <c r="I30" s="42" t="s">
+        <v>665</v>
+      </c>
+      <c r="J30" s="42" t="s">
+        <v>667</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9159,34 +8969,34 @@
         <v>9</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="113" t="s">
-        <v>514</v>
-      </c>
-      <c r="D31" s="113" t="s">
-        <v>515</v>
-      </c>
-      <c r="E31" s="113" t="s">
-        <v>514</v>
-      </c>
-      <c r="F31" s="113" t="s">
-        <v>516</v>
-      </c>
-      <c r="G31" s="113" t="s">
-        <v>515</v>
-      </c>
-      <c r="H31" s="113" t="s">
-        <v>514</v>
-      </c>
-      <c r="I31" s="113" t="s">
-        <v>516</v>
-      </c>
-      <c r="J31" s="113" t="s">
-        <v>517</v>
-      </c>
-      <c r="K31" s="113" t="s">
-        <v>518</v>
+        <v>147</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>669</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>670</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>669</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>671</v>
+      </c>
+      <c r="G31" s="42" t="s">
+        <v>670</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>669</v>
+      </c>
+      <c r="I31" s="42" t="s">
+        <v>671</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9194,34 +9004,34 @@
         <v>10</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" s="113" t="s">
-        <v>519</v>
-      </c>
-      <c r="D32" s="113" t="s">
-        <v>520</v>
-      </c>
-      <c r="E32" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="F32" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="G32" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="H32" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="I32" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="J32" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="K32" s="77" t="s">
-        <v>222</v>
+        <v>153</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>674</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>675</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>674</v>
+      </c>
+      <c r="F32" s="58" t="s">
+        <v>676</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>675</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>674</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>676</v>
+      </c>
+      <c r="J32" s="58" t="s">
+        <v>677</v>
+      </c>
+      <c r="K32" s="58" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9229,34 +9039,34 @@
         <v>12</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="F33" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="G33" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="H33" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="I33" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="J33" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="K33" s="77" t="s">
-        <v>228</v>
+        <v>160</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="K33" s="58" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9264,34 +9074,34 @@
         <v>13</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="F34" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="G34" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="H34" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="I34" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="J34" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="K34" s="77" t="s">
-        <v>237</v>
+        <v>166</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="G34" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="J34" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="58" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="42.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9299,34 +9109,34 @@
         <v>14</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="D35" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="E35" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="F35" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="H35" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="I35" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="J35" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="K35" s="77" t="s">
-        <v>245</v>
+        <v>175</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="J35" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="K35" s="58" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="37.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9334,34 +9144,34 @@
         <v>16</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>247</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>249</v>
-      </c>
-      <c r="H36" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="I36" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="J36" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="K36" s="77" t="s">
-        <v>253</v>
+        <v>184</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="J36" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="K36" s="58" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9369,221 +9179,221 @@
         <v>17</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="D37" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="G37" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="H37" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="I37" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="J37" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="K37" s="77" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="64.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>193</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="J37" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="K37" s="58" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="D38" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="G38" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="H38" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="I38" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="J38" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="K38" s="77" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="64.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>202</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="G38" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="H38" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="J38" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="K38" s="58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="D39" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="G39" s="42" t="s">
-        <v>273</v>
-      </c>
-      <c r="H39" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="I39" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="J39" s="42" t="s">
-        <v>276</v>
-      </c>
-      <c r="K39" s="77" t="s">
-        <v>261</v>
+        <v>211</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="H39" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="K39" s="58" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="57"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="58"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="60"/>
       <c r="K40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="57"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="58"/>
+      <c r="A41" s="59"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="60"/>
       <c r="K41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="58"/>
+      <c r="A42" s="59"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="60"/>
       <c r="K42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="57"/>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="58"/>
+      <c r="A43" s="59"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="60"/>
       <c r="K43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="57"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="58"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="60"/>
       <c r="K44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="57"/>
-      <c r="B45" s="57"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="58"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="60"/>
       <c r="K45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="57"/>
-      <c r="B46" s="57"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="58"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="60"/>
       <c r="K46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="57"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="58"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="60"/>
       <c r="K47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="57"/>
-      <c r="B48" s="57"/>
-      <c r="C48" s="57"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="58"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="60"/>
       <c r="K48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9682,7 +9492,7 @@
       <c r="I56" s="42"/>
       <c r="K56" s="35"/>
     </row>
-    <row r="57" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="54" t="s">
         <v>91</v>
       </c>
@@ -9714,532 +9524,532 @@
         <v>100</v>
       </c>
       <c r="K57" s="55" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="56" t="n">
         <v>1</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C58" s="113" t="s">
-        <v>521</v>
-      </c>
-      <c r="D58" s="113" t="s">
-        <v>522</v>
-      </c>
-      <c r="E58" s="113" t="s">
-        <v>521</v>
-      </c>
-      <c r="F58" s="113" t="s">
-        <v>523</v>
-      </c>
-      <c r="G58" s="113" t="s">
-        <v>524</v>
-      </c>
-      <c r="H58" s="113" t="s">
-        <v>525</v>
-      </c>
-      <c r="I58" s="113" t="s">
-        <v>526</v>
-      </c>
-      <c r="J58" s="113" t="s">
-        <v>527</v>
-      </c>
-      <c r="K58" s="113" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>680</v>
+      </c>
+      <c r="E58" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>681</v>
+      </c>
+      <c r="G58" s="42" t="s">
+        <v>682</v>
+      </c>
+      <c r="H58" s="42" t="s">
+        <v>683</v>
+      </c>
+      <c r="I58" s="42" t="s">
+        <v>684</v>
+      </c>
+      <c r="J58" s="42" t="s">
+        <v>685</v>
+      </c>
+      <c r="K58" s="42" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="56" t="n">
         <v>2</v>
       </c>
       <c r="B59" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="113" t="s">
-        <v>529</v>
-      </c>
-      <c r="D59" s="113" t="s">
-        <v>530</v>
-      </c>
-      <c r="E59" s="113" t="s">
-        <v>529</v>
-      </c>
-      <c r="F59" s="113" t="s">
-        <v>531</v>
-      </c>
-      <c r="G59" s="113" t="s">
-        <v>532</v>
-      </c>
-      <c r="H59" s="113" t="s">
-        <v>533</v>
-      </c>
-      <c r="I59" s="113" t="s">
-        <v>534</v>
-      </c>
-      <c r="J59" s="113" t="s">
-        <v>535</v>
-      </c>
-      <c r="K59" s="113" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="17.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>687</v>
+      </c>
+      <c r="D59" s="42" t="s">
+        <v>688</v>
+      </c>
+      <c r="E59" s="42" t="s">
+        <v>687</v>
+      </c>
+      <c r="F59" s="42" t="s">
+        <v>689</v>
+      </c>
+      <c r="G59" s="42" t="s">
+        <v>690</v>
+      </c>
+      <c r="H59" s="42" t="s">
+        <v>691</v>
+      </c>
+      <c r="I59" s="42" t="s">
+        <v>692</v>
+      </c>
+      <c r="J59" s="42" t="s">
+        <v>693</v>
+      </c>
+      <c r="K59" s="42" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="56" t="n">
         <v>4</v>
       </c>
       <c r="B60" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="113" t="s">
-        <v>537</v>
-      </c>
-      <c r="D60" s="113" t="s">
-        <v>538</v>
-      </c>
-      <c r="E60" s="113" t="s">
-        <v>537</v>
-      </c>
-      <c r="F60" s="113" t="s">
-        <v>539</v>
-      </c>
-      <c r="G60" s="113" t="s">
-        <v>540</v>
-      </c>
-      <c r="H60" s="113" t="s">
-        <v>541</v>
-      </c>
-      <c r="I60" s="113" t="s">
-        <v>542</v>
-      </c>
-      <c r="J60" s="113" t="s">
-        <v>543</v>
-      </c>
-      <c r="K60" s="113" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>695</v>
+      </c>
+      <c r="D60" s="42" t="s">
+        <v>696</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>695</v>
+      </c>
+      <c r="F60" s="42" t="s">
+        <v>697</v>
+      </c>
+      <c r="G60" s="42" t="s">
+        <v>698</v>
+      </c>
+      <c r="H60" s="42" t="s">
+        <v>699</v>
+      </c>
+      <c r="I60" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="J60" s="42" t="s">
+        <v>701</v>
+      </c>
+      <c r="K60" s="42" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="n">
         <v>5</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="C61" s="113" t="s">
-        <v>545</v>
-      </c>
-      <c r="D61" s="113" t="s">
-        <v>546</v>
-      </c>
-      <c r="E61" s="113" t="s">
-        <v>545</v>
-      </c>
-      <c r="F61" s="113" t="s">
-        <v>547</v>
-      </c>
-      <c r="G61" s="113" t="s">
-        <v>548</v>
-      </c>
-      <c r="H61" s="113" t="s">
-        <v>549</v>
-      </c>
-      <c r="I61" s="113" t="s">
-        <v>550</v>
-      </c>
-      <c r="J61" s="113" t="s">
-        <v>551</v>
-      </c>
-      <c r="K61" s="113" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="D61" s="42" t="s">
+        <v>704</v>
+      </c>
+      <c r="E61" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="F61" s="42" t="s">
+        <v>705</v>
+      </c>
+      <c r="G61" s="42" t="s">
+        <v>706</v>
+      </c>
+      <c r="H61" s="42" t="s">
+        <v>707</v>
+      </c>
+      <c r="I61" s="42" t="s">
+        <v>708</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>709</v>
+      </c>
+      <c r="K61" s="42" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="n">
         <v>6</v>
       </c>
       <c r="B62" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" s="113" t="s">
-        <v>553</v>
-      </c>
-      <c r="D62" s="113" t="s">
-        <v>554</v>
-      </c>
-      <c r="E62" s="113" t="s">
-        <v>553</v>
-      </c>
-      <c r="F62" s="113" t="s">
-        <v>555</v>
-      </c>
-      <c r="G62" s="113" t="s">
-        <v>556</v>
-      </c>
-      <c r="H62" s="113" t="s">
-        <v>557</v>
-      </c>
-      <c r="I62" s="113" t="s">
-        <v>558</v>
-      </c>
-      <c r="J62" s="113" t="s">
-        <v>559</v>
-      </c>
-      <c r="K62" s="113" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>135</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>711</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>712</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>711</v>
+      </c>
+      <c r="F62" s="42" t="s">
+        <v>713</v>
+      </c>
+      <c r="G62" s="42" t="s">
+        <v>714</v>
+      </c>
+      <c r="H62" s="42" t="s">
+        <v>715</v>
+      </c>
+      <c r="I62" s="42" t="s">
+        <v>716</v>
+      </c>
+      <c r="J62" s="42" t="s">
+        <v>717</v>
+      </c>
+      <c r="K62" s="42" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="n">
         <v>8</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="C63" s="113" t="s">
-        <v>561</v>
-      </c>
-      <c r="D63" s="113" t="s">
-        <v>562</v>
-      </c>
-      <c r="E63" s="113" t="s">
-        <v>561</v>
-      </c>
-      <c r="F63" s="113" t="s">
-        <v>563</v>
-      </c>
-      <c r="G63" s="113" t="s">
-        <v>564</v>
-      </c>
-      <c r="H63" s="113" t="s">
-        <v>565</v>
-      </c>
-      <c r="I63" s="113" t="s">
-        <v>566</v>
-      </c>
-      <c r="J63" s="113" t="s">
-        <v>567</v>
-      </c>
-      <c r="K63" s="113" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>141</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>719</v>
+      </c>
+      <c r="D63" s="42" t="s">
+        <v>720</v>
+      </c>
+      <c r="E63" s="42" t="s">
+        <v>719</v>
+      </c>
+      <c r="F63" s="42" t="s">
+        <v>721</v>
+      </c>
+      <c r="G63" s="42" t="s">
+        <v>722</v>
+      </c>
+      <c r="H63" s="42" t="s">
+        <v>723</v>
+      </c>
+      <c r="I63" s="42" t="s">
+        <v>724</v>
+      </c>
+      <c r="J63" s="42" t="s">
+        <v>725</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="56" t="n">
         <v>9</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C64" s="113" t="s">
-        <v>569</v>
-      </c>
-      <c r="D64" s="113" t="s">
-        <v>570</v>
-      </c>
-      <c r="E64" s="113" t="s">
-        <v>569</v>
-      </c>
-      <c r="F64" s="113" t="s">
-        <v>571</v>
-      </c>
-      <c r="G64" s="113" t="s">
-        <v>572</v>
-      </c>
-      <c r="H64" s="113" t="s">
-        <v>573</v>
-      </c>
-      <c r="I64" s="113" t="s">
-        <v>574</v>
-      </c>
-      <c r="J64" s="113" t="s">
-        <v>575</v>
-      </c>
-      <c r="K64" s="113" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>727</v>
+      </c>
+      <c r="D64" s="42" t="s">
+        <v>728</v>
+      </c>
+      <c r="E64" s="42" t="s">
+        <v>727</v>
+      </c>
+      <c r="F64" s="42" t="s">
+        <v>729</v>
+      </c>
+      <c r="G64" s="42" t="s">
+        <v>730</v>
+      </c>
+      <c r="H64" s="42" t="s">
+        <v>731</v>
+      </c>
+      <c r="I64" s="42" t="s">
+        <v>732</v>
+      </c>
+      <c r="J64" s="42" t="s">
+        <v>733</v>
+      </c>
+      <c r="K64" s="42" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="56" t="n">
         <v>10</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="D65" s="42" t="s">
-        <v>334</v>
-      </c>
-      <c r="E65" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="F65" s="42" t="s">
-        <v>335</v>
-      </c>
-      <c r="G65" s="42" t="s">
-        <v>336</v>
-      </c>
-      <c r="H65" s="42" t="s">
-        <v>337</v>
-      </c>
-      <c r="I65" s="42" t="s">
-        <v>338</v>
-      </c>
-      <c r="J65" s="42" t="s">
-        <v>339</v>
-      </c>
-      <c r="K65" s="77" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>153</v>
+      </c>
+      <c r="C65" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="D65" s="58" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F65" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="G65" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="H65" s="58" t="s">
+        <v>280</v>
+      </c>
+      <c r="I65" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="J65" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="K65" s="58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="56" t="n">
         <v>12</v>
       </c>
       <c r="B66" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C66" s="42" t="s">
-        <v>341</v>
-      </c>
-      <c r="D66" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="E66" s="42" t="s">
-        <v>341</v>
-      </c>
-      <c r="F66" s="42" t="s">
-        <v>343</v>
-      </c>
-      <c r="G66" s="42" t="s">
-        <v>344</v>
-      </c>
-      <c r="H66" s="42" t="s">
-        <v>345</v>
-      </c>
-      <c r="I66" s="42" t="s">
-        <v>346</v>
-      </c>
-      <c r="J66" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="K66" s="77" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+      <c r="C66" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="58" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="F66" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="G66" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="H66" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="I66" s="58" t="s">
+        <v>289</v>
+      </c>
+      <c r="J66" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="K66" s="58" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="56" t="n">
         <v>13</v>
       </c>
       <c r="B67" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C67" s="42" t="s">
-        <v>349</v>
-      </c>
-      <c r="D67" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="E67" s="42" t="s">
-        <v>349</v>
-      </c>
-      <c r="F67" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="G67" s="42" t="s">
-        <v>352</v>
-      </c>
-      <c r="H67" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="I67" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="J67" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="K67" s="77" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>166</v>
+      </c>
+      <c r="C67" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="D67" s="58" t="s">
+        <v>293</v>
+      </c>
+      <c r="E67" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="F67" s="58" t="s">
+        <v>294</v>
+      </c>
+      <c r="G67" s="58" t="s">
+        <v>295</v>
+      </c>
+      <c r="H67" s="58" t="s">
+        <v>296</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>297</v>
+      </c>
+      <c r="J67" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="K67" s="58" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="56" t="n">
         <v>14</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C68" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="D68" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="F68" s="42" t="s">
-        <v>359</v>
-      </c>
-      <c r="G68" s="42" t="s">
-        <v>360</v>
-      </c>
-      <c r="H68" s="42" t="s">
-        <v>361</v>
-      </c>
-      <c r="I68" s="42" t="s">
-        <v>362</v>
-      </c>
-      <c r="J68" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="K68" s="77" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+      <c r="C68" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="D68" s="58" t="s">
+        <v>301</v>
+      </c>
+      <c r="E68" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="F68" s="58" t="s">
+        <v>302</v>
+      </c>
+      <c r="G68" s="58" t="s">
+        <v>303</v>
+      </c>
+      <c r="H68" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="I68" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="J68" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="K68" s="58" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="56" t="n">
         <v>16</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C69" s="42" t="s">
-        <v>365</v>
-      </c>
-      <c r="D69" s="42" t="s">
-        <v>366</v>
-      </c>
-      <c r="E69" s="42" t="s">
-        <v>365</v>
-      </c>
-      <c r="F69" s="42" t="s">
-        <v>367</v>
-      </c>
-      <c r="G69" s="42" t="s">
-        <v>368</v>
-      </c>
-      <c r="H69" s="42" t="s">
-        <v>369</v>
-      </c>
-      <c r="I69" s="42" t="s">
-        <v>370</v>
-      </c>
-      <c r="J69" s="42" t="s">
-        <v>371</v>
-      </c>
-      <c r="K69" s="77" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" s="58" t="s">
+        <v>309</v>
+      </c>
+      <c r="E69" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="F69" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="G69" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="H69" s="58" t="s">
+        <v>312</v>
+      </c>
+      <c r="I69" s="58" t="s">
+        <v>313</v>
+      </c>
+      <c r="J69" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="K69" s="58" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>17</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C70" s="42" t="s">
-        <v>373</v>
-      </c>
-      <c r="D70" s="42" t="s">
-        <v>374</v>
-      </c>
-      <c r="E70" s="42" t="s">
-        <v>373</v>
-      </c>
-      <c r="F70" s="42" t="s">
-        <v>375</v>
-      </c>
-      <c r="G70" s="42" t="s">
-        <v>376</v>
-      </c>
-      <c r="H70" s="42" t="s">
-        <v>377</v>
-      </c>
-      <c r="I70" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="J70" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="K70" s="77" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>193</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70" s="58" t="s">
+        <v>317</v>
+      </c>
+      <c r="E70" s="58" t="s">
+        <v>316</v>
+      </c>
+      <c r="F70" s="58" t="s">
+        <v>318</v>
+      </c>
+      <c r="G70" s="58" t="s">
+        <v>319</v>
+      </c>
+      <c r="H70" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="I70" s="58" t="s">
+        <v>321</v>
+      </c>
+      <c r="J70" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="K70" s="58" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="56" t="n">
         <v>18</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C71" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="D71" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="E71" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="F71" s="42" t="s">
-        <v>383</v>
-      </c>
-      <c r="G71" s="42" t="s">
-        <v>384</v>
-      </c>
-      <c r="H71" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="I71" s="42" t="s">
-        <v>386</v>
-      </c>
-      <c r="J71" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="K71" s="77" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="33.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>202</v>
+      </c>
+      <c r="C71" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="D71" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="E71" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="F71" s="58" t="s">
+        <v>326</v>
+      </c>
+      <c r="G71" s="58" t="s">
+        <v>327</v>
+      </c>
+      <c r="H71" s="58" t="s">
+        <v>328</v>
+      </c>
+      <c r="I71" s="58" t="s">
+        <v>329</v>
+      </c>
+      <c r="J71" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="K71" s="58" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>20</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" s="42" t="s">
-        <v>389</v>
-      </c>
-      <c r="D72" s="42" t="s">
-        <v>390</v>
-      </c>
-      <c r="E72" s="42" t="s">
-        <v>389</v>
-      </c>
-      <c r="F72" s="42" t="s">
-        <v>391</v>
-      </c>
-      <c r="G72" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="H72" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="I72" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="J72" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="K72" s="77" t="s">
-        <v>380</v>
+        <v>211</v>
+      </c>
+      <c r="C72" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="D72" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="F72" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="G72" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="H72" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="I72" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="J72" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="K72" s="58" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="34.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -10250,8 +10060,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
+++ b/TFG_MODELOS_SIMPLES/02_datasets/metadata/METADATA.xlsx
@@ -5105,7 +5105,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="114">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5342,16 +5342,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -5424,14 +5420,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -5652,14 +5640,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>170280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>309240</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>28800</xdr:rowOff>
+      <xdr:colOff>308520</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>104040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5672,8 +5660,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13852440" y="20862360"/>
-          <a:ext cx="4638240" cy="3891960"/>
+          <a:off x="15723720" y="20862360"/>
+          <a:ext cx="5222880" cy="3891240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5689,14 +5677,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>88920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>309240</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:colOff>308520</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5709,8 +5697,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13852440" y="25155000"/>
-          <a:ext cx="4638240" cy="3890520"/>
+          <a:off x="15723720" y="25155000"/>
+          <a:ext cx="5222880" cy="3889800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5726,14 +5714,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>309240</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>55800</xdr:rowOff>
+      <xdr:colOff>308520</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>167400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5746,8 +5734,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13852440" y="29447640"/>
-          <a:ext cx="4638240" cy="3890520"/>
+          <a:off x="15723720" y="29447640"/>
+          <a:ext cx="5222880" cy="3889800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5763,14 +5751,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>170280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>333000</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:colOff>332280</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5783,8 +5771,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20381040" y="20862360"/>
-          <a:ext cx="4638240" cy="3890520"/>
+          <a:off x="23135040" y="20862360"/>
+          <a:ext cx="5220360" cy="3889800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5800,14 +5788,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>88920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>333000</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:colOff>332280</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>21600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5820,8 +5808,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20381040" y="25155000"/>
-          <a:ext cx="4638240" cy="3890520"/>
+          <a:off x="23135040" y="25155000"/>
+          <a:ext cx="5220360" cy="3889800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5842,14 +5830,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>848160</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>72720</xdr:rowOff>
+      <xdr:colOff>847440</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>96120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5862,8 +5850,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12450960" y="22102560"/>
-          <a:ext cx="5085000" cy="3893400"/>
+          <a:off x="14133960" y="22102560"/>
+          <a:ext cx="5655600" cy="3892680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5879,14 +5867,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>14400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>405360</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>9000</xdr:rowOff>
+      <xdr:colOff>404640</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>158040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5899,8 +5887,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12450960" y="26538480"/>
-          <a:ext cx="4642200" cy="3893400"/>
+          <a:off x="14133960" y="26538480"/>
+          <a:ext cx="5212800" cy="3892680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5916,14 +5904,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>143280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>405360</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>21600</xdr:rowOff>
+      <xdr:colOff>404640</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>129600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5936,8 +5924,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12450960" y="30832920"/>
-          <a:ext cx="4642200" cy="3893400"/>
+          <a:off x="14133960" y="30832920"/>
+          <a:ext cx="5212800" cy="3892680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5953,14 +5941,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>336960</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>72720</xdr:rowOff>
+      <xdr:colOff>336240</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>96120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5973,8 +5961,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18083520" y="22102560"/>
-          <a:ext cx="4642200" cy="3893400"/>
+          <a:off x="20526480" y="22102560"/>
+          <a:ext cx="5224320" cy="3892680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5990,14 +5978,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>14400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>336960</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>9000</xdr:rowOff>
+      <xdr:colOff>336240</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>158040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6010,8 +5998,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18083520" y="26538480"/>
-          <a:ext cx="4642200" cy="3893400"/>
+          <a:off x="20526480" y="26538480"/>
+          <a:ext cx="5224320" cy="3892680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6032,14 +6020,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1714680</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>64080</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>237240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>191520</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>119160</xdr:rowOff>
+      <xdr:colOff>190800</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>86760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6053,7 +6041,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1714680" y="21578400"/>
-          <a:ext cx="4644720" cy="3881880"/>
+          <a:ext cx="5476320" cy="3881160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6069,14 +6057,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>749160</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:colOff>748440</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6089,8 +6077,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7461360" y="21514320"/>
-          <a:ext cx="4644720" cy="3881880"/>
+          <a:off x="8468280" y="21514320"/>
+          <a:ext cx="5170680" cy="3881160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6106,14 +6094,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>266400</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:colOff>265680</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6126,8 +6114,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12604680" y="21514320"/>
-          <a:ext cx="4644720" cy="3881880"/>
+          <a:off x="14306400" y="21514320"/>
+          <a:ext cx="5235840" cy="3881160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6143,14 +6131,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1899360</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>376200</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:colOff>375480</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>157320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6164,7 +6152,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1899360" y="26161200"/>
-          <a:ext cx="4644720" cy="3881880"/>
+          <a:ext cx="5476320" cy="3881160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6180,14 +6168,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>749160</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:colOff>748440</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>157320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6200,8 +6188,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7461360" y="26161200"/>
-          <a:ext cx="4644720" cy="3881880"/>
+          <a:off x="8468280" y="26161200"/>
+          <a:ext cx="5170680" cy="3881160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6829,7 +6817,7 @@
       <c r="E34" s="34"/>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
         <v>58</v>
       </c>
@@ -6879,7 +6867,7 @@
       <c r="E38" s="34"/>
       <c r="F38" s="35"/>
     </row>
-    <row r="39" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
         <v>64</v>
       </c>
@@ -6924,8 +6912,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9028,7 +9016,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>17</v>
       </c>
@@ -9098,7 +9086,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>20</v>
       </c>
@@ -9133,7 +9121,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="59"/>
       <c r="B81" s="60" t="s">
         <v>341</v>
@@ -9151,1083 +9139,1083 @@
         <v>345</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="60" t="s">
         <v>346</v>
       </c>
-      <c r="B82" s="61" t="s">
+      <c r="B82" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="C82" s="61" t="s">
+      <c r="C82" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="D82" s="61" t="s">
+      <c r="D82" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="E82" s="61" t="s">
+      <c r="E82" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="F82" s="61" t="s">
+      <c r="F82" s="42" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="60" t="s">
         <v>352</v>
       </c>
-      <c r="B83" s="61" t="s">
+      <c r="B83" s="42" t="s">
         <v>353</v>
       </c>
-      <c r="C83" s="61" t="s">
+      <c r="C83" s="42" t="s">
         <v>354</v>
       </c>
-      <c r="D83" s="61" t="s">
+      <c r="D83" s="42" t="s">
         <v>355</v>
       </c>
-      <c r="E83" s="61" t="s">
+      <c r="E83" s="42" t="s">
         <v>356</v>
       </c>
-      <c r="F83" s="61" t="s">
+      <c r="F83" s="42" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="60" t="s">
         <v>358</v>
       </c>
-      <c r="B84" s="61" t="s">
+      <c r="B84" s="42" t="s">
         <v>359</v>
       </c>
-      <c r="C84" s="61" t="s">
+      <c r="C84" s="42" t="s">
         <v>360</v>
       </c>
-      <c r="D84" s="61" t="s">
+      <c r="D84" s="42" t="s">
         <v>361</v>
       </c>
-      <c r="E84" s="61" t="s">
+      <c r="E84" s="42" t="s">
         <v>362</v>
       </c>
-      <c r="F84" s="61" t="s">
+      <c r="F84" s="42" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="60" t="s">
         <v>364</v>
       </c>
-      <c r="B85" s="61" t="s">
+      <c r="B85" s="42" t="s">
         <v>365</v>
       </c>
-      <c r="C85" s="61" t="s">
+      <c r="C85" s="42" t="s">
         <v>366</v>
       </c>
-      <c r="D85" s="61" t="s">
+      <c r="D85" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="E85" s="61" t="s">
+      <c r="E85" s="42" t="s">
         <v>368</v>
       </c>
-      <c r="F85" s="61" t="s">
+      <c r="F85" s="42" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="60" t="s">
         <v>370</v>
       </c>
-      <c r="B86" s="61" t="s">
+      <c r="B86" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="C86" s="61" t="s">
+      <c r="C86" s="42" t="s">
         <v>372</v>
       </c>
-      <c r="D86" s="61" t="s">
+      <c r="D86" s="42" t="s">
         <v>373</v>
       </c>
-      <c r="E86" s="61" t="s">
+      <c r="E86" s="42" t="s">
         <v>374</v>
       </c>
-      <c r="F86" s="61" t="s">
+      <c r="F86" s="42" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="60" t="s">
         <v>376</v>
       </c>
-      <c r="B87" s="61" t="s">
+      <c r="B87" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="C87" s="61" t="s">
+      <c r="C87" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="D87" s="61" t="s">
+      <c r="D87" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="E87" s="61" t="s">
+      <c r="E87" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="F87" s="61" t="s">
+      <c r="F87" s="42" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="60" t="s">
         <v>382</v>
       </c>
-      <c r="B88" s="61" t="s">
+      <c r="B88" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="C88" s="61" t="s">
+      <c r="C88" s="42" t="s">
         <v>384</v>
       </c>
-      <c r="D88" s="61" t="s">
+      <c r="D88" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="E88" s="61" t="s">
+      <c r="E88" s="42" t="s">
         <v>386</v>
       </c>
-      <c r="F88" s="61" t="s">
+      <c r="F88" s="42" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="60" t="s">
         <v>388</v>
       </c>
-      <c r="B89" s="61" t="s">
+      <c r="B89" s="42" t="s">
         <v>389</v>
       </c>
-      <c r="C89" s="61" t="s">
+      <c r="C89" s="42" t="s">
         <v>390</v>
       </c>
-      <c r="D89" s="61" t="s">
+      <c r="D89" s="42" t="s">
         <v>391</v>
       </c>
-      <c r="E89" s="61" t="s">
+      <c r="E89" s="42" t="s">
         <v>392</v>
       </c>
-      <c r="F89" s="61" t="s">
+      <c r="F89" s="42" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="60" t="s">
         <v>394</v>
       </c>
-      <c r="B90" s="61" t="s">
+      <c r="B90" s="42" t="s">
         <v>395</v>
       </c>
-      <c r="C90" s="61" t="s">
+      <c r="C90" s="42" t="s">
         <v>396</v>
       </c>
-      <c r="D90" s="61" t="s">
+      <c r="D90" s="42" t="s">
         <v>397</v>
       </c>
-      <c r="E90" s="61" t="s">
+      <c r="E90" s="42" t="s">
         <v>398</v>
       </c>
-      <c r="F90" s="61" t="s">
+      <c r="F90" s="42" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="60" t="s">
         <v>400</v>
       </c>
-      <c r="B91" s="61" t="s">
+      <c r="B91" s="42" t="s">
         <v>401</v>
       </c>
-      <c r="C91" s="61" t="s">
+      <c r="C91" s="42" t="s">
         <v>402</v>
       </c>
-      <c r="D91" s="61" t="s">
+      <c r="D91" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="E91" s="61" t="s">
+      <c r="E91" s="42" t="s">
         <v>404</v>
       </c>
-      <c r="F91" s="61" t="s">
+      <c r="F91" s="42" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="60" t="s">
         <v>406</v>
       </c>
-      <c r="B92" s="61" t="s">
+      <c r="B92" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="C92" s="61" t="s">
+      <c r="C92" s="42" t="s">
         <v>408</v>
       </c>
-      <c r="D92" s="61" t="s">
+      <c r="D92" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="E92" s="61" t="s">
+      <c r="E92" s="42" t="s">
         <v>410</v>
       </c>
-      <c r="F92" s="61" t="s">
+      <c r="F92" s="42" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="60" t="s">
         <v>412</v>
       </c>
-      <c r="B93" s="61" t="s">
+      <c r="B93" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="C93" s="61" t="s">
+      <c r="C93" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="D93" s="61" t="s">
+      <c r="D93" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="E93" s="61" t="s">
+      <c r="E93" s="42" t="s">
         <v>416</v>
       </c>
-      <c r="F93" s="61" t="s">
+      <c r="F93" s="42" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="60" t="s">
         <v>418</v>
       </c>
-      <c r="B94" s="61" t="s">
+      <c r="B94" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="C94" s="61" t="s">
+      <c r="C94" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="D94" s="61" t="s">
+      <c r="D94" s="42" t="s">
         <v>421</v>
       </c>
-      <c r="E94" s="61" t="s">
+      <c r="E94" s="42" t="s">
         <v>422</v>
       </c>
-      <c r="F94" s="61" t="s">
+      <c r="F94" s="42" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="60" t="s">
         <v>424</v>
       </c>
-      <c r="B95" s="61" t="s">
+      <c r="B95" s="42" t="s">
         <v>425</v>
       </c>
-      <c r="C95" s="61" t="s">
+      <c r="C95" s="42" t="s">
         <v>426</v>
       </c>
-      <c r="D95" s="61" t="s">
+      <c r="D95" s="42" t="s">
         <v>427</v>
       </c>
-      <c r="E95" s="61" t="s">
+      <c r="E95" s="42" t="s">
         <v>428</v>
       </c>
-      <c r="F95" s="61" t="s">
+      <c r="F95" s="42" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="60" t="s">
         <v>430</v>
       </c>
-      <c r="B96" s="61" t="s">
+      <c r="B96" s="42" t="s">
         <v>431</v>
       </c>
-      <c r="C96" s="61" t="s">
+      <c r="C96" s="42" t="s">
         <v>432</v>
       </c>
-      <c r="D96" s="61" t="s">
+      <c r="D96" s="42" t="s">
         <v>433</v>
       </c>
-      <c r="E96" s="61" t="s">
+      <c r="E96" s="42" t="s">
         <v>434</v>
       </c>
-      <c r="F96" s="61" t="s">
+      <c r="F96" s="42" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="60" t="s">
         <v>436</v>
       </c>
-      <c r="B97" s="61" t="s">
+      <c r="B97" s="42" t="s">
         <v>437</v>
       </c>
-      <c r="C97" s="61" t="s">
+      <c r="C97" s="42" t="s">
         <v>438</v>
       </c>
-      <c r="D97" s="61" t="s">
+      <c r="D97" s="42" t="s">
         <v>439</v>
       </c>
-      <c r="E97" s="61" t="s">
+      <c r="E97" s="42" t="s">
         <v>440</v>
       </c>
-      <c r="F97" s="61" t="s">
+      <c r="F97" s="42" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="60" t="s">
         <v>442</v>
       </c>
-      <c r="B98" s="61" t="s">
+      <c r="B98" s="42" t="s">
         <v>443</v>
       </c>
-      <c r="C98" s="61" t="s">
+      <c r="C98" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="D98" s="61" t="s">
+      <c r="D98" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="E98" s="61" t="s">
+      <c r="E98" s="42" t="s">
         <v>446</v>
       </c>
-      <c r="F98" s="61" t="s">
+      <c r="F98" s="42" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="60" t="s">
         <v>448</v>
       </c>
-      <c r="B99" s="61" t="s">
+      <c r="B99" s="42" t="s">
         <v>449</v>
       </c>
-      <c r="C99" s="61" t="s">
+      <c r="C99" s="42" t="s">
         <v>450</v>
       </c>
-      <c r="D99" s="61" t="s">
+      <c r="D99" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="E99" s="61" t="s">
+      <c r="E99" s="42" t="s">
         <v>452</v>
       </c>
-      <c r="F99" s="61" t="s">
+      <c r="F99" s="42" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="60" t="s">
         <v>454</v>
       </c>
-      <c r="B100" s="61" t="s">
+      <c r="B100" s="42" t="s">
         <v>455</v>
       </c>
-      <c r="C100" s="61" t="s">
+      <c r="C100" s="42" t="s">
         <v>456</v>
       </c>
-      <c r="D100" s="61" t="s">
+      <c r="D100" s="42" t="s">
         <v>457</v>
       </c>
-      <c r="E100" s="61" t="s">
+      <c r="E100" s="42" t="s">
         <v>458</v>
       </c>
-      <c r="F100" s="61" t="s">
+      <c r="F100" s="42" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="60" t="s">
         <v>460</v>
       </c>
-      <c r="B101" s="61" t="s">
+      <c r="B101" s="42" t="s">
         <v>461</v>
       </c>
-      <c r="C101" s="61" t="s">
+      <c r="C101" s="42" t="s">
         <v>462</v>
       </c>
-      <c r="D101" s="61" t="s">
+      <c r="D101" s="42" t="s">
         <v>463</v>
       </c>
-      <c r="E101" s="61" t="s">
+      <c r="E101" s="42" t="s">
         <v>464</v>
       </c>
-      <c r="F101" s="61" t="s">
+      <c r="F101" s="42" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="60" t="s">
         <v>466</v>
       </c>
-      <c r="B102" s="61" t="s">
+      <c r="B102" s="42" t="s">
         <v>467</v>
       </c>
-      <c r="C102" s="61" t="s">
+      <c r="C102" s="42" t="s">
         <v>468</v>
       </c>
-      <c r="D102" s="61" t="s">
+      <c r="D102" s="42" t="s">
         <v>469</v>
       </c>
-      <c r="E102" s="61" t="s">
+      <c r="E102" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="F102" s="61" t="s">
+      <c r="F102" s="42" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="60" t="s">
         <v>472</v>
       </c>
-      <c r="B103" s="61" t="s">
+      <c r="B103" s="42" t="s">
         <v>473</v>
       </c>
-      <c r="C103" s="61" t="s">
+      <c r="C103" s="42" t="s">
         <v>474</v>
       </c>
-      <c r="D103" s="61" t="s">
+      <c r="D103" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="E103" s="61" t="s">
+      <c r="E103" s="42" t="s">
         <v>476</v>
       </c>
-      <c r="F103" s="61" t="s">
+      <c r="F103" s="42" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="60" t="s">
         <v>478</v>
       </c>
-      <c r="B104" s="61" t="s">
+      <c r="B104" s="42" t="s">
         <v>479</v>
       </c>
-      <c r="C104" s="61" t="s">
+      <c r="C104" s="42" t="s">
         <v>480</v>
       </c>
-      <c r="D104" s="61" t="s">
+      <c r="D104" s="42" t="s">
         <v>481</v>
       </c>
-      <c r="E104" s="61" t="s">
+      <c r="E104" s="42" t="s">
         <v>482</v>
       </c>
-      <c r="F104" s="61" t="s">
+      <c r="F104" s="42" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="60" t="s">
         <v>484</v>
       </c>
-      <c r="B105" s="61" t="s">
+      <c r="B105" s="42" t="s">
         <v>485</v>
       </c>
-      <c r="C105" s="61" t="s">
+      <c r="C105" s="42" t="s">
         <v>486</v>
       </c>
-      <c r="D105" s="61" t="s">
+      <c r="D105" s="42" t="s">
         <v>487</v>
       </c>
-      <c r="E105" s="61" t="s">
+      <c r="E105" s="42" t="s">
         <v>488</v>
       </c>
-      <c r="F105" s="61" t="s">
+      <c r="F105" s="42" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="60" t="s">
         <v>490</v>
       </c>
-      <c r="B106" s="61" t="s">
+      <c r="B106" s="42" t="s">
         <v>491</v>
       </c>
-      <c r="C106" s="61" t="s">
+      <c r="C106" s="42" t="s">
         <v>492</v>
       </c>
-      <c r="D106" s="61" t="s">
+      <c r="D106" s="42" t="s">
         <v>493</v>
       </c>
-      <c r="E106" s="61" t="s">
+      <c r="E106" s="42" t="s">
         <v>494</v>
       </c>
-      <c r="F106" s="61" t="s">
+      <c r="F106" s="42" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="60" t="s">
         <v>496</v>
       </c>
-      <c r="B107" s="61" t="s">
+      <c r="B107" s="42" t="s">
         <v>497</v>
       </c>
-      <c r="C107" s="61" t="s">
+      <c r="C107" s="42" t="s">
         <v>498</v>
       </c>
-      <c r="D107" s="61" t="s">
+      <c r="D107" s="42" t="s">
         <v>499</v>
       </c>
-      <c r="E107" s="61" t="s">
+      <c r="E107" s="42" t="s">
         <v>500</v>
       </c>
-      <c r="F107" s="61" t="s">
+      <c r="F107" s="42" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="B108" s="61" t="s">
+      <c r="B108" s="42" t="s">
         <v>503</v>
       </c>
-      <c r="C108" s="61" t="s">
+      <c r="C108" s="42" t="s">
         <v>504</v>
       </c>
-      <c r="D108" s="61" t="s">
+      <c r="D108" s="42" t="s">
         <v>505</v>
       </c>
-      <c r="E108" s="61" t="s">
+      <c r="E108" s="42" t="s">
         <v>506</v>
       </c>
-      <c r="F108" s="61" t="s">
+      <c r="F108" s="42" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="60" t="s">
         <v>508</v>
       </c>
-      <c r="B109" s="61" t="s">
+      <c r="B109" s="42" t="s">
         <v>509</v>
       </c>
-      <c r="C109" s="61" t="s">
+      <c r="C109" s="42" t="s">
         <v>510</v>
       </c>
-      <c r="D109" s="61" t="s">
+      <c r="D109" s="42" t="s">
         <v>511</v>
       </c>
-      <c r="E109" s="61" t="s">
+      <c r="E109" s="42" t="s">
         <v>512</v>
       </c>
-      <c r="F109" s="61" t="s">
+      <c r="F109" s="42" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="60" t="s">
         <v>514</v>
       </c>
-      <c r="B110" s="61" t="s">
+      <c r="B110" s="42" t="s">
         <v>515</v>
       </c>
-      <c r="C110" s="61" t="s">
+      <c r="C110" s="42" t="s">
         <v>516</v>
       </c>
-      <c r="D110" s="61" t="s">
+      <c r="D110" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="E110" s="61" t="s">
+      <c r="E110" s="42" t="s">
         <v>518</v>
       </c>
-      <c r="F110" s="61" t="s">
+      <c r="F110" s="42" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="B111" s="61" t="s">
+      <c r="B111" s="42" t="s">
         <v>521</v>
       </c>
-      <c r="C111" s="61" t="s">
+      <c r="C111" s="42" t="s">
         <v>522</v>
       </c>
-      <c r="D111" s="61" t="s">
+      <c r="D111" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="E111" s="61" t="s">
+      <c r="E111" s="42" t="s">
         <v>524</v>
       </c>
-      <c r="F111" s="61" t="s">
+      <c r="F111" s="42" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="60" t="s">
         <v>526</v>
       </c>
-      <c r="B112" s="61" t="s">
+      <c r="B112" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="C112" s="61" t="s">
+      <c r="C112" s="42" t="s">
         <v>528</v>
       </c>
-      <c r="D112" s="61" t="s">
+      <c r="D112" s="42" t="s">
         <v>529</v>
       </c>
-      <c r="E112" s="61" t="s">
+      <c r="E112" s="42" t="s">
         <v>530</v>
       </c>
-      <c r="F112" s="61" t="s">
+      <c r="F112" s="42" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="60" t="s">
         <v>532</v>
       </c>
-      <c r="B113" s="61" t="s">
+      <c r="B113" s="42" t="s">
         <v>533</v>
       </c>
-      <c r="C113" s="61" t="s">
+      <c r="C113" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="D113" s="61" t="s">
+      <c r="D113" s="42" t="s">
         <v>535</v>
       </c>
-      <c r="E113" s="61" t="s">
+      <c r="E113" s="42" t="s">
         <v>536</v>
       </c>
-      <c r="F113" s="61" t="s">
+      <c r="F113" s="42" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="60" t="s">
         <v>538</v>
       </c>
-      <c r="B114" s="61" t="s">
+      <c r="B114" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="C114" s="61" t="s">
+      <c r="C114" s="42" t="s">
         <v>540</v>
       </c>
-      <c r="D114" s="61" t="s">
+      <c r="D114" s="42" t="s">
         <v>541</v>
       </c>
-      <c r="E114" s="61" t="s">
+      <c r="E114" s="42" t="s">
         <v>542</v>
       </c>
-      <c r="F114" s="61" t="s">
+      <c r="F114" s="42" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="60" t="s">
         <v>544</v>
       </c>
-      <c r="B115" s="61" t="s">
+      <c r="B115" s="42" t="s">
         <v>545</v>
       </c>
-      <c r="C115" s="61" t="s">
+      <c r="C115" s="42" t="s">
         <v>546</v>
       </c>
-      <c r="D115" s="61" t="s">
+      <c r="D115" s="42" t="s">
         <v>547</v>
       </c>
-      <c r="E115" s="61" t="s">
+      <c r="E115" s="42" t="s">
         <v>548</v>
       </c>
-      <c r="F115" s="61" t="s">
+      <c r="F115" s="42" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="60" t="s">
         <v>550</v>
       </c>
-      <c r="B116" s="61" t="s">
+      <c r="B116" s="42" t="s">
         <v>551</v>
       </c>
-      <c r="C116" s="61" t="s">
+      <c r="C116" s="42" t="s">
         <v>552</v>
       </c>
-      <c r="D116" s="61" t="s">
+      <c r="D116" s="42" t="s">
         <v>553</v>
       </c>
-      <c r="E116" s="61" t="s">
+      <c r="E116" s="42" t="s">
         <v>554</v>
       </c>
-      <c r="F116" s="61" t="s">
+      <c r="F116" s="42" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="60" t="s">
         <v>556</v>
       </c>
-      <c r="B117" s="61" t="s">
+      <c r="B117" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="C117" s="61" t="s">
+      <c r="C117" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="D117" s="61" t="s">
+      <c r="D117" s="42" t="s">
         <v>559</v>
       </c>
-      <c r="E117" s="61" t="s">
+      <c r="E117" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="F117" s="61" t="s">
+      <c r="F117" s="42" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="60" t="s">
         <v>562</v>
       </c>
-      <c r="B118" s="61" t="s">
+      <c r="B118" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="C118" s="61" t="s">
+      <c r="C118" s="42" t="s">
         <v>564</v>
       </c>
-      <c r="D118" s="61" t="s">
+      <c r="D118" s="42" t="s">
         <v>565</v>
       </c>
-      <c r="E118" s="61" t="s">
+      <c r="E118" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="F118" s="61" t="s">
+      <c r="F118" s="42" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="60" t="s">
         <v>568</v>
       </c>
-      <c r="B119" s="61" t="s">
+      <c r="B119" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="C119" s="61" t="s">
+      <c r="C119" s="42" t="s">
         <v>570</v>
       </c>
-      <c r="D119" s="61" t="s">
+      <c r="D119" s="42" t="s">
         <v>571</v>
       </c>
-      <c r="E119" s="61" t="s">
+      <c r="E119" s="42" t="s">
         <v>572</v>
       </c>
-      <c r="F119" s="61" t="s">
+      <c r="F119" s="42" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="60" t="s">
         <v>574</v>
       </c>
-      <c r="B120" s="61" t="s">
+      <c r="B120" s="42" t="s">
         <v>575</v>
       </c>
-      <c r="C120" s="61" t="s">
+      <c r="C120" s="42" t="s">
         <v>576</v>
       </c>
-      <c r="D120" s="61" t="s">
+      <c r="D120" s="42" t="s">
         <v>577</v>
       </c>
-      <c r="E120" s="61" t="s">
+      <c r="E120" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="F120" s="61" t="s">
+      <c r="F120" s="42" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="60" t="s">
         <v>580</v>
       </c>
-      <c r="B121" s="61" t="s">
+      <c r="B121" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="C121" s="61" t="s">
+      <c r="C121" s="42" t="s">
         <v>582</v>
       </c>
-      <c r="D121" s="61" t="s">
+      <c r="D121" s="42" t="s">
         <v>583</v>
       </c>
-      <c r="E121" s="61" t="s">
+      <c r="E121" s="42" t="s">
         <v>584</v>
       </c>
-      <c r="F121" s="61" t="s">
+      <c r="F121" s="42" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="60" t="s">
         <v>586</v>
       </c>
-      <c r="B122" s="61" t="s">
+      <c r="B122" s="42" t="s">
         <v>587</v>
       </c>
-      <c r="C122" s="61" t="s">
+      <c r="C122" s="42" t="s">
         <v>588</v>
       </c>
-      <c r="D122" s="61" t="s">
+      <c r="D122" s="42" t="s">
         <v>589</v>
       </c>
-      <c r="E122" s="61" t="s">
+      <c r="E122" s="42" t="s">
         <v>590</v>
       </c>
-      <c r="F122" s="61" t="s">
+      <c r="F122" s="42" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="60" t="s">
         <v>592</v>
       </c>
-      <c r="B123" s="61" t="s">
+      <c r="B123" s="42" t="s">
         <v>593</v>
       </c>
-      <c r="C123" s="61" t="s">
+      <c r="C123" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="D123" s="61" t="s">
+      <c r="D123" s="42" t="s">
         <v>595</v>
       </c>
-      <c r="E123" s="61" t="s">
+      <c r="E123" s="42" t="s">
         <v>596</v>
       </c>
-      <c r="F123" s="61" t="s">
+      <c r="F123" s="42" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="60" t="s">
         <v>598</v>
       </c>
-      <c r="B124" s="61" t="s">
+      <c r="B124" s="42" t="s">
         <v>599</v>
       </c>
-      <c r="C124" s="61" t="s">
+      <c r="C124" s="42" t="s">
         <v>600</v>
       </c>
-      <c r="D124" s="61" t="s">
+      <c r="D124" s="42" t="s">
         <v>601</v>
       </c>
-      <c r="E124" s="61" t="s">
+      <c r="E124" s="42" t="s">
         <v>602</v>
       </c>
-      <c r="F124" s="61" t="s">
+      <c r="F124" s="42" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="60" t="s">
         <v>604</v>
       </c>
-      <c r="B125" s="61" t="s">
+      <c r="B125" s="42" t="s">
         <v>605</v>
       </c>
-      <c r="C125" s="61" t="s">
+      <c r="C125" s="42" t="s">
         <v>606</v>
       </c>
-      <c r="D125" s="61" t="s">
+      <c r="D125" s="42" t="s">
         <v>607</v>
       </c>
-      <c r="E125" s="61" t="s">
+      <c r="E125" s="42" t="s">
         <v>608</v>
       </c>
-      <c r="F125" s="61" t="s">
+      <c r="F125" s="42" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="60" t="s">
         <v>610</v>
       </c>
-      <c r="B126" s="61" t="s">
+      <c r="B126" s="42" t="s">
         <v>611</v>
       </c>
-      <c r="C126" s="61" t="s">
+      <c r="C126" s="42" t="s">
         <v>612</v>
       </c>
-      <c r="D126" s="61" t="s">
+      <c r="D126" s="42" t="s">
         <v>613</v>
       </c>
-      <c r="E126" s="61" t="s">
+      <c r="E126" s="42" t="s">
         <v>614</v>
       </c>
-      <c r="F126" s="61" t="s">
+      <c r="F126" s="42" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="60" t="s">
         <v>616</v>
       </c>
-      <c r="B127" s="61" t="s">
+      <c r="B127" s="42" t="s">
         <v>617</v>
       </c>
-      <c r="C127" s="61" t="s">
+      <c r="C127" s="42" t="s">
         <v>618</v>
       </c>
-      <c r="D127" s="61" t="s">
+      <c r="D127" s="42" t="s">
         <v>619</v>
       </c>
-      <c r="E127" s="61" t="s">
+      <c r="E127" s="42" t="s">
         <v>620</v>
       </c>
-      <c r="F127" s="61" t="s">
+      <c r="F127" s="42" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="60" t="s">
         <v>622</v>
       </c>
-      <c r="B128" s="61" t="s">
+      <c r="B128" s="42" t="s">
         <v>623</v>
       </c>
-      <c r="C128" s="61" t="s">
+      <c r="C128" s="42" t="s">
         <v>624</v>
       </c>
-      <c r="D128" s="61" t="s">
+      <c r="D128" s="42" t="s">
         <v>625</v>
       </c>
-      <c r="E128" s="61" t="s">
+      <c r="E128" s="42" t="s">
         <v>626</v>
       </c>
-      <c r="F128" s="61" t="s">
+      <c r="F128" s="42" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="60" t="s">
         <v>628</v>
       </c>
-      <c r="B129" s="61" t="s">
+      <c r="B129" s="42" t="s">
         <v>629</v>
       </c>
-      <c r="C129" s="61" t="s">
+      <c r="C129" s="42" t="s">
         <v>630</v>
       </c>
-      <c r="D129" s="61" t="s">
+      <c r="D129" s="42" t="s">
         <v>631</v>
       </c>
-      <c r="E129" s="61" t="s">
+      <c r="E129" s="42" t="s">
         <v>632</v>
       </c>
-      <c r="F129" s="61" t="s">
+      <c r="F129" s="42" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="60" t="s">
         <v>634</v>
       </c>
-      <c r="B130" s="61" t="s">
+      <c r="B130" s="42" t="s">
         <v>635</v>
       </c>
-      <c r="C130" s="61" t="s">
+      <c r="C130" s="42" t="s">
         <v>636</v>
       </c>
-      <c r="D130" s="61" t="s">
+      <c r="D130" s="42" t="s">
         <v>637</v>
       </c>
-      <c r="E130" s="61" t="s">
+      <c r="E130" s="42" t="s">
         <v>638</v>
       </c>
-      <c r="F130" s="61" t="s">
+      <c r="F130" s="42" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="60" t="s">
         <v>640</v>
       </c>
-      <c r="B131" s="61" t="s">
+      <c r="B131" s="42" t="s">
         <v>641</v>
       </c>
-      <c r="C131" s="61" t="s">
+      <c r="C131" s="42" t="s">
         <v>642</v>
       </c>
-      <c r="D131" s="61" t="s">
+      <c r="D131" s="42" t="s">
         <v>643</v>
       </c>
-      <c r="E131" s="61" t="s">
+      <c r="E131" s="42" t="s">
         <v>644</v>
       </c>
-      <c r="F131" s="61" t="s">
+      <c r="F131" s="42" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="60" t="s">
         <v>646</v>
       </c>
-      <c r="B132" s="61" t="s">
+      <c r="B132" s="42" t="s">
         <v>647</v>
       </c>
-      <c r="C132" s="61" t="s">
+      <c r="C132" s="42" t="s">
         <v>648</v>
       </c>
-      <c r="D132" s="61" t="s">
+      <c r="D132" s="42" t="s">
         <v>649</v>
       </c>
-      <c r="E132" s="61" t="s">
+      <c r="E132" s="42" t="s">
         <v>650</v>
       </c>
-      <c r="F132" s="61" t="s">
+      <c r="F132" s="42" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="60" t="s">
         <v>652</v>
       </c>
-      <c r="B133" s="61" t="s">
+      <c r="B133" s="42" t="s">
         <v>653</v>
       </c>
-      <c r="C133" s="61" t="s">
+      <c r="C133" s="42" t="s">
         <v>654</v>
       </c>
-      <c r="D133" s="61" t="s">
+      <c r="D133" s="42" t="s">
         <v>655</v>
       </c>
-      <c r="E133" s="61" t="s">
+      <c r="E133" s="42" t="s">
         <v>656</v>
       </c>
-      <c r="F133" s="61" t="s">
+      <c r="F133" s="42" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="60" t="s">
         <v>658</v>
       </c>
-      <c r="B134" s="61" t="s">
+      <c r="B134" s="42" t="s">
         <v>659</v>
       </c>
-      <c r="C134" s="61" t="s">
+      <c r="C134" s="42" t="s">
         <v>660</v>
       </c>
-      <c r="D134" s="61" t="s">
+      <c r="D134" s="42" t="s">
         <v>661</v>
       </c>
-      <c r="E134" s="61" t="s">
+      <c r="E134" s="42" t="s">
         <v>662</v>
       </c>
-      <c r="F134" s="61" t="s">
+      <c r="F134" s="42" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="16.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="60" t="s">
         <v>664</v>
       </c>
-      <c r="B135" s="61" t="s">
+      <c r="B135" s="42" t="s">
         <v>665</v>
       </c>
-      <c r="C135" s="61" t="s">
+      <c r="C135" s="42" t="s">
         <v>666</v>
       </c>
-      <c r="D135" s="61" t="s">
+      <c r="D135" s="42" t="s">
         <v>667</v>
       </c>
-      <c r="E135" s="61" t="s">
+      <c r="E135" s="42" t="s">
         <v>668</v>
       </c>
-      <c r="F135" s="61" t="s">
+      <c r="F135" s="42" t="s">
         <v>669</v>
       </c>
     </row>
@@ -10236,8 +10224,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -10259,7 +10247,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="71.46"/>
   </cols>
   <sheetData>
-    <row r="1" s="63" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="62" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10278,8 +10266,8 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -10298,8 +10286,8 @@
         <v>672</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
     </row>
     <row r="3" customFormat="false" ht="135.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
@@ -10318,8 +10306,8 @@
         <v>674</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" customFormat="false" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12"/>
@@ -10328,8 +10316,8 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
     </row>
     <row r="5" customFormat="false" ht="76.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
@@ -10346,8 +10334,8 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
     </row>
     <row r="6" customFormat="false" ht="23.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17"/>
@@ -10356,8 +10344,8 @@
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
     </row>
     <row r="7" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -10374,8 +10362,8 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17"/>
@@ -10384,8 +10372,8 @@
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
       <c r="F8" s="20"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
     </row>
     <row r="9" customFormat="false" ht="101.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
@@ -10402,8 +10390,8 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
     </row>
     <row r="10" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17"/>
@@ -10412,8 +10400,8 @@
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
@@ -10432,8 +10420,8 @@
         <v>680</v>
       </c>
       <c r="F11" s="24"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25"/>
@@ -10442,8 +10430,8 @@
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="118" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
@@ -10460,8 +10448,8 @@
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="32"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33"/>
@@ -10470,8 +10458,8 @@
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="111.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
@@ -10488,8 +10476,8 @@
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="32"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
     </row>
     <row r="16" s="12" customFormat="true" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33"/>
@@ -10498,8 +10486,8 @@
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
     </row>
     <row r="17" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
@@ -10516,12 +10504,12 @@
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
     </row>
     <row r="19" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
@@ -10540,12 +10528,12 @@
         <v>686</v>
       </c>
       <c r="F19" s="32"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
     </row>
     <row r="21" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
@@ -10604,8 +10592,8 @@
       <c r="F25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" customFormat="false" ht="97.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
@@ -10624,12 +10612,12 @@
         <v>692</v>
       </c>
       <c r="F27" s="32"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" customFormat="false" ht="159.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
@@ -10688,8 +10676,8 @@
       <c r="F33" s="32"/>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
     </row>
     <row r="35" customFormat="false" ht="100.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
@@ -10708,12 +10696,12 @@
         <v>698</v>
       </c>
       <c r="F35" s="32"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
     </row>
     <row r="37" customFormat="false" ht="108.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
@@ -10730,13 +10718,13 @@
       </c>
       <c r="E37" s="30"/>
       <c r="F37" s="32"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
     </row>
     <row r="39" customFormat="false" ht="88.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
@@ -10753,13 +10741,13 @@
       </c>
       <c r="E39" s="30"/>
       <c r="F39" s="32"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="33"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
     </row>
     <row r="41" customFormat="false" ht="98.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="29" t="s">
@@ -10776,72 +10764,72 @@
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="32"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
     </row>
     <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
     </row>
     <row r="46" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G46" s="64"/>
-      <c r="H46" s="64"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G47" s="64"/>
-      <c r="H47" s="64"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
     </row>
     <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G50" s="64"/>
-      <c r="H50" s="64"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G51" s="64"/>
-      <c r="H51" s="64"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G52" s="64"/>
-      <c r="H52" s="64"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G54" s="64"/>
-      <c r="H54" s="64"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10867,35 +10855,35 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="35" width="19.8"/>
   </cols>
   <sheetData>
-    <row r="1" s="72" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="66" t="s">
+    <row r="1" s="71" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="66" t="s">
         <v>703</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="67" t="s">
         <v>704</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="69" t="s">
+      <c r="G1" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="70" t="s">
+      <c r="I1" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="71"/>
+      <c r="J1" s="70"/>
       <c r="L1" s="39"/>
       <c r="M1" s="39"/>
       <c r="N1" s="39"/>
@@ -10930,16 +10918,16 @@
       <c r="XFD1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="74" t="n">
+      <c r="B2" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="74" t="n">
+      <c r="C2" s="73" t="n">
         <v>2273097</v>
       </c>
-      <c r="D2" s="75" t="n">
+      <c r="D2" s="74" t="n">
         <v>2095051</v>
       </c>
       <c r="E2" s="42" t="n">
@@ -10990,16 +10978,16 @@
       <c r="AO2" s="35"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="72" t="s">
         <v>705</v>
       </c>
-      <c r="B3" s="74" t="n">
+      <c r="B3" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="74" t="n">
+      <c r="C3" s="73" t="n">
         <v>231073</v>
       </c>
-      <c r="D3" s="75" t="n">
+      <c r="D3" s="74" t="n">
         <v>172846</v>
       </c>
       <c r="E3" s="42" t="n">
@@ -11050,16 +11038,16 @@
       <c r="AO3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="72" t="s">
         <v>706</v>
       </c>
-      <c r="B4" s="74" t="n">
+      <c r="B4" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="74" t="n">
+      <c r="C4" s="73" t="n">
         <v>128027</v>
       </c>
-      <c r="D4" s="75" t="n">
+      <c r="D4" s="74" t="n">
         <v>128014</v>
       </c>
       <c r="E4" s="42" t="n">
@@ -11110,16 +11098,16 @@
       <c r="AO4" s="35"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="72" t="s">
         <v>707</v>
       </c>
-      <c r="B5" s="74" t="n">
+      <c r="B5" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="74" t="n">
+      <c r="C5" s="73" t="n">
         <v>158930</v>
       </c>
-      <c r="D5" s="75" t="n">
+      <c r="D5" s="74" t="n">
         <v>90694</v>
       </c>
       <c r="E5" s="42" t="n">
@@ -11170,16 +11158,16 @@
       <c r="AO5" s="35"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="72" t="s">
         <v>708</v>
       </c>
-      <c r="B6" s="74" t="n">
+      <c r="B6" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="74" t="n">
+      <c r="C6" s="73" t="n">
         <v>10293</v>
       </c>
-      <c r="D6" s="75" t="n">
+      <c r="D6" s="74" t="n">
         <v>10286</v>
       </c>
       <c r="E6" s="42" t="n">
@@ -11230,16 +11218,16 @@
       <c r="AO6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="72" t="s">
         <v>709</v>
       </c>
-      <c r="B7" s="74" t="n">
+      <c r="B7" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="74" t="n">
+      <c r="C7" s="73" t="n">
         <v>7938</v>
       </c>
-      <c r="D7" s="75" t="n">
+      <c r="D7" s="74" t="n">
         <v>5931</v>
       </c>
       <c r="E7" s="42" t="n">
@@ -11290,16 +11278,16 @@
       <c r="AO7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="72" t="s">
         <v>710</v>
       </c>
-      <c r="B8" s="74" t="n">
+      <c r="B8" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="74" t="n">
+      <c r="C8" s="73" t="n">
         <v>5796</v>
       </c>
-      <c r="D8" s="75" t="n">
+      <c r="D8" s="74" t="n">
         <v>5385</v>
       </c>
       <c r="E8" s="42" t="n">
@@ -11350,16 +11338,16 @@
       <c r="AO8" s="35"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="72" t="s">
         <v>711</v>
       </c>
-      <c r="B9" s="74" t="n">
+      <c r="B9" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="74" t="n">
+      <c r="C9" s="73" t="n">
         <v>5499</v>
       </c>
-      <c r="D9" s="75" t="n">
+      <c r="D9" s="74" t="n">
         <v>5228</v>
       </c>
       <c r="E9" s="42" t="n">
@@ -11410,16 +11398,16 @@
       <c r="AO9" s="35"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="72" t="s">
         <v>712</v>
       </c>
-      <c r="B10" s="74" t="n">
+      <c r="B10" s="73" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="74" t="n">
+      <c r="C10" s="73" t="n">
         <v>5897</v>
       </c>
-      <c r="D10" s="75" t="n">
+      <c r="D10" s="74" t="n">
         <v>3219</v>
       </c>
       <c r="E10" s="42" t="n">
@@ -11470,16 +11458,16 @@
       <c r="AO10" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="74" t="n">
+      <c r="B11" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="74" t="n">
+      <c r="C11" s="73" t="n">
         <v>1966</v>
       </c>
-      <c r="D11" s="75" t="n">
+      <c r="D11" s="74" t="n">
         <v>1948</v>
       </c>
       <c r="E11" s="42" t="n">
@@ -11529,17 +11517,17 @@
       <c r="AN11" s="35"/>
       <c r="AO11" s="35"/>
     </row>
-    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="73" t="s">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="72" t="s">
         <v>713</v>
       </c>
-      <c r="B12" s="74" t="n">
+      <c r="B12" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="74" t="n">
+      <c r="C12" s="73" t="n">
         <v>1507</v>
       </c>
-      <c r="D12" s="75" t="n">
+      <c r="D12" s="74" t="n">
         <v>1470</v>
       </c>
       <c r="E12" s="42" t="n">
@@ -11590,16 +11578,16 @@
       <c r="AO12" s="35"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="72" t="s">
         <v>714</v>
       </c>
-      <c r="B13" s="74" t="n">
+      <c r="B13" s="73" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="74" t="n">
+      <c r="C13" s="73" t="n">
         <v>652</v>
       </c>
-      <c r="D13" s="75" t="n">
+      <c r="D13" s="74" t="n">
         <v>652</v>
       </c>
       <c r="E13" s="42" t="n">
@@ -11620,16 +11608,16 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="72" t="s">
         <v>715</v>
       </c>
-      <c r="B14" s="74" t="n">
+      <c r="B14" s="73" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="74" t="n">
+      <c r="C14" s="73" t="n">
         <v>36</v>
       </c>
-      <c r="D14" s="75" t="n">
+      <c r="D14" s="74" t="n">
         <v>36</v>
       </c>
       <c r="E14" s="42" t="n">
@@ -11650,16 +11638,16 @@
       <c r="K14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="72" t="s">
         <v>716</v>
       </c>
-      <c r="B15" s="74" t="n">
+      <c r="B15" s="73" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="74" t="n">
+      <c r="C15" s="73" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="75" t="n">
+      <c r="D15" s="74" t="n">
         <v>21</v>
       </c>
       <c r="E15" s="42" t="n">
@@ -11680,16 +11668,16 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="75" t="s">
         <v>717</v>
       </c>
-      <c r="B16" s="77" t="n">
+      <c r="B16" s="76" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="77" t="n">
+      <c r="C16" s="76" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="77" t="n">
+      <c r="D16" s="76" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="49" t="n">
@@ -11741,17 +11729,17 @@
       <c r="K17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="78"/>
+      <c r="E18" s="77"/>
       <c r="I18" s="35"/>
       <c r="K18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="78"/>
+      <c r="E19" s="77"/>
       <c r="I19" s="35"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="78" t="s">
         <v>90</v>
       </c>
       <c r="C20" s="42" t="n">
@@ -12001,7 +11989,7 @@
     </row>
     <row r="29" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" s="56" t="s">
         <v>120</v>
@@ -12066,7 +12054,7 @@
     </row>
     <row r="30" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>129</v>
@@ -12131,7 +12119,7 @@
     </row>
     <row r="31" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="56" t="s">
         <v>135</v>
@@ -12196,7 +12184,7 @@
     </row>
     <row r="32" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B32" s="56" t="s">
         <v>143</v>
@@ -12261,7 +12249,7 @@
     </row>
     <row r="33" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B33" s="56" t="s">
         <v>149</v>
@@ -12326,7 +12314,7 @@
     </row>
     <row r="34" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>155</v>
@@ -12391,7 +12379,7 @@
     </row>
     <row r="35" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>161</v>
@@ -12456,7 +12444,7 @@
     </row>
     <row r="36" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B36" s="56" t="s">
         <v>167</v>
@@ -12521,7 +12509,7 @@
     </row>
     <row r="37" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B37" s="56" t="s">
         <v>176</v>
@@ -12586,7 +12574,7 @@
     </row>
     <row r="38" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>185</v>
@@ -12651,7 +12639,7 @@
     </row>
     <row r="39" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B39" s="56" t="s">
         <v>194</v>
@@ -12716,7 +12704,7 @@
     </row>
     <row r="40" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B40" s="56" t="s">
         <v>203</v>
@@ -12781,7 +12769,7 @@
     </row>
     <row r="41" s="35" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B41" s="56" t="s">
         <v>212</v>
@@ -13437,7 +13425,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>17</v>
       </c>
@@ -13507,7 +13495,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="56" t="n">
         <v>20</v>
       </c>
@@ -13553,26 +13541,26 @@
       <c r="F82" s="35"/>
     </row>
     <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="80"/>
-      <c r="B83" s="81" t="s">
+      <c r="A83" s="59"/>
+      <c r="B83" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="C83" s="81" t="s">
+      <c r="C83" s="60" t="s">
         <v>342</v>
       </c>
-      <c r="D83" s="81" t="s">
+      <c r="D83" s="60" t="s">
         <v>343</v>
       </c>
-      <c r="E83" s="81" t="s">
+      <c r="E83" s="60" t="s">
         <v>344</v>
       </c>
-      <c r="F83" s="81" t="s">
+      <c r="F83" s="60" t="s">
         <v>345</v>
       </c>
-      <c r="I83" s="79"/>
+      <c r="I83" s="78"/>
     </row>
     <row r="84" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="81" t="s">
+      <c r="A84" s="60" t="s">
         <v>945</v>
       </c>
       <c r="B84" s="42" t="s">
@@ -13592,7 +13580,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="81" t="s">
+      <c r="A85" s="60" t="s">
         <v>358</v>
       </c>
       <c r="B85" s="42" t="s">
@@ -13612,7 +13600,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="81" t="s">
+      <c r="A86" s="60" t="s">
         <v>956</v>
       </c>
       <c r="B86" s="42" t="s">
@@ -13632,7 +13620,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="81" t="s">
+      <c r="A87" s="60" t="s">
         <v>962</v>
       </c>
       <c r="B87" s="42" t="s">
@@ -13651,8 +13639,8 @@
         <v>967</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="81" t="s">
+    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="60" t="s">
         <v>968</v>
       </c>
       <c r="B88" s="42" t="s">
@@ -13671,8 +13659,8 @@
         <v>973</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="81" t="s">
+    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="60" t="s">
         <v>974</v>
       </c>
       <c r="B89" s="42" t="s">
@@ -13691,8 +13679,8 @@
         <v>979</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="81" t="s">
+    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="60" t="s">
         <v>980</v>
       </c>
       <c r="B90" s="42" t="s">
@@ -13711,8 +13699,8 @@
         <v>985</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="81" t="s">
+    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="60" t="s">
         <v>986</v>
       </c>
       <c r="B91" s="42" t="s">
@@ -13731,8 +13719,8 @@
         <v>991</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="81" t="s">
+    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="60" t="s">
         <v>992</v>
       </c>
       <c r="B92" s="42" t="s">
@@ -13751,8 +13739,8 @@
         <v>997</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="81" t="s">
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="60" t="s">
         <v>998</v>
       </c>
       <c r="B93" s="42" t="s">
@@ -13771,8 +13759,8 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="81" t="s">
+    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="60" t="s">
         <v>1004</v>
       </c>
       <c r="B94" s="42" t="s">
@@ -13791,8 +13779,8 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="81" t="s">
+    <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="60" t="s">
         <v>448</v>
       </c>
       <c r="B95" s="42" t="s">
@@ -13811,8 +13799,8 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="81" t="s">
+    <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="60" t="s">
         <v>454</v>
       </c>
       <c r="B96" s="42" t="s">
@@ -13831,8 +13819,8 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="81" t="s">
+    <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="60" t="s">
         <v>460</v>
       </c>
       <c r="B97" s="42" t="s">
@@ -13851,8 +13839,8 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="81" t="s">
+    <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="60" t="s">
         <v>466</v>
       </c>
       <c r="B98" s="42" t="s">
@@ -13871,8 +13859,8 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="81" t="s">
+    <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="60" t="s">
         <v>478</v>
       </c>
       <c r="B99" s="42" t="s">
@@ -13891,8 +13879,8 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="81" t="s">
+    <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="60" t="s">
         <v>484</v>
       </c>
       <c r="B100" s="42" t="s">
@@ -13911,8 +13899,8 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="81" t="s">
+    <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="60" t="s">
         <v>496</v>
       </c>
       <c r="B101" s="42" t="s">
@@ -13931,8 +13919,8 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="81" t="s">
+    <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="60" t="s">
         <v>1045</v>
       </c>
       <c r="B102" s="42" t="s">
@@ -13951,8 +13939,8 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="81" t="s">
+    <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="60" t="s">
         <v>508</v>
       </c>
       <c r="B103" s="42" t="s">
@@ -13971,8 +13959,8 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="81" t="s">
+    <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="60" t="s">
         <v>514</v>
       </c>
       <c r="B104" s="42" t="s">
@@ -13991,8 +13979,8 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="81" t="s">
+    <row r="105" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="60" t="s">
         <v>520</v>
       </c>
       <c r="B105" s="42" t="s">
@@ -14011,8 +13999,8 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="81" t="s">
+    <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="60" t="s">
         <v>526</v>
       </c>
       <c r="B106" s="42" t="s">
@@ -14031,8 +14019,8 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="81" t="s">
+    <row r="107" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="60" t="s">
         <v>532</v>
       </c>
       <c r="B107" s="42" t="s">
@@ -14051,8 +14039,8 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="81" t="s">
+    <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="60" t="s">
         <v>1076</v>
       </c>
       <c r="B108" s="42" t="s">
@@ -14071,8 +14059,8 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="81" t="s">
+    <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="60" t="s">
         <v>1082</v>
       </c>
       <c r="B109" s="42" t="s">
@@ -14091,8 +14079,8 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="81" t="s">
+    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="60" t="s">
         <v>1088</v>
       </c>
       <c r="B110" s="42" t="s">
@@ -14111,8 +14099,8 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="81" t="s">
+    <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="60" t="s">
         <v>1094</v>
       </c>
       <c r="B111" s="42" t="s">
@@ -14131,8 +14119,8 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="81" t="s">
+    <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="60" t="s">
         <v>1100</v>
       </c>
       <c r="B112" s="42" t="s">
@@ -14151,8 +14139,8 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="81" t="s">
+    <row r="113" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="60" t="s">
         <v>1106</v>
       </c>
       <c r="B113" s="42" t="s">
@@ -14171,8 +14159,8 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="81" t="s">
+    <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="60" t="s">
         <v>1112</v>
       </c>
       <c r="B114" s="42" t="s">
@@ -14191,8 +14179,8 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="81" t="s">
+    <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="60" t="s">
         <v>1118</v>
       </c>
       <c r="B115" s="42" t="s">
@@ -14211,8 +14199,8 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="81" t="s">
+    <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="60" t="s">
         <v>1124</v>
       </c>
       <c r="B116" s="42" t="s">
@@ -14231,8 +14219,8 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="81" t="s">
+    <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="60" t="s">
         <v>1130</v>
       </c>
       <c r="B117" s="42" t="s">
@@ -14251,8 +14239,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="81" t="s">
+    <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="60" t="s">
         <v>1136</v>
       </c>
       <c r="B118" s="42" t="s">
@@ -14271,8 +14259,8 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="81" t="s">
+    <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="60" t="s">
         <v>1142</v>
       </c>
       <c r="B119" s="42" t="s">
@@ -14291,8 +14279,8 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="81" t="s">
+    <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="60" t="s">
         <v>1148</v>
       </c>
       <c r="B120" s="42" t="s">
@@ -14311,8 +14299,8 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="81" t="s">
+    <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="60" t="s">
         <v>1154</v>
       </c>
       <c r="B121" s="42" t="s">
@@ -14331,8 +14319,8 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="81" t="s">
+    <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="60" t="s">
         <v>1160</v>
       </c>
       <c r="B122" s="42" t="s">
@@ -14351,8 +14339,8 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="81" t="s">
+    <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="60" t="s">
         <v>1166</v>
       </c>
       <c r="B123" s="42" t="s">
@@ -14371,8 +14359,8 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="81" t="s">
+    <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="60" t="s">
         <v>1172</v>
       </c>
       <c r="B124" s="42" t="s">
@@ -14391,8 +14379,8 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="81" t="s">
+    <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="60" t="s">
         <v>1178</v>
       </c>
       <c r="B125" s="42" t="s">
@@ -14411,8 +14399,8 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="81" t="s">
+    <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="60" t="s">
         <v>628</v>
       </c>
       <c r="B126" s="42" t="s">
@@ -14431,8 +14419,8 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="81" t="s">
+    <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="60" t="s">
         <v>634</v>
       </c>
       <c r="B127" s="42" t="s">
@@ -14451,8 +14439,8 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="81" t="s">
+    <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="60" t="s">
         <v>640</v>
       </c>
       <c r="B128" s="42" t="s">
@@ -14471,8 +14459,8 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="81" t="s">
+    <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="60" t="s">
         <v>646</v>
       </c>
       <c r="B129" s="42" t="s">
@@ -14491,8 +14479,8 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="81" t="s">
+    <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="60" t="s">
         <v>1204</v>
       </c>
       <c r="B130" s="42" t="s">
@@ -14516,8 +14504,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -14531,7 +14519,7 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="10.18359375" defaultRowHeight="16.15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="82" width="36.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="79" width="36.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="90.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="77.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="65.07"/>
@@ -14540,733 +14528,733 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83" t="s">
+      <c r="E1" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="81" t="s">
         <v>1210</v>
       </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83" t="s">
         <v>1211</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="83" t="s">
         <v>1212</v>
       </c>
-      <c r="F2" s="87"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
     </row>
     <row r="3" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86" t="s">
+      <c r="A3" s="82"/>
+      <c r="B3" s="83" t="s">
         <v>1213</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="85" t="s">
         <v>1214</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="E3" s="83" t="s">
         <v>1212</v>
       </c>
-      <c r="F3" s="87"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="83" t="s">
         <v>1215</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="85" t="s">
         <v>1216</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="83" t="s">
         <v>1217</v>
       </c>
-      <c r="F4" s="87"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" customFormat="false" ht="85.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="85"/>
-      <c r="B5" s="86" t="s">
+      <c r="A5" s="82"/>
+      <c r="B5" s="83" t="s">
         <v>1218</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="85" t="s">
         <v>1214</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="83" t="s">
         <v>1217</v>
       </c>
-      <c r="E5" s="86" t="s">
+      <c r="E5" s="83" t="s">
         <v>1212</v>
       </c>
-      <c r="F5" s="87"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="75.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86" t="s">
+      <c r="A6" s="82"/>
+      <c r="B6" s="83" t="s">
         <v>1219</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="85" t="s">
         <v>1220</v>
       </c>
-      <c r="D6" s="86" t="s">
+      <c r="D6" s="83" t="s">
         <v>1217</v>
       </c>
-      <c r="E6" s="88" t="s">
+      <c r="E6" s="85" t="s">
         <v>1221</v>
       </c>
-      <c r="F6" s="87"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="224.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="82" t="s">
         <v>1222</v>
       </c>
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="86" t="s">
         <v>1223</v>
       </c>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="87" t="s">
         <v>1224</v>
       </c>
-      <c r="D7" s="90" t="s">
+      <c r="D7" s="87" t="s">
         <v>1225</v>
       </c>
-      <c r="E7" s="90" t="s">
+      <c r="E7" s="87" t="s">
         <v>1226</v>
       </c>
-      <c r="F7" s="87"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="86" t="s">
         <v>1227</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="87" t="s">
         <v>1228</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="87" t="s">
         <v>1225</v>
       </c>
-      <c r="E8" s="90" t="s">
+      <c r="E8" s="87" t="s">
         <v>1229</v>
       </c>
-      <c r="F8" s="87"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="86" t="s">
         <v>1230</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="87" t="s">
         <v>1224</v>
       </c>
-      <c r="D9" s="90" t="s">
+      <c r="D9" s="87" t="s">
         <v>1229</v>
       </c>
-      <c r="E9" s="90" t="s">
+      <c r="E9" s="87" t="s">
         <v>1231</v>
       </c>
-      <c r="F9" s="87"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="106.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="89" t="s">
         <v>1232</v>
       </c>
-      <c r="C10" s="93" t="s">
+      <c r="C10" s="90" t="s">
         <v>1233</v>
       </c>
-      <c r="D10" s="93" t="s">
+      <c r="D10" s="90" t="s">
         <v>1225</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="E10" s="90" t="s">
         <v>1234</v>
       </c>
       <c r="F10" s="24"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
     </row>
     <row r="11" customFormat="false" ht="242.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="94" t="s">
+      <c r="A11" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="92" t="s">
         <v>1235</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="93" t="s">
         <v>1224</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="93" t="s">
         <v>1234</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="93" t="s">
         <v>1236</v>
       </c>
-      <c r="F11" s="97"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
     </row>
     <row r="12" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="93" t="s">
         <v>1237</v>
       </c>
-      <c r="C12" s="96" t="s">
+      <c r="C12" s="93" t="s">
         <v>1238</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="93" t="s">
         <v>1239</v>
       </c>
-      <c r="E12" s="96"/>
-      <c r="F12" s="98" t="s">
+      <c r="E12" s="93"/>
+      <c r="F12" s="95" t="s">
         <v>1240</v>
       </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
     </row>
     <row r="13" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="93" t="s">
         <v>1241</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="93" t="s">
         <v>1242</v>
       </c>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="93" t="s">
         <v>1243</v>
       </c>
-      <c r="E13" s="96"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
     </row>
     <row r="14" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
+      <c r="A14" s="96"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="15" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="102"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="90" t="s">
         <v>1244</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="90" t="s">
         <v>1228</v>
       </c>
-      <c r="D16" s="93" t="s">
+      <c r="D16" s="90" t="s">
         <v>1245</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="90" t="s">
         <v>1246</v>
       </c>
-      <c r="F16" s="105"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
     </row>
     <row r="17" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="96" t="s">
+      <c r="B17" s="93" t="s">
         <v>1247</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="93" t="s">
         <v>1224</v>
       </c>
-      <c r="D17" s="96" t="s">
+      <c r="D17" s="93" t="s">
         <v>1246</v>
       </c>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="93" t="s">
         <v>1248</v>
       </c>
-      <c r="F17" s="98"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" customFormat="false" ht="184.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="106" t="s">
+      <c r="A18" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="104" t="s">
         <v>1249</v>
       </c>
-      <c r="C18" s="107" t="s">
+      <c r="C18" s="104" t="s">
         <v>1238</v>
       </c>
-      <c r="D18" s="107" t="s">
+      <c r="D18" s="104" t="s">
         <v>1250</v>
       </c>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108" t="s">
+      <c r="E18" s="104"/>
+      <c r="F18" s="105" t="s">
         <v>1251</v>
       </c>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
     </row>
     <row r="19" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="100" t="s">
+      <c r="B19" s="97" t="s">
         <v>1252</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="97" t="s">
         <v>1242</v>
       </c>
-      <c r="D19" s="100" t="s">
+      <c r="D19" s="97" t="s">
         <v>1253</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
     </row>
     <row r="20" customFormat="false" ht="207.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
+      <c r="A20" s="96"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
     </row>
     <row r="21" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="109"/>
-      <c r="B21" s="110"/>
-      <c r="C21" s="110"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
     </row>
     <row r="22" customFormat="false" ht="172.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="92" t="s">
+      <c r="B22" s="89" t="s">
         <v>1254</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C22" s="90" t="s">
         <v>1233</v>
       </c>
-      <c r="D22" s="93" t="s">
+      <c r="D22" s="90" t="s">
         <v>1225</v>
       </c>
-      <c r="E22" s="93" t="s">
+      <c r="E22" s="90" t="s">
         <v>1255</v>
       </c>
       <c r="F22" s="24"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="63"/>
     </row>
     <row r="23" customFormat="false" ht="256.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="94" t="s">
+      <c r="A23" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="92" t="s">
         <v>1256</v>
       </c>
-      <c r="C23" s="96" t="s">
+      <c r="C23" s="93" t="s">
         <v>1224</v>
       </c>
-      <c r="D23" s="96" t="s">
+      <c r="D23" s="93" t="s">
         <v>1255</v>
       </c>
-      <c r="E23" s="96" t="s">
+      <c r="E23" s="93" t="s">
         <v>1257</v>
       </c>
-      <c r="F23" s="97"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="63"/>
     </row>
     <row r="24" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="107" t="s">
+      <c r="B24" s="104" t="s">
         <v>1258</v>
       </c>
-      <c r="C24" s="107" t="s">
+      <c r="C24" s="104" t="s">
         <v>1238</v>
       </c>
-      <c r="D24" s="107" t="s">
+      <c r="D24" s="104" t="s">
         <v>1259</v>
       </c>
-      <c r="E24" s="107"/>
-      <c r="F24" s="108" t="s">
+      <c r="E24" s="104"/>
+      <c r="F24" s="105" t="s">
         <v>1260</v>
       </c>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
     </row>
     <row r="25" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="100" t="s">
+      <c r="B25" s="97" t="s">
         <v>1261</v>
       </c>
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="97" t="s">
         <v>1242</v>
       </c>
-      <c r="D25" s="100" t="s">
+      <c r="D25" s="97" t="s">
         <v>1262</v>
       </c>
-      <c r="E25" s="100"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
     </row>
     <row r="26" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="99"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
+      <c r="A26" s="96"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="63"/>
     </row>
     <row r="27" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="102"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
     </row>
     <row r="28" customFormat="false" ht="114.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="91" t="s">
+      <c r="A28" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="90" t="s">
         <v>1263</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="90" t="s">
         <v>1228</v>
       </c>
-      <c r="D28" s="93" t="s">
+      <c r="D28" s="90" t="s">
         <v>1264</v>
       </c>
-      <c r="E28" s="93" t="s">
+      <c r="E28" s="90" t="s">
         <v>1265</v>
       </c>
-      <c r="F28" s="105"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
     </row>
     <row r="29" customFormat="false" ht="195.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="93" t="s">
         <v>1266</v>
       </c>
-      <c r="C29" s="96" t="s">
+      <c r="C29" s="93" t="s">
         <v>1224</v>
       </c>
-      <c r="D29" s="96" t="s">
+      <c r="D29" s="93" t="s">
         <v>1265</v>
       </c>
-      <c r="E29" s="96" t="s">
+      <c r="E29" s="93" t="s">
         <v>1267</v>
       </c>
-      <c r="F29" s="98"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="63"/>
     </row>
     <row r="30" customFormat="false" ht="199" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="106" t="s">
+      <c r="A30" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="107" t="s">
+      <c r="B30" s="104" t="s">
         <v>1268</v>
       </c>
-      <c r="C30" s="107" t="s">
+      <c r="C30" s="104" t="s">
         <v>1238</v>
       </c>
-      <c r="D30" s="107" t="s">
+      <c r="D30" s="104" t="s">
         <v>1269</v>
       </c>
-      <c r="E30" s="107"/>
-      <c r="F30" s="108" t="s">
+      <c r="E30" s="104"/>
+      <c r="F30" s="105" t="s">
         <v>1270</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
     </row>
     <row r="31" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="99" t="s">
+      <c r="A31" s="96" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="100" t="s">
+      <c r="B31" s="97" t="s">
         <v>1271</v>
       </c>
-      <c r="C31" s="100" t="s">
+      <c r="C31" s="97" t="s">
         <v>1242</v>
       </c>
-      <c r="D31" s="100" t="s">
+      <c r="D31" s="97" t="s">
         <v>1272</v>
       </c>
-      <c r="E31" s="100"/>
-      <c r="F31" s="101"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
     </row>
     <row r="32" customFormat="false" ht="153.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="99"/>
-      <c r="B32" s="100"/>
-      <c r="C32" s="100"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
+      <c r="A32" s="96"/>
+      <c r="B32" s="97"/>
+      <c r="C32" s="97"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
     </row>
     <row r="33" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="102"/>
-      <c r="B33" s="112"/>
-      <c r="C33" s="112"/>
-      <c r="D33" s="112"/>
-      <c r="E33" s="112"/>
-      <c r="F33" s="113"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
     </row>
     <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="63"/>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -15292,32 +15280,32 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.47"/>
   </cols>
   <sheetData>
-    <row r="1" s="115" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="66" t="s">
+    <row r="1" s="112" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="66" t="s">
         <v>1273</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="66" t="s">
         <v>1274</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="111" t="s">
         <v>58</v>
       </c>
       <c r="XFC1" s="1"/>
@@ -15714,7 +15702,7 @@
       <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="113" t="s">
         <v>717</v>
       </c>
       <c r="B15" s="48" t="n">
@@ -17033,7 +17021,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="56" t="n">
         <v>17</v>
       </c>
@@ -17103,7 +17091,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="56" t="n">
         <v>20</v>
       </c>
@@ -17536,8 +17524,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
